--- a/merged_df.xlsx
+++ b/merged_df.xlsx
@@ -591,12 +591,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>UG2, UG1, OG2, OG3</t>
+          <t>OG3, UG2, UG1, OG2</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>-8.2, -3.78, 7.939, 11.947</t>
+          <t>11.947, -8.2, -3.78, 7.939</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -616,12 +616,12 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0emPRSOwnDOOTgYleM3B_A, 2g6H0ojnvDdueYpZ_5Zux8, 1rOBySJhH5b9YWwDU_guK1, 2Ru4iRmYDDDfo5eLHGZ8RE</t>
+          <t>2Ru4iRmYDDDfo5eLHGZ8RE, 0emPRSOwnDOOTgYleM3B_A, 2g6H0ojnvDdueYpZ_5Zux8, 1rOBySJhH5b9YWwDU_guK1</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>1224, 1225, 1226, 1227</t>
+          <t>1219, 1227, 1228, 1229</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -686,12 +686,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>OG2, OG3, UG2, UG1, EG, OG1</t>
+          <t>EG, OG1, OG2, OG3, UG2, UG1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>7.939, 11.947, -8.2, -3.78, 0.0, 2.998</t>
+          <t>0.0, 2.998, 7.939, 11.947, -8.2, -3.78</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
@@ -707,12 +707,12 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>18j2PWjBz3nhKzSkJrvM7d, 0wtQ7wfjD5FPd24jrI75yq, 13LOp07jD0lfjp1Ds2xiaX, 3BN76u7jD8SONfck_e054E, 1R$FLavrj8G9Rxnz3lVckG, 0CIMZOOqj8GukY8gSKgU97</t>
+          <t>1R$FLavrj8G9Rxnz3lVckG, 0CIMZOOqj8GukY8gSKgU97, 18j2PWjBz3nhKzSkJrvM7d, 0wtQ7wfjD5FPd24jrI75yq, 13LOp07jD0lfjp1Ds2xiaX, 3BN76u7jD8SONfck_e054E</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>1215, 1216, 1219, 1220, 1221, 1222</t>
+          <t>1215, 1216, 1217, 1218, 1223, 1224</t>
         </is>
       </c>
       <c r="Q3" t="n">
@@ -806,12 +806,12 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>34G_SBUtD7Bx_aSDXbyBOH, 11GLlly7bCgPkVa3553rnS, 3Q30KcAwrFjgFId43DWY8P</t>
+          <t>3Q30KcAwrFjgFId43DWY8P, 34G_SBUtD7Bx_aSDXbyBOH, 11GLlly7bCgPkVa3553rnS</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>1217, 1218, 1228</t>
+          <t>1220, 1221, 1222</t>
         </is>
       </c>
       <c r="Q4" t="n">
@@ -823,7 +823,7 @@
         </is>
       </c>
       <c r="S4" t="n">
-        <v>97.874376</v>
+        <v>97.87437599999998</v>
       </c>
       <c r="T4" t="n">
         <v>39.08309449999999</v>
@@ -905,12 +905,12 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>1830E3dHD5f9qhMIKx9HB6, 14zTAK7eDFxu25AGckILdY, 3_49$ldkHAGOZei44e_8FY, 0jRMZ$SnH9ouX0ZQEwstxo</t>
+          <t>0jRMZ$SnH9ouX0ZQEwstxo, 1830E3dHD5f9qhMIKx9HB6, 14zTAK7eDFxu25AGckILdY, 3_49$ldkHAGOZei44e_8FY</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>1223, 1232, 1233, 1234</t>
+          <t>1225, 1226, 1234, 1235</t>
         </is>
       </c>
       <c r="Q5" t="n">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>1252</t>
+          <t>1254</t>
         </is>
       </c>
       <c r="Q7" t="n">
@@ -1167,7 +1167,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>1255</t>
+          <t>1257</t>
         </is>
       </c>
       <c r="Q8" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>1246</t>
+          <t>1248</t>
         </is>
       </c>
       <c r="Q9" t="n">
@@ -1335,12 +1335,12 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>OG3, EG</t>
+          <t>EG, OG3</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>11.947, 0.0</t>
+          <t>0.0, 11.947</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1360,12 +1360,12 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>2VPJztHKzE5eU2jmaJhVnb, 360G1aSpvFCuurfPO7oVVK, 2gK95MKEPE$O83dwER37Qp, 2u0jNhx4PBahQiA_Mn0fAT, 1XvgrEk2L7Sf0_v9d5iT66, 02z0dETOLCdvSjB6spGLDD, 2dWGfk8A5FP9hGnKCxZb2t, 2smUqi2i10zRE_diOVjJhu, 3Dk2HhiCr35RYXuSaVOvs6, 3AGSwy4Cv9YOBE5MpdNLQt, 0E4QXUam15QfaVaTAymHn2, 0WtOOP9cn9MBUnf0AHUQfJ</t>
+          <t>2smUqi2i10zRE_diOVjJhu, 2VPJztHKzE5eU2jmaJhVnb, 360G1aSpvFCuurfPO7oVVK, 2gK95MKEPE$O83dwER37Qp, 0WtOOP9cn9MBUnf0AHUQfJ, 2u0jNhx4PBahQiA_Mn0fAT, 1XvgrEk2L7Sf0_v9d5iT66, 02z0dETOLCdvSjB6spGLDD, 2dWGfk8A5FP9hGnKCxZb2t, 3Dk2HhiCr35RYXuSaVOvs6, 3AGSwy4Cv9YOBE5MpdNLQt, 0E4QXUam15QfaVaTAymHn2</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>1235, 1236, 1237, 1240, 1241, 1242, 1243, 1244, 1247, 1248, 1249, 1250</t>
+          <t>1236, 1237, 1238, 1239, 1241, 1242, 1243, 1244, 1245, 1249, 1250, 1251</t>
         </is>
       </c>
       <c r="Q10" t="n">
@@ -1377,7 +1377,7 @@
         </is>
       </c>
       <c r="S10" t="n">
-        <v>784.1024639999999</v>
+        <v>784.1024640000001</v>
       </c>
       <c r="T10" t="n">
         <v>0</v>
@@ -1386,7 +1386,7 @@
         <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>693.2650894999999</v>
+        <v>693.2650895</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
@@ -1508,12 +1508,12 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>2VPSmwn8f80wlwsZLQwj7f, 3vBeHUwhfB5OcVQruWBfzN, 2MZESDDfb379fB261rIbnR</t>
+          <t>2MZESDDfb379fB261rIbnR, 2VPSmwn8f80wlwsZLQwj7f, 3vBeHUwhfB5OcVQruWBfzN</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>1251, 1257, 1258</t>
+          <t>1252, 1253, 1259</t>
         </is>
       </c>
       <c r="Q12" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>1261</t>
+          <t>1256</t>
         </is>
       </c>
       <c r="Q13" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>1256</t>
+          <t>1258</t>
         </is>
       </c>
       <c r="Q14" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>1253</t>
+          <t>1255</t>
         </is>
       </c>
       <c r="Q15" t="n">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>2vZ$D3URf34vJnBMMHx9xX, 1D6v$lAcHDiAsIdGYCYrg4, 14Y66SGP5Fm8iYaOLsp2V8, 0XbzWrb4P70RH_r69FZvNC, 3vSADXkCf9CehgpLlu0Bds</t>
+          <t>3vSADXkCf9CehgpLlu0Bds, 2vZ$D3URf34vJnBMMHx9xX, 1D6v$lAcHDiAsIdGYCYrg4, 14Y66SGP5Fm8iYaOLsp2V8, 0XbzWrb4P70RH_r69FZvNC</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>1229, 1230, 1231, 1238, 1239</t>
+          <t>1230, 1231, 1232, 1233, 1240</t>
         </is>
       </c>
       <c r="Q16" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>1254</t>
+          <t>1246</t>
         </is>
       </c>
       <c r="Q17" t="n">
@@ -2127,7 +2127,7 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>1245</t>
+          <t>1247</t>
         </is>
       </c>
       <c r="Q18" t="n">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>1260</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="Q34" t="n">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>1264, 1265</t>
+          <t>1265, 1266</t>
         </is>
       </c>
       <c r="Q35" t="n">
@@ -3809,7 +3809,7 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>1266</t>
+          <t>1260</t>
         </is>
       </c>
       <c r="Q36" t="n">
@@ -3914,7 +3914,7 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>1259</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="Q37" t="n">
@@ -4677,7 +4677,7 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>1272</t>
+          <t>1274</t>
         </is>
       </c>
       <c r="Q46" t="n">
@@ -4782,7 +4782,7 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>1262</t>
+          <t>1263</t>
         </is>
       </c>
       <c r="Q47" t="n">
@@ -4987,12 +4987,12 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>2oV52czXD7zAOL8XOUSL78, 1d_UGp1UD2pfCq6QCu1odj, 1DjBk084n8gfRcElXcnhlR, 1vDbowLhr7nx5SdmnF8FXc</t>
+          <t>1vDbowLhr7nx5SdmnF8FXc, 2oV52czXD7zAOL8XOUSL78, 1d_UGp1UD2pfCq6QCu1odj, 1DjBk084n8gfRcElXcnhlR</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>1271, 1273, 1274, 1275</t>
+          <t>1271, 1272, 1275, 1276</t>
         </is>
       </c>
       <c r="Q49" t="n">
@@ -5097,7 +5097,7 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>1263</t>
+          <t>1264</t>
         </is>
       </c>
       <c r="Q50" t="n">
@@ -5277,12 +5277,12 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>UG2, OG1</t>
+          <t>OG1, UG2</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>-8.2, 2.998</t>
+          <t>2.998, -8.2</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -5302,12 +5302,12 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>1OOeb7pNP5YhVqjcacSVQj, 1FDFHpwUH4NB1tapjSpmKb</t>
+          <t>1FDFHpwUH4NB1tapjSpmKb, 1OOeb7pNP5YhVqjcacSVQj</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>1277, 1278</t>
+          <t>1273, 1278</t>
         </is>
       </c>
       <c r="Q52" t="n">
@@ -5412,7 +5412,7 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>1276, 1282</t>
+          <t>1277, 1282</t>
         </is>
       </c>
       <c r="Q53" t="n">

--- a/merged_df.xlsx
+++ b/merged_df.xlsx
@@ -546,12 +546,12 @@
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>__pivot_7.939_actual</t>
+          <t>__pivot_7.94_actual</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>__pivot_11.947_actual</t>
+          <t>__pivot_11.948_actual</t>
         </is>
       </c>
     </row>
@@ -591,12 +591,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>OG3, UG2, UG1, OG2</t>
+          <t>UG2, UG1, OG2, OG3</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>11.947, -8.2, -3.78, 7.939</t>
+          <t>-8.2, -3.78, 7.94, 11.948</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -616,12 +616,12 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>2Ru4iRmYDDDfo5eLHGZ8RE, 0emPRSOwnDOOTgYleM3B_A, 2g6H0ojnvDdueYpZ_5Zux8, 1rOBySJhH5b9YWwDU_guK1</t>
+          <t>24xm6C08LB6PmPlweCGB8I, 0zR70dM_L5hgHRsQfW3Yo7, 1jaqyoTjT5Bhtkj1U9RyUu, 3yI4yvxYX9aBv$Jk3GB$dy</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>1219, 1227, 1228, 1229</t>
+          <t>1202, 1203, 1204, 1205</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -686,12 +686,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>EG, OG1, OG2, OG3, UG2, UG1</t>
+          <t>OG1, OG2, OG3, UG2, UG1, EG</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.0, 2.998, 7.939, 11.947, -8.2, -3.78</t>
+          <t>2.998, 7.94, 11.948, -8.2, -3.78, 0.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
@@ -707,12 +707,12 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>1R$FLavrj8G9Rxnz3lVckG, 0CIMZOOqj8GukY8gSKgU97, 18j2PWjBz3nhKzSkJrvM7d, 0wtQ7wfjD5FPd24jrI75yq, 13LOp07jD0lfjp1Ds2xiaX, 3BN76u7jD8SONfck_e054E</t>
+          <t>3Hh_lnoOjFseiPP$fBJdTk, 2P3Mbts9P06BZqiOxGDRsK, 39ETwZKMDAou$vKVot7pYG, 0WugxlnUz8xx2oGJ_ePbye, 1TuiyJHazFPP354k0XGOop, 049y1zqcb029syIWXEZkws</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>1215, 1216, 1217, 1218, 1223, 1224</t>
+          <t>1191, 1192, 1193, 1197, 1198, 1199</t>
         </is>
       </c>
       <c r="Q3" t="n">
@@ -806,12 +806,12 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>3Q30KcAwrFjgFId43DWY8P, 34G_SBUtD7Bx_aSDXbyBOH, 11GLlly7bCgPkVa3553rnS</t>
+          <t>0flQ6A_KT1au1P6tc3jqMc, 2F6s1tVBjDqQjhbB3E6WYb, 1ob0Dr3Tb3me5ixnzVhldr</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>1220, 1221, 1222</t>
+          <t>1194, 1195, 1196</t>
         </is>
       </c>
       <c r="Q4" t="n">
@@ -823,13 +823,13 @@
         </is>
       </c>
       <c r="S4" t="n">
-        <v>97.87437599999998</v>
+        <v>101.688451</v>
       </c>
       <c r="T4" t="n">
-        <v>39.08309449999999</v>
+        <v>42.893664</v>
       </c>
       <c r="U4" t="n">
-        <v>58.7912815</v>
+        <v>58.794787</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -905,12 +905,12 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>0jRMZ$SnH9ouX0ZQEwstxo, 1830E3dHD5f9qhMIKx9HB6, 14zTAK7eDFxu25AGckILdY, 3_49$ldkHAGOZei44e_8FY</t>
+          <t>3lSeJHANz4JwuuWWVWxbUH, 1s_RuZ0k90YAlXWhJ4lnX8, 3W2HgVPjj8sgJOb9kc$BUn, 3W8P9$rMX2_fA9sfb6fwqp</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>1225, 1226, 1234, 1235</t>
+          <t>1200, 1201, 1209, 1210</t>
         </is>
       </c>
       <c r="Q5" t="n">
@@ -922,13 +922,13 @@
         </is>
       </c>
       <c r="S5" t="n">
-        <v>62.2703145</v>
+        <v>61.5559585</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>54.69261700000001</v>
+        <v>53.978261</v>
       </c>
       <c r="V5" t="n">
         <v>7.5776975</v>
@@ -1057,12 +1057,12 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>2VcirkfBf6ahuppLqfjuCo</t>
+          <t>2pH4Wqvuf1bu8FEuNmVz7e</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>1254</t>
+          <t>1229</t>
         </is>
       </c>
       <c r="Q7" t="n">
@@ -1162,12 +1162,12 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>3WAjbS9Tz63fT8SRxhsEgW</t>
+          <t>2jZ_u9g6bC0gnFdRULl6Ao</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>1257</t>
+          <t>1233</t>
         </is>
       </c>
       <c r="Q8" t="n">
@@ -1261,12 +1261,12 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>3OwC$bqnH8HPMox51VeeVy</t>
+          <t>0wQhe8bif1LOoZtbl2gXny</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>1248</t>
+          <t>1223</t>
         </is>
       </c>
       <c r="Q9" t="n">
@@ -1340,7 +1340,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0.0, 11.947</t>
+          <t>0.0, 11.948</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1360,12 +1360,12 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>2smUqi2i10zRE_diOVjJhu, 2VPJztHKzE5eU2jmaJhVnb, 360G1aSpvFCuurfPO7oVVK, 2gK95MKEPE$O83dwER37Qp, 0WtOOP9cn9MBUnf0AHUQfJ, 2u0jNhx4PBahQiA_Mn0fAT, 1XvgrEk2L7Sf0_v9d5iT66, 02z0dETOLCdvSjB6spGLDD, 2dWGfk8A5FP9hGnKCxZb2t, 3Dk2HhiCr35RYXuSaVOvs6, 3AGSwy4Cv9YOBE5MpdNLQt, 0E4QXUam15QfaVaTAymHn2</t>
+          <t>0HX_qt1yzF3xKWplASPhYe, 2qXFUIy2T3SBxq9lBM4xHo, 2RrGEvz4H6O8oYwW_ERzQ6, 1AENlAVbf0FPNqAceD_OOg, 0eDs_7T5r34RBessIb8ALy, 2KTKdUnXz3EAT3eZQsBIVW, 1dm6hXA1TAHxySfbOH_SuE, 3Ko5GwjxPFa8wWHDHgsYet, 0bj3cexLz16A$8LPJ5vRgB, 2CKlKmb3L8if01dRSHZkQk, 3VSDX0a6j5R9Sc3ExLWrsf, 1DAsWzcd53mxYOR7lJYiHX</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>1236, 1237, 1238, 1239, 1241, 1242, 1243, 1244, 1245, 1249, 1250, 1251</t>
+          <t>1211, 1212, 1213, 1214, 1217, 1218, 1219, 1220, 1221, 1224, 1225, 1226</t>
         </is>
       </c>
       <c r="Q10" t="n">
@@ -1377,7 +1377,7 @@
         </is>
       </c>
       <c r="S10" t="n">
-        <v>784.1024640000001</v>
+        <v>801.9748285000001</v>
       </c>
       <c r="T10" t="n">
         <v>0</v>
@@ -1386,7 +1386,7 @@
         <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>693.2650895</v>
+        <v>693.3113715</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
@@ -1395,7 +1395,7 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>90.8373745</v>
+        <v>108.663457</v>
       </c>
     </row>
     <row r="11">
@@ -1488,7 +1488,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>11.947, 0.0</t>
+          <t>11.948, 0.0</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1508,12 +1508,12 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>2MZESDDfb379fB261rIbnR, 2VPSmwn8f80wlwsZLQwj7f, 3vBeHUwhfB5OcVQruWBfzN</t>
+          <t>2jDi0spfj5xugCuK32MU8B, 1JP2teRZzAKhVlWoAk44Gi, 0cuCI57f5FDx6c5xjTH_wt</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>1252, 1253, 1259</t>
+          <t>1227, 1228, 1235</t>
         </is>
       </c>
       <c r="Q12" t="n">
@@ -1525,7 +1525,7 @@
         </is>
       </c>
       <c r="S12" t="n">
-        <v>880.1147865</v>
+        <v>878.8663225</v>
       </c>
       <c r="T12" t="n">
         <v>0</v>
@@ -1534,7 +1534,7 @@
         <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>627.669683</v>
+        <v>627.6705645</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
@@ -1543,7 +1543,7 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>252.4451035</v>
+        <v>251.195758</v>
       </c>
     </row>
     <row r="13">
@@ -1611,12 +1611,12 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>3dUr5q39zEXBCsj4PLV405</t>
+          <t>3sBsqaQPb0euZE5Csd1V40</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>1256</t>
+          <t>1232</t>
         </is>
       </c>
       <c r="Q13" t="n">
@@ -1628,7 +1628,7 @@
         </is>
       </c>
       <c r="S13" t="n">
-        <v>73.566976</v>
+        <v>73.5662785</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
         <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>73.566976</v>
+        <v>73.5662785</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
@@ -1716,12 +1716,12 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>2F9RWBhUfEZ8$cJ_kTeVpx</t>
+          <t>0owNcgsrLCORAeZymoLxMZ</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>1258</t>
+          <t>1234</t>
         </is>
       </c>
       <c r="Q14" t="n">
@@ -1733,7 +1733,7 @@
         </is>
       </c>
       <c r="S14" t="n">
-        <v>295.86007</v>
+        <v>295.8120275</v>
       </c>
       <c r="T14" t="n">
         <v>0</v>
@@ -1742,7 +1742,7 @@
         <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>295.86007</v>
+        <v>295.8120275</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
@@ -1821,12 +1821,12 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>07p_i19HfFMxUYszLXHx0R</t>
+          <t>1y6$NkJCn2eRH9vQ05Vfth</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>1255</t>
+          <t>1230</t>
         </is>
       </c>
       <c r="Q15" t="n">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>3vSADXkCf9CehgpLlu0Bds, 2vZ$D3URf34vJnBMMHx9xX, 1D6v$lAcHDiAsIdGYCYrg4, 14Y66SGP5Fm8iYaOLsp2V8, 0XbzWrb4P70RH_r69FZvNC</t>
+          <t>367VhQ1U19B8v9mWQKmOzz, 2Hxz6DXsT92vehhFG6_ShJ, 38tAZDumv6$hnRXN0FwtYj, 2vghzoGT51TxNQvOAAv0j4, 2rIGmJBcz82eOKIU2HIoRF</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>1230, 1231, 1232, 1233, 1240</t>
+          <t>1206, 1207, 1208, 1215, 1216</t>
         </is>
       </c>
       <c r="Q16" t="n">
@@ -1937,7 +1937,7 @@
         </is>
       </c>
       <c r="S16" t="n">
-        <v>389.091511</v>
+        <v>389.1074575</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
@@ -1946,7 +1946,7 @@
         <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>389.091511</v>
+        <v>389.1074575</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
@@ -2021,12 +2021,12 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>1MqvEZmU539xzlBdmFG0Gt</t>
+          <t>0a48Ih65rFx8QfDnXMMhEl</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>1246</t>
+          <t>1231</t>
         </is>
       </c>
       <c r="Q17" t="n">
@@ -2122,12 +2122,12 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>3eJReeN3j08hoB6uk90Meh</t>
+          <t>3Zzx4L78nBqBHz3ZA4ivSQ</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>1247</t>
+          <t>1222</t>
         </is>
       </c>
       <c r="Q18" t="n">
@@ -2227,12 +2227,12 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>2jn0CO4WT6agpI_e3theVz</t>
+          <t>30_jhjUID1lOEnoZkbwPlR</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>1305</t>
+          <t>1281</t>
         </is>
       </c>
       <c r="Q19" t="n">
@@ -2332,12 +2332,12 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>0R6CzIVUf9Xg$xY9ZGMPOI</t>
+          <t>3v_If9$uz3fwzdtVKMHQ8o</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>1306</t>
+          <t>1282</t>
         </is>
       </c>
       <c r="Q20" t="n">
@@ -2417,7 +2417,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>7.939</t>
+          <t>7.94</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2437,12 +2437,12 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0mgHCA5Bj2q8PGPshAJwdu</t>
+          <t>2EdAa2vnvDwv$K313aI9nH</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>1289</t>
+          <t>1265</t>
         </is>
       </c>
       <c r="Q21" t="n">
@@ -2542,12 +2542,12 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>2q$FhMpurDpQLxyHcG7QMH</t>
+          <t>0snplPWT179OZgXqJkFdam</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>1292</t>
+          <t>1268</t>
         </is>
       </c>
       <c r="Q22" t="n">
@@ -2647,12 +2647,12 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>0lrhQ1hBL3UB9wu$bziAIW</t>
+          <t>1PFX2sV$1EtwB4cgbdYiiR</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>1294</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="Q23" t="n">
@@ -2752,12 +2752,12 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>15q5B8t2H1jOLW$YLJTSCd</t>
+          <t>3QuKuIVNvEDebBjhENRHdp</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>1293</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="Q24" t="n">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>1PXOCrKLD2ohK81bqcw5L8</t>
+          <t>1nHVq1BLj3N83VoxI$QAiV</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>1285</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="Q25" t="n">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>37pvr1fmPFoPR8VqDaFSaH</t>
+          <t>1xAkayK$92b8rEYvsI7ddA</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>1291</t>
+          <t>1267</t>
         </is>
       </c>
       <c r="Q26" t="n">
@@ -3120,12 +3120,12 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>0x9I5spTf0W8z7GhPCk1ky</t>
+          <t>3tE0xz5ivFbule77FUWYT7</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>1300</t>
+          <t>1276</t>
         </is>
       </c>
       <c r="Q28" t="n">
@@ -3137,7 +3137,7 @@
         </is>
       </c>
       <c r="S28" t="n">
-        <v>123.877062</v>
+        <v>123.8381265</v>
       </c>
       <c r="T28" t="n">
         <v>0</v>
@@ -3146,7 +3146,7 @@
         <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>123.877062</v>
+        <v>123.8381265</v>
       </c>
       <c r="W28" t="n">
         <v>0</v>
@@ -3225,12 +3225,12 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>2VOStX3MjEzAywBgrc2Ymz</t>
+          <t>2b761ZbMf7OQyYTjBYwlqS</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>1296</t>
+          <t>1272</t>
         </is>
       </c>
       <c r="Q29" t="n">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>1K1FlaQx1EExBCUKfCbQFS</t>
+          <t>2TkX3v9lLDHfNhAwV_173q</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>1271</t>
         </is>
       </c>
       <c r="Q30" t="n">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>1R9Imo_5167B$XHbYy7aZ6</t>
+          <t>0bebBo2BjBix6YQ7lpTjg5</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>1262</t>
+          <t>1238</t>
         </is>
       </c>
       <c r="Q34" t="n">
@@ -3699,12 +3699,12 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>2v3d7GGqDEd8IyrTdRXWWY, 2_kl8xFAvE_Oi0Djmy1jeA</t>
+          <t>3P24pHOeX7huTaoUa46vgT, 0OAGNaNgv3wwzf3ckQ_KTm</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>1265, 1266</t>
+          <t>1241, 1242</t>
         </is>
       </c>
       <c r="Q35" t="n">
@@ -3804,12 +3804,12 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>3LuW9jHbHBBAyJit_$Yn3$</t>
+          <t>3EFA13Ox1F58pYx6_i5NyU</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>1260</t>
+          <t>1236</t>
         </is>
       </c>
       <c r="Q36" t="n">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>0ZrdVUR4b0zxBrw6VrPmpy</t>
+          <t>0VzQ2RIZnBkuyXmMpvbN9_</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>1261</t>
+          <t>1237</t>
         </is>
       </c>
       <c r="Q37" t="n">
@@ -4015,7 +4015,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>-8.2, -3.78, 0.0, 2.998, 7.939, 11.947</t>
+          <t>-8.2, -3.78, 0.0, 2.998, 7.94, 11.948</t>
         </is>
       </c>
       <c r="L39" t="inlineStr"/>
@@ -4027,12 +4027,12 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>220mi7GG59YuA9V0nhWv8f, 1CV6oaRyn1HQP8tN4myNln, 2JYUQcEU93zwiGeMtni83Z, 2O9cNxLZXB48ei75HpXuVM, 2E_TZJZ7r4DgKH0p0YQJl8, 1AmWYBKrzAYQ$BPe2iH8In</t>
+          <t>11rtg$OHHCQgjPenPfbWHc, 1IKxMLTg96xBLZwOLJkOep, 2lJbeNWPr69PR6Bv8eHLx5, 0sM00mZHr6DOEYTFqh$IrG, 0rjMKvNtzAnefNaYJ97j52, 0qFk07a55D6POPpcM5bCmf</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>1309, 1311, 1317, 1324, 1329, 1333</t>
+          <t>1285, 1287, 1293, 1300, 1305, 1309</t>
         </is>
       </c>
       <c r="Q39" t="n">
@@ -4044,16 +4044,16 @@
         </is>
       </c>
       <c r="S39" t="n">
-        <v>3885.43503</v>
+        <v>3885.5616805</v>
       </c>
       <c r="T39" t="n">
-        <v>946.7568455000001</v>
+        <v>946.7966155</v>
       </c>
       <c r="U39" t="n">
-        <v>944.3010395</v>
+        <v>944.3288025000001</v>
       </c>
       <c r="V39" t="n">
-        <v>635.4141235</v>
+        <v>635.473241</v>
       </c>
       <c r="W39" t="n">
         <v>607.3553475</v>
@@ -4082,7 +4082,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>-8.2, -3.78, 0.0, 2.998, 7.939, 11.947</t>
+          <t>-8.2, -3.78, 0.0, 2.998, 7.94, 11.948</t>
         </is>
       </c>
       <c r="L40" t="inlineStr"/>
@@ -4094,12 +4094,12 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>2h61zMFo5AJAPRusVng_Xn, 1ocReKPMH6yQHek4DHBHWe, 1WVo1W$JrFBwJk1Ud33P2_, 2tu7qWjqT2KwS8C7vq8SbN, 2rXFWc8jX9X9uAiF4mg4_c, 1xVbGem8z8Yw7KMlDD7tyl, 29mRuo3Gj2kAoruOaOpQPk, 2UYbzXfWX4jeekEZZounLu, 2iqV3awXnFaPEu0T7HAtp4, 2HDdALzov8sOiati08LIYR, 191C_eUqLBjwUYQYjuyzbJ</t>
+          <t>2g7lHgM9fCfeWFLbqCROTN, 2TjpIVE3fEjf2yeWwF5tbt, 37U7QqRiD3K8YpI0EDvqEG, 3Phqv9RFv0aPLT5D_Im9QT, 2CTrriW1D4XfbevcRhL0D$, 3ue0$unPz0uux7AwL1STF3, 0BPV577Cv2qOXbm$_0BLlX, 0D49X8G8b21vMvV9fI6DYy, 3QbhoocVL16heqVtso3nIe, 1vS9xL68j7QRd7X5GTAvLE, 1MeUygKbr5gwqhdLnI1$fr</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>1307, 1308, 1310, 1314, 1315, 1316, 1321, 1322, 1323, 1328, 1332</t>
+          <t>1283, 1284, 1286, 1290, 1291, 1292, 1297, 1298, 1299, 1304, 1308</t>
         </is>
       </c>
       <c r="Q40" t="n">
@@ -4111,16 +4111,16 @@
         </is>
       </c>
       <c r="S40" t="n">
-        <v>5484.661963</v>
+        <v>5484.879056999999</v>
       </c>
       <c r="T40" t="n">
-        <v>1893.5052305</v>
+        <v>1893.5763265</v>
       </c>
       <c r="U40" t="n">
-        <v>944.3010395</v>
+        <v>944.3288025000001</v>
       </c>
       <c r="V40" t="n">
-        <v>1280.054072</v>
+        <v>1280.172307</v>
       </c>
       <c r="W40" t="n">
         <v>615.1939470000001</v>
@@ -4252,12 +4252,12 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>2rnYpcA2j5ORd2uupGEvG0</t>
+          <t>1elxkk8h12l8VI66SES48s</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>1281</t>
+          <t>1256</t>
         </is>
       </c>
       <c r="Q42" t="n">
@@ -4357,12 +4357,12 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>21ftMaN2H3x9V_1Iuv7_Lz</t>
+          <t>2jQqxIN7D0G9XrN3psKCHB</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t>1255</t>
         </is>
       </c>
       <c r="Q43" t="n">
@@ -4462,12 +4462,12 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>0kB0A2S5z5auQg3$i3qAjO</t>
+          <t>0SfLsfaY1DQQexHNkqpPq8</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>1279</t>
+          <t>1254</t>
         </is>
       </c>
       <c r="Q44" t="n">
@@ -4479,10 +4479,10 @@
         </is>
       </c>
       <c r="S44" t="n">
-        <v>24.194584</v>
+        <v>24.251362</v>
       </c>
       <c r="T44" t="n">
-        <v>24.194584</v>
+        <v>24.251362</v>
       </c>
       <c r="U44" t="n">
         <v>0</v>
@@ -4547,7 +4547,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>-3.78, 7.939</t>
+          <t>-3.78, 7.94</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -4567,12 +4567,12 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>3fS1w73ELCBRUIqHWvP3$z, 2FQ8B6_JP08wqgDmUUSwZn</t>
+          <t>25qvKAslv4su4AGnfPnQAy, 0$R0qHln98kepMxkmwzDXO</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>1283, 1284</t>
+          <t>1259, 1260</t>
         </is>
       </c>
       <c r="Q45" t="n">
@@ -4584,13 +4584,13 @@
         </is>
       </c>
       <c r="S45" t="n">
-        <v>7.9612265</v>
+        <v>8.0182985</v>
       </c>
       <c r="T45" t="n">
         <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>3.582502</v>
+        <v>3.639574</v>
       </c>
       <c r="V45" t="n">
         <v>0</v>
@@ -4672,12 +4672,12 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>0qoMVDV8fAzBp8ww__y4Tz</t>
+          <t>1KAZImcajE19VMZ2urkS9A</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>1274</t>
+          <t>1249</t>
         </is>
       </c>
       <c r="Q46" t="n">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>0teRCO0lj5OQYpPkvQztRq</t>
+          <t>0p4XPibzXDmfYuHdDNQKoi</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>1263</t>
+          <t>1239</t>
         </is>
       </c>
       <c r="Q47" t="n">
@@ -4794,7 +4794,7 @@
         </is>
       </c>
       <c r="S47" t="n">
-        <v>34.123994</v>
+        <v>34.1596555</v>
       </c>
       <c r="T47" t="n">
         <v>0</v>
@@ -4803,7 +4803,7 @@
         <v>0</v>
       </c>
       <c r="V47" t="n">
-        <v>34.123994</v>
+        <v>34.1596555</v>
       </c>
       <c r="W47" t="n">
         <v>0</v>
@@ -4882,12 +4882,12 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>1F3Fkq$vj7GQErmS_ow7lc, 1acftYr2jDufGYUUZLoAmB</t>
+          <t>2DRzef4hn3IgIiLgkhkHE9, 2EaietiEbAIPhvSO2Cvy$b</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>1269, 1270</t>
+          <t>1245, 1246</t>
         </is>
       </c>
       <c r="Q48" t="n">
@@ -4987,12 +4987,12 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>1vDbowLhr7nx5SdmnF8FXc, 2oV52czXD7zAOL8XOUSL78, 1d_UGp1UD2pfCq6QCu1odj, 1DjBk084n8gfRcElXcnhlR</t>
+          <t>2_ozTiGP19wxfIiizV$YDP, 1hrw6SBSX5_xz0kjcf$lQq, 3MbScePwXCG951Z0r4L0yN, 3YWB1QD45A0ffgE_grSlSK</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>1271, 1272, 1275, 1276</t>
+          <t>1247, 1248, 1250, 1251</t>
         </is>
       </c>
       <c r="Q49" t="n">
@@ -5004,13 +5004,13 @@
         </is>
       </c>
       <c r="S49" t="n">
-        <v>168.6224655</v>
+        <v>169.608867</v>
       </c>
       <c r="T49" t="n">
         <v>0</v>
       </c>
       <c r="U49" t="n">
-        <v>168.6224655</v>
+        <v>169.608867</v>
       </c>
       <c r="V49" t="n">
         <v>0</v>
@@ -5092,12 +5092,12 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>3O5OUxbKP5_PZAUUrtfSgZ</t>
+          <t>3vzyyhvhTCCxHI3Ujz_Pdk</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>1264</t>
+          <t>1240</t>
         </is>
       </c>
       <c r="Q50" t="n">
@@ -5109,7 +5109,7 @@
         </is>
       </c>
       <c r="S50" t="n">
-        <v>13.396027</v>
+        <v>13.502395</v>
       </c>
       <c r="T50" t="n">
         <v>0</v>
@@ -5118,7 +5118,7 @@
         <v>0</v>
       </c>
       <c r="V50" t="n">
-        <v>13.396027</v>
+        <v>13.502395</v>
       </c>
       <c r="W50" t="n">
         <v>0</v>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>1MPw1r9hv6$h6AZYdCPJK4</t>
+          <t>2lK1NiaZXE9g_b2KyM_qzf</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>1268</t>
+          <t>1244</t>
         </is>
       </c>
       <c r="Q51" t="n">
@@ -5277,12 +5277,12 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>OG1, UG2</t>
+          <t>UG2, OG1</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2.998, -8.2</t>
+          <t>-8.2, 2.998</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -5302,12 +5302,12 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>1FDFHpwUH4NB1tapjSpmKb, 1OOeb7pNP5YhVqjcacSVQj</t>
+          <t>0fphzOn3z3ffzYnIZDfkRZ, 3$MWY95kL37xnSaojxj3cW</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>1273, 1278</t>
+          <t>1252, 1253</t>
         </is>
       </c>
       <c r="Q52" t="n">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>OG1, UG2</t>
+          <t>UG2, OG1</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2.998, -8.2</t>
+          <t>-8.2, 2.998</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -5407,12 +5407,12 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>2qwEpCHpPBQhWqR0aH8a_c, 3fqw08GKT8VB$WT6lvspWB</t>
+          <t>1mK10My2H1Jf6TH2FFyNJl, 0v8vKsFUHEhuGCI94TqyuL</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>1277, 1282</t>
+          <t>1257, 1258</t>
         </is>
       </c>
       <c r="Q53" t="n">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>-3.78, 7.939</t>
+          <t>-3.78, 7.94</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -5616,12 +5616,12 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>2goFLwB6DCTwDTgbAWEEIH, 0d65XwDRr8KPZICzeqHSW5</t>
+          <t>2gsiWFr2TB1AHTbv7ojX6m, 3jgApaggT6VOj2drGLqhV$</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>1301, 1302</t>
+          <t>1277, 1278</t>
         </is>
       </c>
       <c r="Q56" t="n">
@@ -5701,7 +5701,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>-3.78, 7.939</t>
+          <t>-3.78, 7.94</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -5721,12 +5721,12 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>0WJ65NDaH54RWZcOZo2hFz, 0DQARhKmnCX83BGrsfeEgq</t>
+          <t>0L$CPopvL2ng78uaCkxmd2, 2R0Ko1_rT45gQWRWnSw8Rh</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>1303, 1304</t>
+          <t>1279, 1280</t>
         </is>
       </c>
       <c r="Q57" t="n">
@@ -5826,12 +5826,12 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>1wnl70Hcf4J91aH6kWoQ5w</t>
+          <t>2pxOd96v91mxlwof2bdwwu</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>1267</t>
+          <t>1243</t>
         </is>
       </c>
       <c r="Q58" t="n">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>11.947</t>
+          <t>11.948</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -5931,12 +5931,12 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>3542EqJCz3j9Eu7i7LwKQI</t>
+          <t>2RQb_YuIX0cupTG8njrqa5</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>1290</t>
+          <t>1266</t>
         </is>
       </c>
       <c r="Q59" t="n">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>1H1NJxt1P4dhBGOFdbv$N4</t>
+          <t>3V04x_Gn9CsOd3mf5kjSS7</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>1298</t>
+          <t>1274</t>
         </is>
       </c>
       <c r="Q60" t="n">
@@ -6121,7 +6121,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>11.947</t>
+          <t>11.948</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -6141,12 +6141,12 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>1xCUaRipzEBRjcRGOUa__w</t>
+          <t>0ydbChVXH5YeiOECwP0lP5</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>1299</t>
+          <t>1275</t>
         </is>
       </c>
       <c r="Q61" t="n">
@@ -6226,7 +6226,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>11.947</t>
+          <t>11.948</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -6246,12 +6246,12 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>3gQV9bpHv7NfVbjzlui7Lj</t>
+          <t>3865N6dr5D2QZmKnsV5UjA</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="Q62" t="n">
@@ -6331,7 +6331,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>11.947</t>
+          <t>11.948</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -6351,12 +6351,12 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>0x5OAt7GXB6Rq0gRG_tICL</t>
+          <t>2dCF9Z2NrCiPs79T_2XETx</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>1287</t>
+          <t>1263</t>
         </is>
       </c>
       <c r="Q63" t="n">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>1nbtU4bcH2MeFbv04K7ZN2</t>
+          <t>3th3YBjLPEbgeAFO8BnVLM</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>1297</t>
+          <t>1273</t>
         </is>
       </c>
       <c r="Q64" t="n">
@@ -6541,7 +6541,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>7.939</t>
+          <t>7.94</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -6561,12 +6561,12 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>0CmilJIZr6B8RyG4QW7HcZ</t>
+          <t>2V_TDJQGX5u9IXI55MWQFM</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>1288</t>
+          <t>1264</t>
         </is>
       </c>
       <c r="Q65" t="n">
@@ -6620,7 +6620,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>0.0, 2.998, 7.939, 11.947</t>
+          <t>0.0, 2.998, 7.94, 11.948</t>
         </is>
       </c>
       <c r="L66" t="inlineStr"/>
@@ -6632,12 +6632,12 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>1dO_bQkdz9nwDyTkTE7ib2, 1Bex$LLBz14RGCBVd_3SHQ, 0s4lbBN6v2wQ56baFu8aCK, 19fOi9h4H1XBR85Agg_fkE, 1YjQd29ADBdhHAaWT8IdQR, 2yWWAdHcT0Ee9Cxo9n9g3E</t>
+          <t>0XnoVHZ5b7YeZWNQ2bXPFm, 3aH$lMb654_u$4SW_WvFAN, 14l9pM3sL8xfYz1mvXCNWG, 0hYc3lmMH2T91sw96db3JM, 0pnXM2gsT77R5nDFj8mzSx, 3hhMFg80L1LfBHM_a3hr7A</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>1313, 1319, 1320, 1325, 1326, 1331</t>
+          <t>1289, 1295, 1296, 1301, 1302, 1307</t>
         </is>
       </c>
       <c r="Q66" t="n">
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="S66" t="n">
-        <v>164.6158945</v>
+        <v>166.5463805</v>
       </c>
       <c r="T66" t="n">
         <v>0</v>
@@ -6658,16 +6658,16 @@
         <v>0</v>
       </c>
       <c r="V66" t="n">
-        <v>16.361301</v>
+        <v>17.082447</v>
       </c>
       <c r="W66" t="n">
-        <v>50.5339195</v>
+        <v>51.266701</v>
       </c>
       <c r="X66" t="n">
-        <v>57.0922475</v>
+        <v>57.619245</v>
       </c>
       <c r="Y66" t="n">
-        <v>40.6284265</v>
+        <v>40.5779875</v>
       </c>
     </row>
     <row r="67">
@@ -6691,7 +6691,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>0.0, 2.998, 7.939, 11.947</t>
+          <t>0.0, 2.998, 7.94, 11.948</t>
         </is>
       </c>
       <c r="L67" t="inlineStr"/>
@@ -6703,12 +6703,12 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>3S19U$d1v2EAwMe1MFmPkg, 0cZezKqu94ovlQgVTxGUP9, 0Dg5sNnYTBWwyKrJUXkFTO, 3eXcdEMUX3XuwJXhU1bBiW</t>
+          <t>1CcwMqeXT8UesKx8nLd6OD, 1MQDEFDcX439MvQ3uigCM$, 2$k1ahqBDFJPjWMBdR8WtC, 3r8c5tGbPC_fDRkxzKA81G</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>1312, 1318, 1327, 1330</t>
+          <t>1288, 1294, 1303, 1306</t>
         </is>
       </c>
       <c r="Q67" t="n">
@@ -6720,7 +6720,7 @@
         </is>
       </c>
       <c r="S67" t="n">
-        <v>27.30605</v>
+        <v>41.80292</v>
       </c>
       <c r="T67" t="n">
         <v>0</v>
@@ -6729,16 +6729,16 @@
         <v>0</v>
       </c>
       <c r="V67" t="n">
-        <v>6.8265125</v>
+        <v>10.45073</v>
       </c>
       <c r="W67" t="n">
-        <v>6.8265125</v>
+        <v>10.45073</v>
       </c>
       <c r="X67" t="n">
-        <v>6.8265125</v>
+        <v>10.45073</v>
       </c>
       <c r="Y67" t="n">
-        <v>6.8265125</v>
+        <v>10.45073</v>
       </c>
     </row>
   </sheetData>

--- a/merged_df.xlsx
+++ b/merged_df.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y67"/>
+  <dimension ref="A1:Y65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -526,32 +526,32 @@
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>__pivot_-8.2_actual</t>
+          <t>__pivot_-9.25_actual</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>__pivot_-3.78_actual</t>
+          <t>__pivot_-6.4_actual</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
+          <t>__pivot_-3.6_actual</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
           <t>__pivot_0.0_actual</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>__pivot_2.998_actual</t>
-        </is>
-      </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>__pivot_7.94_actual</t>
+          <t>__pivot_3.65_actual</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>__pivot_11.948_actual</t>
+          <t>__pivot_7.65_actual</t>
         </is>
       </c>
     </row>
@@ -591,12 +591,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>UG2, UG1, OG2, OG3</t>
+          <t>1. Geschoss</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>-8.2, -3.78, 7.94, 11.948</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -616,16 +616,16 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>24xm6C08LB6PmPlweCGB8I, 0zR70dM_L5hgHRsQfW3Yo7, 1jaqyoTjT5Bhtkj1U9RyUu, 3yI4yvxYX9aBv$Jk3GB$dy</t>
+          <t>3R2xljncLFrwUcVRqrVWQB</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>1202, 1203, 1204, 1205</t>
+          <t>1220</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
@@ -633,13 +633,13 @@
         </is>
       </c>
       <c r="S2" t="n">
-        <v>56.0238215</v>
+        <v>40.81309</v>
       </c>
       <c r="T2" t="n">
-        <v>10.7493655</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>18.0784765</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -648,10 +648,10 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>13.6486625</v>
+        <v>40.81309</v>
       </c>
       <c r="Y2" t="n">
-        <v>13.547317</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -686,12 +686,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>OG1, OG2, OG3, UG2, UG1, EG</t>
+          <t>-3. Geschoss, -2. Geschoss, EG, 1. Geschoss, OG</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2.998, 7.94, 11.948, -8.2, -3.78, 0.0</t>
+          <t>-9.25, -6.4, 0.0, 3.65, 7.65</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
@@ -707,12 +707,12 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>3Hh_lnoOjFseiPP$fBJdTk, 2P3Mbts9P06BZqiOxGDRsK, 39ETwZKMDAou$vKVot7pYG, 0WugxlnUz8xx2oGJ_ePbye, 1TuiyJHazFPP354k0XGOop, 049y1zqcb029syIWXEZkws</t>
+          <t>0QGjRpssrCEf62jJYAXlKy, 2179hTJDz4qe$lLgQDGjs5, 2bfZjgao1Dv97JNyykkr_m, 0oLpxmuLrD3vpEnaHL8ZBj, 1qKOcF2ODCce7VLD9rsXEH, 2PljEqQLzB2ubXqkxHG$np</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>1191, 1192, 1193, 1197, 1198, 1199</t>
+          <t>1203, 1204, 1205, 1206, 1207, 1208</t>
         </is>
       </c>
       <c r="Q3" t="n">
@@ -724,25 +724,25 @@
         </is>
       </c>
       <c r="S3" t="n">
-        <v>41.376825</v>
+        <v>30.033636</v>
       </c>
       <c r="T3" t="n">
-        <v>2.3140405</v>
+        <v>15.671564</v>
       </c>
       <c r="U3" t="n">
-        <v>2.312567</v>
+        <v>6.229276</v>
       </c>
       <c r="V3" t="n">
-        <v>29.7644175</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>2.3140405</v>
+        <v>2.710932</v>
       </c>
       <c r="X3" t="n">
-        <v>2.3140405</v>
+        <v>2.710932</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.357719</v>
+        <v>2.710932</v>
       </c>
     </row>
     <row r="4">
@@ -781,12 +781,12 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>UG2, UG1</t>
+          <t>-3. Geschoss, -2. Geschoss, UG, EG, 1. Geschoss, OG</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>-8.2, -3.78</t>
+          <t>-9.25, -6.4, -3.6, 0.0, 3.65, 7.65</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -806,16 +806,16 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>0flQ6A_KT1au1P6tc3jqMc, 2F6s1tVBjDqQjhbB3E6WYb, 1ob0Dr3Tb3me5ixnzVhldr</t>
+          <t>0zMGxe1BH1TxrCrIVjVasx, 0r$EqdMpj3RfiqlR4uoawX, 3Iu9ARz1n06eCv$RLYK8mN, 1PBVp6jL50d9XpS2BSM7Q3, 3dOvSe5UX79wzz5B1UL_ow, 0xFnUORwv85B7hCDyxBIe3</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>1194, 1195, 1196</t>
+          <t>1209, 1210, 1211, 1212, 1213, 1214</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -823,25 +823,25 @@
         </is>
       </c>
       <c r="S4" t="n">
-        <v>101.688451</v>
+        <v>74.875981</v>
       </c>
       <c r="T4" t="n">
-        <v>42.893664</v>
+        <v>8.5472</v>
       </c>
       <c r="U4" t="n">
-        <v>58.794787</v>
+        <v>8.5472</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>8.5472</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>14.820174</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>14.820174</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>19.594033</v>
       </c>
     </row>
     <row r="5">
@@ -880,12 +880,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>EG, UG1</t>
+          <t>EG, 1. Geschoss, OG, -3. Geschoss, -2. Geschoss, UG</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.0, -3.78</t>
+          <t>0.0, 3.65, 7.65, -9.25, -6.4, -3.6</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -905,16 +905,16 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>3lSeJHANz4JwuuWWVWxbUH, 1s_RuZ0k90YAlXWhJ4lnX8, 3W2HgVPjj8sgJOb9kc$BUn, 3W8P9$rMX2_fA9sfb6fwqp</t>
+          <t>3bagB9kcv85vun_VdjVODa, 0at7qB32n7xwYKBY7SyXY4, 3_LTi1Z9TDWRmn1Acr_AH5, 01SSfasGf4gu$W_Yordu28, 2_slEYTbH0uwkjArsmzKBU, 31kIq08c57IhP5TEcyAIRZ, 0IHz2m9ov5YgNzsWm0g81F, 2rdVzlqnn3yOJdDWB7Lf3k, 3YxZGBMHn7qO_DYBivbzUS</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>1200, 1201, 1209, 1210</t>
+          <t>1215, 1216, 1217, 1218, 1219, 1222, 1223, 1224, 1225</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
@@ -922,25 +922,25 @@
         </is>
       </c>
       <c r="S5" t="n">
-        <v>61.5559585</v>
+        <v>199.928687</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>46.315696</v>
       </c>
       <c r="U5" t="n">
-        <v>53.978261</v>
+        <v>52.826958</v>
       </c>
       <c r="V5" t="n">
-        <v>7.5776975</v>
+        <v>41.415856</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>27.22131</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>19.352178</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>12.796689</v>
       </c>
     </row>
     <row r="6">
@@ -1025,75 +1025,23 @@
       <c r="H7" t="n">
         <v>390</v>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>ALL</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>EG</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>BUF</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>Aussenbereich</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>EXTERNAL</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>2pH4Wqvuf1bu8FEuNmVz7e</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>1229</t>
-        </is>
-      </c>
-      <c r="Q7" t="n">
-        <v>1</v>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>Aussenbereich_ALL</t>
-        </is>
-      </c>
-      <c r="S7" t="n">
-        <v>396.6236325</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" t="n">
-        <v>396.6236325</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0</v>
-      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1162,12 +1110,12 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>2jZ_u9g6bC0gnFdRULl6Ao</t>
+          <t>3nn4tnKqz1a9xEhA8QGB9a</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>1233</t>
+          <t>1235</t>
         </is>
       </c>
       <c r="Q8" t="n">
@@ -1179,7 +1127,7 @@
         </is>
       </c>
       <c r="S8" t="n">
-        <v>29.849794</v>
+        <v>17.459065</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -1188,10 +1136,10 @@
         <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>29.849794</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>17.459065</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1229,75 +1177,23 @@
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>AVF</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>EG</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>BUF</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>Aussenbereich</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>EXTERNAL</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>0wQhe8bif1LOoZtbl2gXny</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>1223</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>1</v>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>Aussenbereich_AVF</t>
-        </is>
-      </c>
-      <c r="S9" t="n">
-        <v>12.9937485</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" t="n">
-        <v>12.9937485</v>
-      </c>
-      <c r="W9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>0</v>
-      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1335,12 +1231,12 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>EG, OG3</t>
+          <t>OG, 1. Geschoss</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0.0, 11.948</t>
+          <t>7.65, 3.65</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1360,16 +1256,16 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>0HX_qt1yzF3xKWplASPhYe, 2qXFUIy2T3SBxq9lBM4xHo, 2RrGEvz4H6O8oYwW_ERzQ6, 1AENlAVbf0FPNqAceD_OOg, 0eDs_7T5r34RBessIb8ALy, 2KTKdUnXz3EAT3eZQsBIVW, 1dm6hXA1TAHxySfbOH_SuE, 3Ko5GwjxPFa8wWHDHgsYet, 0bj3cexLz16A$8LPJ5vRgB, 2CKlKmb3L8if01dRSHZkQk, 3VSDX0a6j5R9Sc3ExLWrsf, 1DAsWzcd53mxYOR7lJYiHX</t>
+          <t>2FfePHlQb1H8ONBzgx2KjG, 0Gz4j4MRX6XvLzeg45njs3, 3CxQ1gWQ51uhZIBxj8axdL</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>1211, 1212, 1213, 1214, 1217, 1218, 1219, 1220, 1221, 1224, 1225, 1226</t>
+          <t>1221, 1229, 1230</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
@@ -1377,7 +1273,7 @@
         </is>
       </c>
       <c r="S10" t="n">
-        <v>801.9748285000001</v>
+        <v>501.804965</v>
       </c>
       <c r="T10" t="n">
         <v>0</v>
@@ -1386,16 +1282,16 @@
         <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>693.3113715</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>234.720456</v>
       </c>
       <c r="Y10" t="n">
-        <v>108.663457</v>
+        <v>267.084509</v>
       </c>
     </row>
     <row r="11">
@@ -1483,12 +1379,12 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>OG3, EG</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>11.948, 0.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1508,16 +1404,16 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>2jDi0spfj5xugCuK32MU8B, 1JP2teRZzAKhVlWoAk44Gi, 0cuCI57f5FDx6c5xjTH_wt</t>
+          <t>3xQxX0PgLFyhEfNxq5ExSw</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>1227, 1228, 1235</t>
+          <t>1226</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R12" t="inlineStr">
         <is>
@@ -1525,7 +1421,7 @@
         </is>
       </c>
       <c r="S12" t="n">
-        <v>878.8663225</v>
+        <v>937.550941</v>
       </c>
       <c r="T12" t="n">
         <v>0</v>
@@ -1534,16 +1430,16 @@
         <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>627.6705645</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>937.550941</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>251.195758</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1611,12 +1507,12 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>3sBsqaQPb0euZE5Csd1V40</t>
+          <t>0PEqNgC89CshH_53Wkr3$b</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>1232</t>
+          <t>1234</t>
         </is>
       </c>
       <c r="Q13" t="n">
@@ -1628,7 +1524,7 @@
         </is>
       </c>
       <c r="S13" t="n">
-        <v>73.5662785</v>
+        <v>255.723749</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
@@ -1637,10 +1533,10 @@
         <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>73.5662785</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>255.723749</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
@@ -1684,75 +1580,23 @@
       <c r="H14" t="n">
         <v>300</v>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>PAK</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>EG</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>BUF</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>Aussenbereich</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>EXTERNAL</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>0owNcgsrLCORAeZymoLxMZ</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>1234</t>
-        </is>
-      </c>
-      <c r="Q14" t="n">
-        <v>1</v>
-      </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>Aussenbereich_PAK</t>
-        </is>
-      </c>
-      <c r="S14" t="n">
-        <v>295.8120275</v>
-      </c>
-      <c r="T14" t="n">
-        <v>0</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" t="n">
-        <v>295.8120275</v>
-      </c>
-      <c r="W14" t="n">
-        <v>0</v>
-      </c>
-      <c r="X14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>0</v>
-      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1789,75 +1633,23 @@
       <c r="H15" t="n">
         <v>12</v>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>PPA</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>EG</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>BUF</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>Aussenbereich</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>EXTERNAL</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>1y6$NkJCn2eRH9vQ05Vfth</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>1230</t>
-        </is>
-      </c>
-      <c r="Q15" t="n">
-        <v>1</v>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>Aussenbereich_PPA</t>
-        </is>
-      </c>
-      <c r="S15" t="n">
-        <v>17.289957</v>
-      </c>
-      <c r="T15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" t="n">
-        <v>17.289957</v>
-      </c>
-      <c r="W15" t="n">
-        <v>0</v>
-      </c>
-      <c r="X15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>0</v>
-      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1888,75 +1680,23 @@
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>UUF</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>EG</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>BUF</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>Aussenbereich</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>EXTERNAL</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>367VhQ1U19B8v9mWQKmOzz, 2Hxz6DXsT92vehhFG6_ShJ, 38tAZDumv6$hnRXN0FwtYj, 2vghzoGT51TxNQvOAAv0j4, 2rIGmJBcz82eOKIU2HIoRF</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>1206, 1207, 1208, 1215, 1216</t>
-        </is>
-      </c>
-      <c r="Q16" t="n">
-        <v>5</v>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>Aussenbereich_UUF</t>
-        </is>
-      </c>
-      <c r="S16" t="n">
-        <v>389.1074575</v>
-      </c>
-      <c r="T16" t="n">
-        <v>0</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" t="n">
-        <v>389.1074575</v>
-      </c>
-      <c r="W16" t="n">
-        <v>0</v>
-      </c>
-      <c r="X16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>0</v>
-      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2021,12 +1761,12 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>0a48Ih65rFx8QfDnXMMhEl</t>
+          <t>1jQMCRdaTCAxYCwHT9ZTYe</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>1231</t>
+          <t>1227</t>
         </is>
       </c>
       <c r="Q17" t="n">
@@ -2038,7 +1778,7 @@
         </is>
       </c>
       <c r="S17" t="n">
-        <v>5.20168</v>
+        <v>7.5</v>
       </c>
       <c r="T17" t="n">
         <v>0</v>
@@ -2047,10 +1787,10 @@
         <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>5.20168</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -2122,12 +1862,12 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>3Zzx4L78nBqBHz3ZA4ivSQ</t>
+          <t>3p8gJcXfrDbeARU6GGAIAQ</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>1222</t>
+          <t>1228</t>
         </is>
       </c>
       <c r="Q18" t="n">
@@ -2139,7 +1879,7 @@
         </is>
       </c>
       <c r="S18" t="n">
-        <v>18.206341</v>
+        <v>15.21</v>
       </c>
       <c r="T18" t="n">
         <v>0</v>
@@ -2148,10 +1888,10 @@
         <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>18.206341</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>15.21</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -2202,12 +1942,12 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>1. Geschoss</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2227,16 +1967,16 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>30_jhjUID1lOEnoZkbwPlR</t>
+          <t>25$VtZP153yhSX5bRPwPaU, 3xYlykRhjAeBm0JhwdmY7E</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>1281</t>
+          <t>1288, 1296</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R19" t="inlineStr">
         <is>
@@ -2244,7 +1984,7 @@
         </is>
       </c>
       <c r="S19" t="n">
-        <v>71.548801</v>
+        <v>76.96207899999999</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
@@ -2253,13 +1993,13 @@
         <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>71.548801</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>76.96207899999999</v>
       </c>
       <c r="Y19" t="n">
         <v>0</v>
@@ -2307,12 +2047,12 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>1. Geschoss</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2332,12 +2072,12 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>3v_If9$uz3fwzdtVKMHQ8o</t>
+          <t>2VjXtZBPn7$QycJJ85z80D</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>1282</t>
+          <t>1289</t>
         </is>
       </c>
       <c r="Q20" t="n">
@@ -2349,7 +2089,7 @@
         </is>
       </c>
       <c r="S20" t="n">
-        <v>53.9113785</v>
+        <v>69.02808</v>
       </c>
       <c r="T20" t="n">
         <v>0</v>
@@ -2358,13 +2098,13 @@
         <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>53.9113785</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>69.02808</v>
       </c>
       <c r="Y20" t="n">
         <v>0</v>
@@ -2412,12 +2152,12 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>OG2</t>
+          <t>1. Geschoss</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>7.94</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2437,7 +2177,7 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>2EdAa2vnvDwv$K313aI9nH</t>
+          <t>38MauQ3FTFVx5MNVVenPpY</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2454,7 +2194,7 @@
         </is>
       </c>
       <c r="S21" t="n">
-        <v>17.5731125</v>
+        <v>16.617348</v>
       </c>
       <c r="T21" t="n">
         <v>0</v>
@@ -2469,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>17.5731125</v>
+        <v>16.617348</v>
       </c>
       <c r="Y21" t="n">
         <v>0</v>
@@ -2542,7 +2282,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0snplPWT179OZgXqJkFdam</t>
+          <t>2uPY50Sib749o5WIuFGRpT</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2559,7 +2299,7 @@
         </is>
       </c>
       <c r="S22" t="n">
-        <v>64.21340600000001</v>
+        <v>42.49605</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
@@ -2568,10 +2308,10 @@
         <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>64.21340600000001</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>42.49605</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
@@ -2647,7 +2387,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>1PFX2sV$1EtwB4cgbdYiiR</t>
+          <t>3aRQdr1dX0NRYyWhsc5L_w</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2664,7 +2404,7 @@
         </is>
       </c>
       <c r="S23" t="n">
-        <v>6.9409425</v>
+        <v>6.174564</v>
       </c>
       <c r="T23" t="n">
         <v>0</v>
@@ -2673,10 +2413,10 @@
         <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>6.9409425</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>6.174564</v>
       </c>
       <c r="X23" t="n">
         <v>0</v>
@@ -2752,7 +2492,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>3QuKuIVNvEDebBjhENRHdp</t>
+          <t>3ZfLIBOpn5IObGi$psA5G_</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -2769,7 +2509,7 @@
         </is>
       </c>
       <c r="S24" t="n">
-        <v>4.44016</v>
+        <v>4.58035</v>
       </c>
       <c r="T24" t="n">
         <v>0</v>
@@ -2778,10 +2518,10 @@
         <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>4.44016</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>4.58035</v>
       </c>
       <c r="X24" t="n">
         <v>0</v>
@@ -2857,12 +2597,12 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>1nHVq1BLj3N83VoxI$QAiV</t>
+          <t>0IlZmRlo50QOL9BoyqRs1A</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>1261</t>
+          <t>1271</t>
         </is>
       </c>
       <c r="Q25" t="n">
@@ -2874,7 +2614,7 @@
         </is>
       </c>
       <c r="S25" t="n">
-        <v>7.189814</v>
+        <v>5.26419</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
@@ -2883,10 +2623,10 @@
         <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>7.189814</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>5.26419</v>
       </c>
       <c r="X25" t="n">
         <v>0</v>
@@ -2962,12 +2702,12 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>1xAkayK$92b8rEYvsI7ddA</t>
+          <t>3unooK3Gb53wP5rjxO9DU1</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>1267</t>
+          <t>1277</t>
         </is>
       </c>
       <c r="Q26" t="n">
@@ -2979,7 +2719,7 @@
         </is>
       </c>
       <c r="S26" t="n">
-        <v>72.32068099999999</v>
+        <v>73.128405</v>
       </c>
       <c r="T26" t="n">
         <v>0</v>
@@ -2988,10 +2728,10 @@
         <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>72.32068099999999</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>73.128405</v>
       </c>
       <c r="X26" t="n">
         <v>0</v>
@@ -3095,12 +2835,12 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>1. Geschoss, EG</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.65, 0.0</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -3120,16 +2860,16 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>3tE0xz5ivFbule77FUWYT7</t>
+          <t>1Dv0nT0wvAc96JfBjMbO63, 1wXQLSsdzAo8tX0e9rPv_0, 1dy$wbFnHA$AUPXvByysgw, 2TMrDToPv0s8QlXMbvZv0x</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>1276</t>
+          <t>1283, 1290, 1291, 1292</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R28" t="inlineStr">
         <is>
@@ -3137,7 +2877,7 @@
         </is>
       </c>
       <c r="S28" t="n">
-        <v>123.8381265</v>
+        <v>107.915895</v>
       </c>
       <c r="T28" t="n">
         <v>0</v>
@@ -3146,13 +2886,13 @@
         <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>123.8381265</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>53.954019</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>53.961876</v>
       </c>
       <c r="Y28" t="n">
         <v>0</v>
@@ -3200,12 +2940,12 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>UG1</t>
+          <t>1. Geschoss</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -3225,12 +2965,12 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>2b761ZbMf7OQyYTjBYwlqS</t>
+          <t>29dhkfqqj1VOZgFMDYpCg3</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>1272</t>
+          <t>1281</t>
         </is>
       </c>
       <c r="Q29" t="n">
@@ -3242,13 +2982,13 @@
         </is>
       </c>
       <c r="S29" t="n">
-        <v>2.8944635</v>
+        <v>6.189876</v>
       </c>
       <c r="T29" t="n">
         <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>2.8944635</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
         <v>0</v>
@@ -3257,7 +2997,7 @@
         <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>6.189876</v>
       </c>
       <c r="Y29" t="n">
         <v>0</v>
@@ -3305,12 +3045,12 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>UG1</t>
+          <t>1. Geschoss</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -3330,12 +3070,12 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>2TkX3v9lLDHfNhAwV_173q</t>
+          <t>1qu0RAu_5Bi9v6wMjwq2hO</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>1271</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="Q30" t="n">
@@ -3347,13 +3087,13 @@
         </is>
       </c>
       <c r="S30" t="n">
-        <v>2.719245</v>
+        <v>6.189876</v>
       </c>
       <c r="T30" t="n">
         <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>2.719245</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
         <v>0</v>
@@ -3362,7 +3102,7 @@
         <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>6.189876</v>
       </c>
       <c r="Y30" t="n">
         <v>0</v>
@@ -3509,23 +3249,75 @@
       <c r="H33" t="n">
         <v>3</v>
       </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr"/>
-      <c r="R33" t="inlineStr"/>
-      <c r="S33" t="inlineStr"/>
-      <c r="T33" t="inlineStr"/>
-      <c r="U33" t="inlineStr"/>
-      <c r="V33" t="inlineStr"/>
-      <c r="W33" t="inlineStr"/>
-      <c r="X33" t="inlineStr"/>
-      <c r="Y33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>WCR</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>EG, 1. Geschoss</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>0.0, 3.65</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>NNF</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>Betreuung</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>INTERNAL</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>0binosZSD2TRmMGGbm$Riz, 0wQ3tggsr80BEk7K$paN07</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>1278, 1279</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>2</v>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>Betreuung_WCR</t>
+        </is>
+      </c>
+      <c r="S33" t="n">
+        <v>5.866476</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" t="n">
+        <v>0</v>
+      </c>
+      <c r="W33" t="n">
+        <v>2.933238</v>
+      </c>
+      <c r="X33" t="n">
+        <v>2.933238</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3569,12 +3361,12 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>UG1</t>
+          <t>UG</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-3.6</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -3594,12 +3386,12 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0bebBo2BjBix6YQ7lpTjg5</t>
+          <t>1zlPnmNiz1DPGCdwjs_BAh</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>1238</t>
+          <t>1233</t>
         </is>
       </c>
       <c r="Q34" t="n">
@@ -3611,16 +3403,16 @@
         </is>
       </c>
       <c r="S34" t="n">
-        <v>25.280915</v>
+        <v>6.229276</v>
       </c>
       <c r="T34" t="n">
         <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>25.280915</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>6.229276</v>
       </c>
       <c r="W34" t="n">
         <v>0</v>
@@ -3667,75 +3459,23 @@
       <c r="H35" t="n">
         <v>90</v>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>HTR_K</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>UG2, UG1</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>-8.2, -3.78</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>FF</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>Funktionsfläche</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>INTERNAL</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>3P24pHOeX7huTaoUa46vgT, 0OAGNaNgv3wwzf3ckQ_KTm</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>1241, 1242</t>
-        </is>
-      </c>
-      <c r="Q35" t="n">
-        <v>2</v>
-      </c>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>Funktionsfläche_HTR_K</t>
-        </is>
-      </c>
-      <c r="S35" t="n">
-        <v>81.8638385</v>
-      </c>
-      <c r="T35" t="n">
-        <v>68.07347249999999</v>
-      </c>
-      <c r="U35" t="n">
-        <v>13.790366</v>
-      </c>
-      <c r="V35" t="n">
-        <v>0</v>
-      </c>
-      <c r="W35" t="n">
-        <v>0</v>
-      </c>
-      <c r="X35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>0</v>
-      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr"/>
+      <c r="S35" t="inlineStr"/>
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr"/>
+      <c r="V35" t="inlineStr"/>
+      <c r="W35" t="inlineStr"/>
+      <c r="X35" t="inlineStr"/>
+      <c r="Y35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3779,12 +3519,12 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>UG2</t>
+          <t>OG, UG</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>-8.2</t>
+          <t>7.65, -3.6</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -3804,16 +3544,16 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>3EFA13Ox1F58pYx6_i5NyU</t>
+          <t>1gy1MO$xP7XRrROZz1e_bn, 2r3VzFO2P8BhGedOcYmqyS, 05phPmber0Agf4IgoU6h56, 2shfm9PYTCFQzCvcxPOOdY</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>1236</t>
+          <t>1231, 1238, 1239, 1240</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R36" t="inlineStr">
         <is>
@@ -3821,16 +3561,16 @@
         </is>
       </c>
       <c r="S36" t="n">
-        <v>130.4597315</v>
+        <v>214.391424</v>
       </c>
       <c r="T36" t="n">
-        <v>130.4597315</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
         <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>198.723156</v>
       </c>
       <c r="W36" t="n">
         <v>0</v>
@@ -3839,7 +3579,7 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>15.668268</v>
       </c>
     </row>
     <row r="37">
@@ -3884,12 +3624,12 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>UG2</t>
+          <t>UG</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>-8.2</t>
+          <t>-3.6</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -3909,12 +3649,12 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>0VzQ2RIZnBkuyXmMpvbN9_</t>
+          <t>329ZR9gIvFJgW$Yp42rcBC</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>1237</t>
+          <t>1232</t>
         </is>
       </c>
       <c r="Q37" t="n">
@@ -3926,16 +3666,16 @@
         </is>
       </c>
       <c r="S37" t="n">
-        <v>38.861445</v>
+        <v>33.822831</v>
       </c>
       <c r="T37" t="n">
-        <v>38.861445</v>
+        <v>0</v>
       </c>
       <c r="U37" t="n">
         <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>33.822831</v>
       </c>
       <c r="W37" t="n">
         <v>0</v>
@@ -4010,12 +3750,12 @@
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
-          <t>UG2, UG1, EG, OG1, OG2, OG3</t>
+          <t>-3. Geschoss, -2. Geschoss, UG, EG, 1. Geschoss, OG</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>-8.2, -3.78, 0.0, 2.998, 7.94, 11.948</t>
+          <t>-9.25, -6.4, -3.6, 0.0, 3.65, 7.65</t>
         </is>
       </c>
       <c r="L39" t="inlineStr"/>
@@ -4027,16 +3767,16 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>11rtg$OHHCQgjPenPfbWHc, 1IKxMLTg96xBLZwOLJkOep, 2lJbeNWPr69PR6Bv8eHLx5, 0sM00mZHr6DOEYTFqh$IrG, 0rjMKvNtzAnefNaYJ97j52, 0qFk07a55D6POPpcM5bCmf</t>
+          <t>32xUYb6gT8ZucWxfAPPPgB, 1gidodw_DBO9zIqA4I4Tyi, 3WZJVz6859o9dSIhC80w61, 1$oL8Hh4H33QJDNcRaLaPg, 3ASPZ5Wb51Rw0CSOTH9tVP, 0iesInyHDFsviRu9$LiyeK, 13q4zSvG9DdwoWJkGCk_fu, 3o72QFQvr7lf7nGhb1DBtF</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>1285, 1287, 1293, 1300, 1305, 1309</t>
+          <t>1295, 1300, 1307, 1308, 1313, 1314, 1317, 1323</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="R39" t="inlineStr">
         <is>
@@ -4044,25 +3784,25 @@
         </is>
       </c>
       <c r="S39" t="n">
-        <v>3885.5616805</v>
+        <v>5479.670978</v>
       </c>
       <c r="T39" t="n">
-        <v>946.7966155</v>
+        <v>1287.12523</v>
       </c>
       <c r="U39" t="n">
-        <v>944.3288025000001</v>
+        <v>1287.12523</v>
       </c>
       <c r="V39" t="n">
-        <v>635.473241</v>
+        <v>1325.614241</v>
       </c>
       <c r="W39" t="n">
-        <v>607.3553475</v>
+        <v>541.0999609999999</v>
       </c>
       <c r="X39" t="n">
-        <v>607.3728175</v>
+        <v>522.619173</v>
       </c>
       <c r="Y39" t="n">
-        <v>144.2348565</v>
+        <v>516.087143</v>
       </c>
     </row>
     <row r="40">
@@ -4077,12 +3817,12 @@
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
-          <t>UG2, UG1, EG, OG1, OG2, OG3</t>
+          <t>-3. Geschoss, -2. Geschoss, UG, EG, 1. Geschoss, OG</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>-8.2, -3.78, 0.0, 2.998, 7.94, 11.948</t>
+          <t>-9.25, -6.4, -3.6, 0.0, 3.65, 7.65</t>
         </is>
       </c>
       <c r="L40" t="inlineStr"/>
@@ -4094,16 +3834,16 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>2g7lHgM9fCfeWFLbqCROTN, 2TjpIVE3fEjf2yeWwF5tbt, 37U7QqRiD3K8YpI0EDvqEG, 3Phqv9RFv0aPLT5D_Im9QT, 2CTrriW1D4XfbevcRhL0D$, 3ue0$unPz0uux7AwL1STF3, 0BPV577Cv2qOXbm$_0BLlX, 0D49X8G8b21vMvV9fI6DYy, 3QbhoocVL16heqVtso3nIe, 1vS9xL68j7QRd7X5GTAvLE, 1MeUygKbr5gwqhdLnI1$fr</t>
+          <t>20NpxpK69BFusUiDDRtf10, 3E$tswQAPCsPCgMRjNrHsH, 1qrbHXBMX2yRhjue$7geb$, 1eupe3juT8aftOlJ9hg638, 2ZCe634fb8iAvhVJag1Fcc, 0FxKGVCyz3Of58MYD8Mv3b, 2ul_LbSif04OvKs5CQ_IKY, 0ZW72VIr95rvOTTkPJLq6U, 2sTcAT2vnE1hVbGM9h6Tnm, 1wAuqP15H2LOxT7LD11zVk, 2gWaEX$Kj1hO1wo$Ao7Kks, 21YsDo5uzBdg3lkyBC3bVL, 3dgN8ScwjAL8S2O$LS6ZfP, 3G6rr_NhPEYvBraTj5LRYF, 3JmSL5c0j0Y8vrCOJ5enu8, 3biGXOu7f9lB4VQJQ9hvUL, 1rr$OnbQ96LAXyyNlpar0j, 2HEec9CxzEQh9FJ8XfDnu9, 3$b34kgN18YQ50N33qhfdq, 0sC5YvQerEDBnRusKtCUG4, 2xViyMp9n4eg8BzzxxAxL1, 2Ej$q3hWLA$AALtqSSgISc</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>1283, 1284, 1286, 1290, 1291, 1292, 1297, 1298, 1299, 1304, 1308</t>
+          <t>1293, 1294, 1297, 1298, 1299, 1301, 1302, 1303, 1304, 1305, 1306, 1309, 1310, 1311, 1312, 1315, 1316, 1318, 1319, 1320, 1321, 1322</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="R40" t="inlineStr">
         <is>
@@ -4111,25 +3851,25 @@
         </is>
       </c>
       <c r="S40" t="n">
-        <v>5484.879056999999</v>
+        <v>10718.382495</v>
       </c>
       <c r="T40" t="n">
-        <v>1893.5763265</v>
+        <v>2574.25046</v>
       </c>
       <c r="U40" t="n">
-        <v>944.3288025000001</v>
+        <v>2574.25046</v>
       </c>
       <c r="V40" t="n">
-        <v>1280.172307</v>
+        <v>3079.153133</v>
       </c>
       <c r="W40" t="n">
-        <v>615.1939470000001</v>
+        <v>969.3224289999999</v>
       </c>
       <c r="X40" t="n">
-        <v>607.3728175</v>
+        <v>545.0024430000001</v>
       </c>
       <c r="Y40" t="n">
-        <v>144.2348565</v>
+        <v>976.4035699999998</v>
       </c>
     </row>
     <row r="41">
@@ -4167,23 +3907,75 @@
       <c r="H41" t="n">
         <v>20</v>
       </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr"/>
-      <c r="P41" t="inlineStr"/>
-      <c r="Q41" t="inlineStr"/>
-      <c r="R41" t="inlineStr"/>
-      <c r="S41" t="inlineStr"/>
-      <c r="T41" t="inlineStr"/>
-      <c r="U41" t="inlineStr"/>
-      <c r="V41" t="inlineStr"/>
-      <c r="W41" t="inlineStr"/>
-      <c r="X41" t="inlineStr"/>
-      <c r="Y41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>AGH</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>OG</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>7.65</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>NNF</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>Hausdienst</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>INTERNAL</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>2t_chHHxX9fBLHfnDfn8L9, 2dYgk4XDnFFRRPb42IS4Tb</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>1259, 1260</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>2</v>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>Hausdienst_AGH</t>
+        </is>
+      </c>
+      <c r="S41" t="n">
+        <v>408.501664</v>
+      </c>
+      <c r="T41" t="n">
+        <v>0</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
+      </c>
+      <c r="V41" t="n">
+        <v>0</v>
+      </c>
+      <c r="W41" t="n">
+        <v>0</v>
+      </c>
+      <c r="X41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>408.501664</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -4252,12 +4044,12 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>1elxkk8h12l8VI66SES48s</t>
+          <t>0g0QzkYn50YeACUxcPqf9T</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>1256</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="Q42" t="n">
@@ -4269,7 +4061,7 @@
         </is>
       </c>
       <c r="S42" t="n">
-        <v>11.070615</v>
+        <v>12.085796</v>
       </c>
       <c r="T42" t="n">
         <v>0</v>
@@ -4278,10 +4070,10 @@
         <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>11.070615</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>12.085796</v>
       </c>
       <c r="X42" t="n">
         <v>0</v>
@@ -4332,12 +4124,12 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>UG2</t>
+          <t>1. Geschoss</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>-8.2</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -4357,12 +4149,12 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>2jQqxIN7D0G9XrN3psKCHB</t>
+          <t>0zkT_iaZXCl80nJ7Y9EKl4</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>1255</t>
+          <t>1258</t>
         </is>
       </c>
       <c r="Q43" t="n">
@@ -4374,10 +4166,10 @@
         </is>
       </c>
       <c r="S43" t="n">
-        <v>11.5049595</v>
+        <v>23.562948</v>
       </c>
       <c r="T43" t="n">
-        <v>11.5049595</v>
+        <v>0</v>
       </c>
       <c r="U43" t="n">
         <v>0</v>
@@ -4389,7 +4181,7 @@
         <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>23.562948</v>
       </c>
       <c r="Y43" t="n">
         <v>0</v>
@@ -4430,75 +4222,23 @@
       <c r="H44" t="n">
         <v>25</v>
       </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>HRR</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>UG2</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>-8.2</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>NNF</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>Hausdienst</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>INTERNAL</t>
-        </is>
-      </c>
-      <c r="O44" t="inlineStr">
-        <is>
-          <t>0SfLsfaY1DQQexHNkqpPq8</t>
-        </is>
-      </c>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>1254</t>
-        </is>
-      </c>
-      <c r="Q44" t="n">
-        <v>1</v>
-      </c>
-      <c r="R44" t="inlineStr">
-        <is>
-          <t>Hausdienst_HRR</t>
-        </is>
-      </c>
-      <c r="S44" t="n">
-        <v>24.251362</v>
-      </c>
-      <c r="T44" t="n">
-        <v>24.251362</v>
-      </c>
-      <c r="U44" t="n">
-        <v>0</v>
-      </c>
-      <c r="V44" t="n">
-        <v>0</v>
-      </c>
-      <c r="W44" t="n">
-        <v>0</v>
-      </c>
-      <c r="X44" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y44" t="n">
-        <v>0</v>
-      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="inlineStr"/>
+      <c r="S44" t="inlineStr"/>
+      <c r="T44" t="inlineStr"/>
+      <c r="U44" t="inlineStr"/>
+      <c r="V44" t="inlineStr"/>
+      <c r="W44" t="inlineStr"/>
+      <c r="X44" t="inlineStr"/>
+      <c r="Y44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -4542,12 +4282,12 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>UG1, OG2</t>
+          <t>1. Geschoss, UG, EG</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>-3.78, 7.94</t>
+          <t>3.65, -3.6, 0.0</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -4567,16 +4307,16 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>25qvKAslv4su4AGnfPnQAy, 0$R0qHln98kepMxkmwzDXO</t>
+          <t>3wTnr2v4rAteZQ5bF5K2_M, 2j5JNLySbAteSlc$brVcCs, 2JNSHBJa53Sua8Pc8lc41H</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>1259, 1260</t>
+          <t>1262, 1266, 1267</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R45" t="inlineStr">
         <is>
@@ -4584,22 +4324,22 @@
         </is>
       </c>
       <c r="S45" t="n">
-        <v>8.0182985</v>
+        <v>44.366531</v>
       </c>
       <c r="T45" t="n">
         <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>3.639574</v>
+        <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>25.387835</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>9.489348</v>
       </c>
       <c r="X45" t="n">
-        <v>4.3787245</v>
+        <v>9.489348</v>
       </c>
       <c r="Y45" t="n">
         <v>0</v>
@@ -4667,17 +4407,17 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>EXTERNAL</t>
+          <t>INTERNAL</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>1KAZImcajE19VMZ2urkS9A</t>
+          <t>0CAa9Ma5fEHAjsub3tn7O2</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>1249</t>
+          <t>1253</t>
         </is>
       </c>
       <c r="Q46" t="n">
@@ -4689,7 +4429,7 @@
         </is>
       </c>
       <c r="S46" t="n">
-        <v>14.9977755</v>
+        <v>16.617348</v>
       </c>
       <c r="T46" t="n">
         <v>0</v>
@@ -4698,10 +4438,10 @@
         <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>14.9977755</v>
+        <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>16.617348</v>
       </c>
       <c r="X46" t="n">
         <v>0</v>
@@ -4745,75 +4485,23 @@
       <c r="H47" t="n">
         <v>30</v>
       </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>ESP</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>EG</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>VF</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>Sportbereich</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>EXTERNAL</t>
-        </is>
-      </c>
-      <c r="O47" t="inlineStr">
-        <is>
-          <t>0p4XPibzXDmfYuHdDNQKoi</t>
-        </is>
-      </c>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t>1239</t>
-        </is>
-      </c>
-      <c r="Q47" t="n">
-        <v>1</v>
-      </c>
-      <c r="R47" t="inlineStr">
-        <is>
-          <t>Sportbereich_ESP</t>
-        </is>
-      </c>
-      <c r="S47" t="n">
-        <v>34.1596555</v>
-      </c>
-      <c r="T47" t="n">
-        <v>0</v>
-      </c>
-      <c r="U47" t="n">
-        <v>0</v>
-      </c>
-      <c r="V47" t="n">
-        <v>34.1596555</v>
-      </c>
-      <c r="W47" t="n">
-        <v>0</v>
-      </c>
-      <c r="X47" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y47" t="n">
-        <v>0</v>
-      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr"/>
+      <c r="R47" t="inlineStr"/>
+      <c r="S47" t="inlineStr"/>
+      <c r="T47" t="inlineStr"/>
+      <c r="U47" t="inlineStr"/>
+      <c r="V47" t="inlineStr"/>
+      <c r="W47" t="inlineStr"/>
+      <c r="X47" t="inlineStr"/>
+      <c r="Y47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -4857,12 +4545,12 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>UG1</t>
+          <t>-2. Geschoss</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-6.4</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -4882,12 +4570,12 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>2DRzef4hn3IgIiLgkhkHE9, 2EaietiEbAIPhvSO2Cvy$b</t>
+          <t>2MkuFBa9j3ePTZR6et6RVm, 0L1$lPM39FEOrqxv4xuzey</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>1245, 1246</t>
+          <t>1250, 1251</t>
         </is>
       </c>
       <c r="Q48" t="n">
@@ -4899,13 +4587,13 @@
         </is>
       </c>
       <c r="S48" t="n">
-        <v>31.359346</v>
+        <v>31.119685</v>
       </c>
       <c r="T48" t="n">
         <v>0</v>
       </c>
       <c r="U48" t="n">
-        <v>31.359346</v>
+        <v>31.119685</v>
       </c>
       <c r="V48" t="n">
         <v>0</v>
@@ -4962,12 +4650,12 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>UG1</t>
+          <t>-2. Geschoss</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-6.4</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -4987,12 +4675,12 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>2_ozTiGP19wxfIiizV$YDP, 1hrw6SBSX5_xz0kjcf$lQq, 3MbScePwXCG951Z0r4L0yN, 3YWB1QD45A0ffgE_grSlSK</t>
+          <t>2rdOLwb$X52u_kCvUQVX3F, 35xWWY93XABfSkaS7vI23K, 1Ri5H0T4f54A_siIEhqmyK, 1RbjKB6vbE7gqDdeJ9nwPe</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>1247, 1248, 1250, 1251</t>
+          <t>1254, 1255, 1256, 1257</t>
         </is>
       </c>
       <c r="Q49" t="n">
@@ -5004,13 +4692,13 @@
         </is>
       </c>
       <c r="S49" t="n">
-        <v>169.608867</v>
+        <v>185.735414</v>
       </c>
       <c r="T49" t="n">
         <v>0</v>
       </c>
       <c r="U49" t="n">
-        <v>169.608867</v>
+        <v>185.735414</v>
       </c>
       <c r="V49" t="n">
         <v>0</v>
@@ -5067,12 +4755,12 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>UG</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-3.6</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -5092,12 +4780,12 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>3vzyyhvhTCCxHI3Ujz_Pdk</t>
+          <t>2kzklfMtXAHh4tqI4eVVZB</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>1240</t>
+          <t>1245</t>
         </is>
       </c>
       <c r="Q50" t="n">
@@ -5109,7 +4797,7 @@
         </is>
       </c>
       <c r="S50" t="n">
-        <v>13.502395</v>
+        <v>14.753575</v>
       </c>
       <c r="T50" t="n">
         <v>0</v>
@@ -5118,7 +4806,7 @@
         <v>0</v>
       </c>
       <c r="V50" t="n">
-        <v>13.502395</v>
+        <v>14.753575</v>
       </c>
       <c r="W50" t="n">
         <v>0</v>
@@ -5172,12 +4860,12 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>OG1</t>
+          <t>-3. Geschoss</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2.998</t>
+          <t>-9.25</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -5197,12 +4885,12 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>2lK1NiaZXE9g_b2KyM_qzf</t>
+          <t>0OF33YtIv4Hx1G$D83kBWw</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>1244</t>
+          <t>1252</t>
         </is>
       </c>
       <c r="Q51" t="n">
@@ -5214,10 +4902,10 @@
         </is>
       </c>
       <c r="S51" t="n">
-        <v>11.810404</v>
+        <v>20.059019</v>
       </c>
       <c r="T51" t="n">
-        <v>0</v>
+        <v>20.059019</v>
       </c>
       <c r="U51" t="n">
         <v>0</v>
@@ -5226,7 +4914,7 @@
         <v>0</v>
       </c>
       <c r="W51" t="n">
-        <v>11.810404</v>
+        <v>0</v>
       </c>
       <c r="X51" t="n">
         <v>0</v>
@@ -5270,75 +4958,23 @@
       <c r="H52" t="n">
         <v>180</v>
       </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>SGR</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>UG2, OG1</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>-8.2, 2.998</t>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>HNF</t>
-        </is>
-      </c>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>Sportbereich</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>INTERNAL</t>
-        </is>
-      </c>
-      <c r="O52" t="inlineStr">
-        <is>
-          <t>0fphzOn3z3ffzYnIZDfkRZ, 3$MWY95kL37xnSaojxj3cW</t>
-        </is>
-      </c>
-      <c r="P52" t="inlineStr">
-        <is>
-          <t>1252, 1253</t>
-        </is>
-      </c>
-      <c r="Q52" t="n">
-        <v>2</v>
-      </c>
-      <c r="R52" t="inlineStr">
-        <is>
-          <t>Sportbereich_SGR</t>
-        </is>
-      </c>
-      <c r="S52" t="n">
-        <v>179.438013</v>
-      </c>
-      <c r="T52" t="n">
-        <v>89.857005</v>
-      </c>
-      <c r="U52" t="n">
-        <v>0</v>
-      </c>
-      <c r="V52" t="n">
-        <v>0</v>
-      </c>
-      <c r="W52" t="n">
-        <v>89.581008</v>
-      </c>
-      <c r="X52" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y52" t="n">
-        <v>0</v>
-      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr"/>
+      <c r="R52" t="inlineStr"/>
+      <c r="S52" t="inlineStr"/>
+      <c r="T52" t="inlineStr"/>
+      <c r="U52" t="inlineStr"/>
+      <c r="V52" t="inlineStr"/>
+      <c r="W52" t="inlineStr"/>
+      <c r="X52" t="inlineStr"/>
+      <c r="Y52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -5375,75 +5011,23 @@
       <c r="H53" t="n">
         <v>896</v>
       </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>SPH</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>UG2, OG1</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>-8.2, 2.998</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>HNF</t>
-        </is>
-      </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>Sportbereich</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>INTERNAL</t>
-        </is>
-      </c>
-      <c r="O53" t="inlineStr">
-        <is>
-          <t>1mK10My2H1Jf6TH2FFyNJl, 0v8vKsFUHEhuGCI94TqyuL</t>
-        </is>
-      </c>
-      <c r="P53" t="inlineStr">
-        <is>
-          <t>1257, 1258</t>
-        </is>
-      </c>
-      <c r="Q53" t="n">
-        <v>2</v>
-      </c>
-      <c r="R53" t="inlineStr">
-        <is>
-          <t>Sportbereich_SPH</t>
-        </is>
-      </c>
-      <c r="S53" t="n">
-        <v>926.76099</v>
-      </c>
-      <c r="T53" t="n">
-        <v>463.376039</v>
-      </c>
-      <c r="U53" t="n">
-        <v>0</v>
-      </c>
-      <c r="V53" t="n">
-        <v>0</v>
-      </c>
-      <c r="W53" t="n">
-        <v>463.384951</v>
-      </c>
-      <c r="X53" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y53" t="n">
-        <v>0</v>
-      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr"/>
+      <c r="R53" t="inlineStr"/>
+      <c r="S53" t="inlineStr"/>
+      <c r="T53" t="inlineStr"/>
+      <c r="U53" t="inlineStr"/>
+      <c r="V53" t="inlineStr"/>
+      <c r="W53" t="inlineStr"/>
+      <c r="X53" t="inlineStr"/>
+      <c r="Y53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -5480,23 +5064,75 @@
       <c r="H54" t="n">
         <v>10</v>
       </c>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
-      <c r="O54" t="inlineStr"/>
-      <c r="P54" t="inlineStr"/>
-      <c r="Q54" t="inlineStr"/>
-      <c r="R54" t="inlineStr"/>
-      <c r="S54" t="inlineStr"/>
-      <c r="T54" t="inlineStr"/>
-      <c r="U54" t="inlineStr"/>
-      <c r="V54" t="inlineStr"/>
-      <c r="W54" t="inlineStr"/>
-      <c r="X54" t="inlineStr"/>
-      <c r="Y54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>VSR</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>-3.6</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>VF</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>Sportbereich</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>INTERNAL</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>0c0SRnRBf3BBLeCiaKjt2p, 0U$47L9U1EhBqNR_6mg9tg</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>1246, 1247</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>2</v>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>Sportbereich_VSR</t>
+        </is>
+      </c>
+      <c r="S54" t="n">
+        <v>4.89984</v>
+      </c>
+      <c r="T54" t="n">
+        <v>0</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
+      </c>
+      <c r="V54" t="n">
+        <v>4.89984</v>
+      </c>
+      <c r="W54" t="n">
+        <v>0</v>
+      </c>
+      <c r="X54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -5531,23 +5167,75 @@
       <c r="H55" t="n">
         <v>8</v>
       </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
-      <c r="O55" t="inlineStr"/>
-      <c r="P55" t="inlineStr"/>
-      <c r="Q55" t="inlineStr"/>
-      <c r="R55" t="inlineStr"/>
-      <c r="S55" t="inlineStr"/>
-      <c r="T55" t="inlineStr"/>
-      <c r="U55" t="inlineStr"/>
-      <c r="V55" t="inlineStr"/>
-      <c r="W55" t="inlineStr"/>
-      <c r="X55" t="inlineStr"/>
-      <c r="Y55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>WAL</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>1. Geschoss, OG, -3. Geschoss, -2. Geschoss, UG, EG</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>3.65, 7.65, -9.25, -6.4, -3.6, 0.0</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>VF</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>Sportbereich</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>INTERNAL</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>3eRDR1539DfAyqNphQzEld, 0o_Vc6NJL42u6QeIg$vfUv, 3gR2dIIQv1K87prBYZma2s, 1JZ2sCz4j0vBHYKD6E6EZ9, 0ZeDtOxF9B1BRh5BeNaVTG, 19HwThHHbEQhAJY3thvaQZ</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>1236, 1237, 1241, 1242, 1243, 1244</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>6</v>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>Sportbereich_WAL</t>
+        </is>
+      </c>
+      <c r="S55" t="n">
+        <v>78.881229</v>
+      </c>
+      <c r="T55" t="n">
+        <v>13.148786</v>
+      </c>
+      <c r="U55" t="n">
+        <v>13.148786</v>
+      </c>
+      <c r="V55" t="n">
+        <v>13.148786</v>
+      </c>
+      <c r="W55" t="n">
+        <v>13.144957</v>
+      </c>
+      <c r="X55" t="n">
+        <v>13.144957</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>13.144957</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -5591,12 +5279,12 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>UG1, OG2</t>
+          <t>-3. Geschoss, EG</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>-3.78, 7.94</t>
+          <t>-9.25, 0.0</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -5616,12 +5304,12 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>2gsiWFr2TB1AHTbv7ojX6m, 3jgApaggT6VOj2drGLqhV$</t>
+          <t>1GupYPuB9CruRMuqndzcqi, 2PXzDaDKDBjOeh2XaUMhzK</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>1277, 1278</t>
+          <t>1284, 1285</t>
         </is>
       </c>
       <c r="Q56" t="n">
@@ -5633,22 +5321,22 @@
         </is>
       </c>
       <c r="S56" t="n">
-        <v>15.627722</v>
+        <v>20.353308</v>
       </c>
       <c r="T56" t="n">
-        <v>0</v>
+        <v>14.163432</v>
       </c>
       <c r="U56" t="n">
-        <v>9.246236</v>
+        <v>0</v>
       </c>
       <c r="V56" t="n">
         <v>0</v>
       </c>
       <c r="W56" t="n">
-        <v>0</v>
+        <v>6.189876</v>
       </c>
       <c r="X56" t="n">
-        <v>6.381486</v>
+        <v>0</v>
       </c>
       <c r="Y56" t="n">
         <v>0</v>
@@ -5696,12 +5384,12 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>UG1, OG2</t>
+          <t>-3. Geschoss, EG</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>-3.78, 7.94</t>
+          <t>-9.25, 0.0</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -5721,12 +5409,12 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>0L$CPopvL2ng78uaCkxmd2, 2R0Ko1_rT45gQWRWnSw8Rh</t>
+          <t>3fFbnlvNn6yBCGAa2MPByn, 0Nx1PuXgb0a8CG7aDO$ArL</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>1279, 1280</t>
+          <t>1286, 1287</t>
         </is>
       </c>
       <c r="Q57" t="n">
@@ -5738,22 +5426,22 @@
         </is>
       </c>
       <c r="S57" t="n">
-        <v>15.6001035</v>
+        <v>20.359151</v>
       </c>
       <c r="T57" t="n">
-        <v>0</v>
+        <v>14.169275</v>
       </c>
       <c r="U57" t="n">
-        <v>11.0386675</v>
+        <v>0</v>
       </c>
       <c r="V57" t="n">
         <v>0</v>
       </c>
       <c r="W57" t="n">
-        <v>0</v>
+        <v>6.189876</v>
       </c>
       <c r="X57" t="n">
-        <v>4.561436</v>
+        <v>0</v>
       </c>
       <c r="Y57" t="n">
         <v>0</v>
@@ -5801,12 +5489,12 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>UG1</t>
+          <t>-2. Geschoss</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-6.4</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -5826,16 +5514,16 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>2pxOd96v91mxlwof2bdwwu</t>
+          <t>3D5GVSrbL438sA_MPBDGbw, 2EYxBkIxv2Vf417tC4kF_B</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>1243</t>
+          <t>1248, 1249</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R58" t="inlineStr">
         <is>
@@ -5843,13 +5531,13 @@
         </is>
       </c>
       <c r="S58" t="n">
-        <v>3.934619</v>
+        <v>7.012924</v>
       </c>
       <c r="T58" t="n">
         <v>0</v>
       </c>
       <c r="U58" t="n">
-        <v>3.934619</v>
+        <v>7.012924</v>
       </c>
       <c r="V58" t="n">
         <v>0</v>
@@ -5906,12 +5594,12 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>OG3</t>
+          <t>1. Geschoss</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>11.948</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -5931,12 +5619,12 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>2RQb_YuIX0cupTG8njrqa5</t>
+          <t>3lmnlW15D2Wugg6LXVgUh$</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>1266</t>
+          <t>1276</t>
         </is>
       </c>
       <c r="Q59" t="n">
@@ -5948,7 +5636,7 @@
         </is>
       </c>
       <c r="S59" t="n">
-        <v>17.564029</v>
+        <v>16.610202</v>
       </c>
       <c r="T59" t="n">
         <v>0</v>
@@ -5963,10 +5651,10 @@
         <v>0</v>
       </c>
       <c r="X59" t="n">
-        <v>0</v>
+        <v>16.610202</v>
       </c>
       <c r="Y59" t="n">
-        <v>17.564029</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -6036,16 +5724,16 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>3V04x_Gn9CsOd3mf5kjSS7</t>
+          <t>0YH2RK9kLDqwvfXM8yftVB, 1CHulNgsD11gfOQj$248Mm</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>1274</t>
+          <t>1273, 1274</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R60" t="inlineStr">
         <is>
@@ -6053,7 +5741,7 @@
         </is>
       </c>
       <c r="S60" t="n">
-        <v>20.323617</v>
+        <v>31.441863</v>
       </c>
       <c r="T60" t="n">
         <v>0</v>
@@ -6062,10 +5750,10 @@
         <v>0</v>
       </c>
       <c r="V60" t="n">
-        <v>20.323617</v>
+        <v>0</v>
       </c>
       <c r="W60" t="n">
-        <v>0</v>
+        <v>31.441863</v>
       </c>
       <c r="X60" t="n">
         <v>0</v>
@@ -6116,12 +5804,12 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>OG3</t>
+          <t>1. Geschoss</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>11.948</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -6141,7 +5829,7 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>0ydbChVXH5YeiOECwP0lP5</t>
+          <t>2i1NFgikHFlA_lWjrfBTUV</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -6158,7 +5846,7 @@
         </is>
       </c>
       <c r="S61" t="n">
-        <v>35.5960265</v>
+        <v>34.083666</v>
       </c>
       <c r="T61" t="n">
         <v>0</v>
@@ -6173,10 +5861,10 @@
         <v>0</v>
       </c>
       <c r="X61" t="n">
-        <v>0</v>
+        <v>34.083666</v>
       </c>
       <c r="Y61" t="n">
-        <v>35.5960265</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -6221,12 +5909,12 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>OG3</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>11.948</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -6246,12 +5934,12 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>3865N6dr5D2QZmKnsV5UjA</t>
+          <t>3fb_XRdw1BteQSKn8BY9E6</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>1262</t>
+          <t>1272</t>
         </is>
       </c>
       <c r="Q62" t="n">
@@ -6263,7 +5951,7 @@
         </is>
       </c>
       <c r="S62" t="n">
-        <v>17.564029</v>
+        <v>16.610202</v>
       </c>
       <c r="T62" t="n">
         <v>0</v>
@@ -6275,13 +5963,13 @@
         <v>0</v>
       </c>
       <c r="W62" t="n">
-        <v>0</v>
+        <v>16.610202</v>
       </c>
       <c r="X62" t="n">
         <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>17.564029</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -6326,12 +6014,12 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>OG3</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>11.948</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -6351,7 +6039,7 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>2dCF9Z2NrCiPs79T_2XETx</t>
+          <t>33qUnSF8j9cPczPAl_STyj</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -6368,7 +6056,7 @@
         </is>
       </c>
       <c r="S63" t="n">
-        <v>35.517629</v>
+        <v>33.936144</v>
       </c>
       <c r="T63" t="n">
         <v>0</v>
@@ -6380,13 +6068,13 @@
         <v>0</v>
       </c>
       <c r="W63" t="n">
-        <v>0</v>
+        <v>33.936144</v>
       </c>
       <c r="X63" t="n">
         <v>0</v>
       </c>
       <c r="Y63" t="n">
-        <v>35.517629</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -6456,12 +6144,12 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>3th3YBjLPEbgeAFO8BnVLM</t>
+          <t>0YwbNN_Wv11OqMxI4D7nsg</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>1273</t>
+          <t>1282</t>
         </is>
       </c>
       <c r="Q64" t="n">
@@ -6473,7 +6161,7 @@
         </is>
       </c>
       <c r="S64" t="n">
-        <v>90.066202</v>
+        <v>90.623125</v>
       </c>
       <c r="T64" t="n">
         <v>0</v>
@@ -6482,10 +6170,10 @@
         <v>0</v>
       </c>
       <c r="V64" t="n">
-        <v>90.066202</v>
+        <v>0</v>
       </c>
       <c r="W64" t="n">
-        <v>0</v>
+        <v>90.623125</v>
       </c>
       <c r="X64" t="n">
         <v>0</v>
@@ -6536,12 +6224,12 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>OG2</t>
+          <t>1. Geschoss</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>7.94</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -6561,7 +6249,7 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>2V_TDJQGX5u9IXI55MWQFM</t>
+          <t>3K19Ry5FvE$O9E_6DflNxN</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -6578,7 +6266,7 @@
         </is>
       </c>
       <c r="S65" t="n">
-        <v>51.768942</v>
+        <v>51.55713</v>
       </c>
       <c r="T65" t="n">
         <v>0</v>
@@ -6593,152 +6281,10 @@
         <v>0</v>
       </c>
       <c r="X65" t="n">
-        <v>51.768942</v>
+        <v>51.55713</v>
       </c>
       <c r="Y65" t="n">
         <v>0</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr"/>
-      <c r="B66" t="inlineStr"/>
-      <c r="C66" t="inlineStr"/>
-      <c r="D66" t="inlineStr"/>
-      <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr"/>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>aTRH</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>EG, OG1, OG2, OG3</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>0.0, 2.998, 7.94, 11.948</t>
-        </is>
-      </c>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr"/>
-      <c r="N66" t="inlineStr">
-        <is>
-          <t>EXTERNAL</t>
-        </is>
-      </c>
-      <c r="O66" t="inlineStr">
-        <is>
-          <t>0XnoVHZ5b7YeZWNQ2bXPFm, 3aH$lMb654_u$4SW_WvFAN, 14l9pM3sL8xfYz1mvXCNWG, 0hYc3lmMH2T91sw96db3JM, 0pnXM2gsT77R5nDFj8mzSx, 3hhMFg80L1LfBHM_a3hr7A</t>
-        </is>
-      </c>
-      <c r="P66" t="inlineStr">
-        <is>
-          <t>1289, 1295, 1296, 1301, 1302, 1307</t>
-        </is>
-      </c>
-      <c r="Q66" t="n">
-        <v>6</v>
-      </c>
-      <c r="R66" t="inlineStr">
-        <is>
-          <t>aTRH</t>
-        </is>
-      </c>
-      <c r="S66" t="n">
-        <v>166.5463805</v>
-      </c>
-      <c r="T66" t="n">
-        <v>0</v>
-      </c>
-      <c r="U66" t="n">
-        <v>0</v>
-      </c>
-      <c r="V66" t="n">
-        <v>17.082447</v>
-      </c>
-      <c r="W66" t="n">
-        <v>51.266701</v>
-      </c>
-      <c r="X66" t="n">
-        <v>57.619245</v>
-      </c>
-      <c r="Y66" t="n">
-        <v>40.5779875</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr"/>
-      <c r="B67" t="inlineStr"/>
-      <c r="C67" t="inlineStr"/>
-      <c r="D67" t="inlineStr"/>
-      <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr"/>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>aTRHA</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>EG, OG1, OG2, OG3</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>0.0, 2.998, 7.94, 11.948</t>
-        </is>
-      </c>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
-      <c r="N67" t="inlineStr">
-        <is>
-          <t>EXTERNAL</t>
-        </is>
-      </c>
-      <c r="O67" t="inlineStr">
-        <is>
-          <t>1CcwMqeXT8UesKx8nLd6OD, 1MQDEFDcX439MvQ3uigCM$, 2$k1ahqBDFJPjWMBdR8WtC, 3r8c5tGbPC_fDRkxzKA81G</t>
-        </is>
-      </c>
-      <c r="P67" t="inlineStr">
-        <is>
-          <t>1288, 1294, 1303, 1306</t>
-        </is>
-      </c>
-      <c r="Q67" t="n">
-        <v>4</v>
-      </c>
-      <c r="R67" t="inlineStr">
-        <is>
-          <t>aTRHA</t>
-        </is>
-      </c>
-      <c r="S67" t="n">
-        <v>41.80292</v>
-      </c>
-      <c r="T67" t="n">
-        <v>0</v>
-      </c>
-      <c r="U67" t="n">
-        <v>0</v>
-      </c>
-      <c r="V67" t="n">
-        <v>10.45073</v>
-      </c>
-      <c r="W67" t="n">
-        <v>10.45073</v>
-      </c>
-      <c r="X67" t="n">
-        <v>10.45073</v>
-      </c>
-      <c r="Y67" t="n">
-        <v>10.45073</v>
       </c>
     </row>
   </sheetData>

--- a/merged_df.xlsx
+++ b/merged_df.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="812" uniqueCount="373">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="829" uniqueCount="374">
   <si>
     <t>Kürzel (LongName)_target</t>
   </si>
@@ -73,25 +73,22 @@
     <t>sum_Qto_SpaceBaseQuantities.NetFloorArea_actual</t>
   </si>
   <si>
-    <t>__pivot_-8.1_actual</t>
-  </si>
-  <si>
-    <t>__pivot_-5.3_actual</t>
-  </si>
-  <si>
-    <t>__pivot_-4.15_actual</t>
-  </si>
-  <si>
-    <t>__pivot_-1.5_actual</t>
-  </si>
-  <si>
-    <t>__pivot_3.6_actual</t>
-  </si>
-  <si>
-    <t>__pivot_6.8_actual</t>
-  </si>
-  <si>
-    <t>__pivot_10.0_actual</t>
+    <t>__pivot_-6.2_actual</t>
+  </si>
+  <si>
+    <t>__pivot_-3.2_actual</t>
+  </si>
+  <si>
+    <t>__pivot_-0.2_actual</t>
+  </si>
+  <si>
+    <t>__pivot_2.8_actual</t>
+  </si>
+  <si>
+    <t>__pivot_5.8_actual</t>
+  </si>
+  <si>
+    <t>__pivot_8.8_actual</t>
   </si>
   <si>
     <t>KOR</t>
@@ -685,112 +682,106 @@
     <t>Unterricht_TAR</t>
   </si>
   <si>
-    <t>V7-OG2, V7-Dachaufsicht, V7-UG3, V7-UG2, V7-UG1, V7-EG, V7-OG1</t>
-  </si>
-  <si>
-    <t>V7-OG2, V7-UG1, V7-EG, V7-OG1, V7-UG3, V7-UG2</t>
-  </si>
-  <si>
-    <t>V7-Dachaufsicht, V7-EG, V7-UG1</t>
-  </si>
-  <si>
-    <t>V7-OG2, V7-Dachaufsicht</t>
-  </si>
-  <si>
-    <t>V7-EG</t>
-  </si>
-  <si>
-    <t>V7-EG, V7-OG1</t>
-  </si>
-  <si>
-    <t>V7-UG1</t>
-  </si>
-  <si>
-    <t>V7-UG3, V7-UG1</t>
-  </si>
-  <si>
-    <t>V7-UG3, V7-UG2, V7-UG1, V7-EG, V7-OG1, V7-OG2, V7-Dachaufsicht</t>
-  </si>
-  <si>
-    <t>V7-OG2</t>
-  </si>
-  <si>
-    <t>V7-EG, V7-UG2</t>
-  </si>
-  <si>
-    <t>V7-Dachaufsicht</t>
-  </si>
-  <si>
-    <t>V7-UG2, V7-OG2</t>
-  </si>
-  <si>
-    <t>V7-UG3, V7-OG1</t>
-  </si>
-  <si>
-    <t>V7-OG1, V7-OG2, V7-UG3</t>
-  </si>
-  <si>
-    <t>V7-UG2, V7-UG1, V7-EG, V7-OG1, V7-OG2, V7-UG3</t>
-  </si>
-  <si>
-    <t>V7-UG3, V7-EG, V7-OG1</t>
-  </si>
-  <si>
-    <t>V7-OG1, V7-UG3, V7-EG</t>
-  </si>
-  <si>
-    <t>6.8, 10.0, -8.1, -5.3, -4.15, -1.5, 3.6</t>
-  </si>
-  <si>
-    <t>6.8, -4.15, -1.5, 3.6, -8.1, -5.3</t>
-  </si>
-  <si>
-    <t>10.0, -1.5, -4.15</t>
-  </si>
-  <si>
-    <t>6.8, 10.0</t>
-  </si>
-  <si>
-    <t>-1.5</t>
-  </si>
-  <si>
-    <t>-1.5, 3.6</t>
-  </si>
-  <si>
-    <t>-4.15</t>
-  </si>
-  <si>
-    <t>-8.1, -4.15</t>
-  </si>
-  <si>
-    <t>-8.1, -5.3, -4.15, -1.5, 3.6, 6.8, 10.0</t>
-  </si>
-  <si>
-    <t>6.8</t>
-  </si>
-  <si>
-    <t>-1.5, -5.3</t>
-  </si>
-  <si>
-    <t>10.0</t>
-  </si>
-  <si>
-    <t>-5.3, 6.8</t>
-  </si>
-  <si>
-    <t>-8.1, 3.6</t>
-  </si>
-  <si>
-    <t>3.6, 6.8, -8.1</t>
-  </si>
-  <si>
-    <t>-5.3, -4.15, -1.5, 3.6, 6.8, -8.1</t>
-  </si>
-  <si>
-    <t>-8.1, -1.5, 3.6</t>
-  </si>
-  <si>
-    <t>3.6, -8.1, -1.5</t>
+    <t>EG</t>
+  </si>
+  <si>
+    <t>OG_1, OG_2, UG_1, EG, OG</t>
+  </si>
+  <si>
+    <t>UG, UG_1, EG, OG, OG_1, OG_2</t>
+  </si>
+  <si>
+    <t>EG, OG, OG_1, OG_2, UG, UG_1</t>
+  </si>
+  <si>
+    <t>OG_2</t>
+  </si>
+  <si>
+    <t>EG, OG_2</t>
+  </si>
+  <si>
+    <t>OG_1</t>
+  </si>
+  <si>
+    <t>EG, OG_1</t>
+  </si>
+  <si>
+    <t>UG_1, OG, OG_2</t>
+  </si>
+  <si>
+    <t>OG</t>
+  </si>
+  <si>
+    <t>UG_1, OG_2</t>
+  </si>
+  <si>
+    <t>OG, OG_1, OG_2, UG, UG_1, EG</t>
+  </si>
+  <si>
+    <t>OG_1, EG</t>
+  </si>
+  <si>
+    <t>UG, OG</t>
+  </si>
+  <si>
+    <t>UG_1, OG_1</t>
+  </si>
+  <si>
+    <t>OG, UG</t>
+  </si>
+  <si>
+    <t>OG_1, OG_2, UG, UG_1, EG, OG</t>
+  </si>
+  <si>
+    <t>-0.2</t>
+  </si>
+  <si>
+    <t>5.8, 8.8, -3.2, -0.2, 2.8</t>
+  </si>
+  <si>
+    <t>-6.2, -3.2, -0.2, 2.8, 5.8, 8.8</t>
+  </si>
+  <si>
+    <t>-0.2, 2.8, 5.8, 8.8, -6.2, -3.2</t>
+  </si>
+  <si>
+    <t>8.8</t>
+  </si>
+  <si>
+    <t>-0.2, 8.8</t>
+  </si>
+  <si>
+    <t>5.8</t>
+  </si>
+  <si>
+    <t>-0.2, 5.8</t>
+  </si>
+  <si>
+    <t>-3.2, 2.8, 8.8</t>
+  </si>
+  <si>
+    <t>2.8</t>
+  </si>
+  <si>
+    <t>-3.2, 8.8</t>
+  </si>
+  <si>
+    <t>2.8, 5.8, 8.8, -6.2, -3.2, -0.2</t>
+  </si>
+  <si>
+    <t>5.8, -0.2</t>
+  </si>
+  <si>
+    <t>-6.2, 2.8</t>
+  </si>
+  <si>
+    <t>-3.2, 5.8</t>
+  </si>
+  <si>
+    <t>2.8, -6.2</t>
+  </si>
+  <si>
+    <t>5.8, 8.8, -6.2, -3.2, -0.2, 2.8</t>
   </si>
   <si>
     <t>INTERNAL</t>
@@ -805,328 +796,340 @@
     <t>USERDEFINED</t>
   </si>
   <si>
-    <t>2cyYozs$L1cAmp6ZQ7EmAJ, 0YC4dl0pj7c93CzKfFP8E4, 1nicHFrgnBbRgrqYcCfl72, 3MnFOF4ZX6DBSqE0FNpobh, 0p3Ve33Y97SB7EnLtci0l4, 0RJ5dwV2534f4GvShe2i_1, 3uVc4PibP10AiBQj9xLz$v</t>
-  </si>
-  <si>
-    <t>3XyCkZudP378sNP21jOw0k, 3kUV1mO41Cu88t1X4XqniL, 1JbxNP6H57ngqTcrXUBRiD, 1O5Gdh3tj6Nh0Cx0xKZa8m, 3AegQKv891KvC8vc6MPEYv, 34L4Tsi8LAwgtmfRC1FSkw, 3rR8LfP2rEovE_BgzUnJDH, 3V0z2cK6rFAuq6jgiw7xLw, 0ZpBWL4cf8vQEwztsgVNqD, 1ZBPPVXp18ixvTKNeN5kTi, 1epTATSDD79wWeM$kqiiee, 176btooLX2W8PsOpO2ziWz</t>
-  </si>
-  <si>
-    <t>0Z6uFHd8X2dBLdkZ8x_h7f, 3DpJpndpHBYgH4bHUwLpYt, 3CWc0sMFD1yByrRYSIpb5Y, 3BCAXr8i19_QptbXsf4af6, 30O1q4KBHC$9j7uzmL659a, 0xE_NEbHDEYw3WuxfbF0Vy, 32GG5ruUrC9BqNDrq$M7BQ, 0rFVUxKsvDy9J1E6MC6Myw</t>
-  </si>
-  <si>
-    <t>0PXzfT90PF7w4BqNLgVm$a, 3ehe1WWh1BvQecDVQ71DXn</t>
-  </si>
-  <si>
-    <t>1xpPnHqyX5LwISJj0WWzFt, 2hCIveUzf9$OYyff11yInX, 1mHgixDzXBBxjUa6BpOyFl, 1YYYmwKrb6$9UBQ8O0Kas7</t>
-  </si>
-  <si>
-    <t>14Y3XiOjb9KB2p9R_JROTQ</t>
-  </si>
-  <si>
-    <t>3$P2F2nLP6ifGh1mH7hoal, 1ix9RUimH0EOtWDFDEQirm</t>
-  </si>
-  <si>
-    <t>3ivM$6RkD2DBr$vAaDxO1x, 2a18t_biX6uvuIhc$U4RTu, 0uRRHvYKPB08V1h9j_QDtK</t>
-  </si>
-  <si>
-    <t>3RU2RNcjbF$gZ2H5NVu8vN, 1pHIWQ0Qz8ge7Yrdqg4O5S, 35VKPakgj7TO3ekTEP17JP</t>
-  </si>
-  <si>
-    <t>1mKVZ00kvDsuOVXoiQpt0D</t>
-  </si>
-  <si>
-    <t>2JoB81W$rEyOgUi59HrDww</t>
-  </si>
-  <si>
-    <t>3kCSWAu4136vgZBaXegeWe, 3FHmkCMfL3mg3jcNKCTcDi, 0FKXXAiij2v990Lf982PiT, 3P$j3emi1AcOyJcQBNCb6S</t>
-  </si>
-  <si>
-    <t>21apPGvjH2thnDixIMmn4t</t>
-  </si>
-  <si>
-    <t>14fwTTdkn19QjVNmDOApUi, 3JKFErOY99OADNp0MAro5N</t>
-  </si>
-  <si>
-    <t>0_rck5jLX1aBax2vWJINGE</t>
-  </si>
-  <si>
-    <t>3ebj1Mr9rFFgESBeGxLNwW</t>
-  </si>
-  <si>
-    <t>2rfeuCqVr23BhA$CC37j88</t>
-  </si>
-  <si>
-    <t>3_3_gPIePCoPbRh5tdIL3Q</t>
-  </si>
-  <si>
-    <t>2LogZ9rKfBHPGdW874Q8wB</t>
-  </si>
-  <si>
-    <t>2dRwqEizf6ThYfP$cyV4Al, 0EOk9tqzT3IgrObijvu7mh</t>
-  </si>
-  <si>
-    <t>1sI$Wtrl1D08Mz3JqyClG2</t>
-  </si>
-  <si>
-    <t>03HLpY$698bBoWxzOABhvQ</t>
-  </si>
-  <si>
-    <t>3yGDI0tT5048gYOIRs2JqY</t>
-  </si>
-  <si>
-    <t>3KfgC1t053SwNMQH$AEvYh</t>
-  </si>
-  <si>
-    <t>38R1n8Vtj60AAaCoDaB78F</t>
-  </si>
-  <si>
-    <t>2QFkbTT49DOOBd3rsKSqzD</t>
-  </si>
-  <si>
-    <t>2Kxncku1XApwJyJ93pXcrN</t>
-  </si>
-  <si>
-    <t>19fUGy1nzAlxQZ0xLyiHp_</t>
-  </si>
-  <si>
-    <t>3aN3Xub_z6JwKLy5toYGOo</t>
-  </si>
-  <si>
-    <t>1VTCtd601B8O$qm$VjADep, 1piwhcpYTD_BwHTp0410_n</t>
-  </si>
-  <si>
-    <t>1CwMnjctT99RZn$n4VnfTw, 1xIF0v9cn7vu9nv0hLbhR7, 3qoQBIFVP4gwcfWQyVYZGP, 2OPuCjvlLAVh7ceiY7bKbm, 0EMWNIsFj2XPzqTTnGflAM, 2LwMnGJ1H709Gkr$jKTpyE, 3dZxR5j8D5VeEakqsWlUPx, 1MsnmmWQD8E8_yhWZc1ixw</t>
-  </si>
-  <si>
-    <t>0m6PtG1VX1Cf6vYN5PGzuf, 2mmZ1wzlHEVw_uPJiu2Dp4, 2_KgIZaMnBphH7ocSANdkQ, 3skCwKecXEyuQ_q6tv9gUm, 2gk3igOQX9bh_GCY$Yvffx, 1cp2Qxhyj00QVhnipmaAKs, 0HCbkl$6XCihFEJQqpSz6g, 3rUwzC4xz6RhPWDdvCMCYf, 06i4JDb8H6cQ6utezy_FzM, 3FvzuJ0XX3m8xPh9kOj5dI, 2ZZ$4CY0PC_xZL$EK_Br9A, 2H_e5LH$fFvgd2yVvQKt7i, 0NDd1SyOPEPQUBS_by7D5M, 2RROtxfEz0QxGJNW1oiUhJ, 02iRBrKrTDvepZvtBTxDSV</t>
-  </si>
-  <si>
-    <t>29zAYmCx51QwWGf_IPHyAn</t>
-  </si>
-  <si>
-    <t>2HtcOWDdT5rAw_o9Juqmyy</t>
-  </si>
-  <si>
-    <t>33vng_YRz1UvagLeubEJGg</t>
-  </si>
-  <si>
-    <t>2QvA8GtJ966wlh2hhM8wqS, 05$3kJeHDBfQTjQXPO3dYZ</t>
-  </si>
-  <si>
-    <t>1N610nBD50g9PQAu0EfSna</t>
-  </si>
-  <si>
-    <t>0LLmPvMeP0XfBFnf8gcR0h</t>
-  </si>
-  <si>
-    <t>2HWO2R4Kr8pOmhSfbbhHbl, 3OMbk7jTr9Ig$sgvo_Kxop</t>
-  </si>
-  <si>
-    <t>3cTmKYFfjCkesrFLhXRab3</t>
-  </si>
-  <si>
-    <t>37raU0b2z11eKALbrf9ic4, 2TgeON4HrEQP2VCBWhITDw</t>
-  </si>
-  <si>
-    <t>1c6uJ$GTPCdQfIbl1Qcots, 1d3beeu4f6OAz6b0FpqHRn</t>
-  </si>
-  <si>
-    <t>2yudcXTRz9XP14gDfpzFbK, 2qEqWLqenDUxeOUu2SZheg, 3ZLFdDEGLAp9JUhBcPErko</t>
-  </si>
-  <si>
-    <t>0371nCQUv0YARnzvCQ00BJ, 0NoPSxw295vvjPM9Renr9$, 0HagFjBcfDDP1BRQ0NZCWi, 2Sid7WbAbDbOpgEK3OCTqz, 1kxdDIZ3jFohIP0pOpkbZe, 3LMZSnYxj2CwZm5BuoWeBQ</t>
-  </si>
-  <si>
-    <t>2rChpxjmz5BxfPm_bdnXXo, 2pI7Flim123gA3fyW$FY4d, 37Cje6DAH3$h$0Dio3ex4h</t>
-  </si>
-  <si>
-    <t>3mjWz6n750JvWeoGOIDIx6, 32oTeaiNXByA5KMWoDLW7c, 0T96LPFu93AuZ$NiOuZ_Yl</t>
-  </si>
-  <si>
-    <t>1RIjlzmRfAiAgHr1tLrJXU, 0Izpa8ow13WP3EjgVEodLg</t>
-  </si>
-  <si>
-    <t>1pvq_XTsX5OPu92AiW9QQA</t>
-  </si>
-  <si>
-    <t>3NbbrYaHb4uuDwgy8N4Wpe</t>
-  </si>
-  <si>
-    <t>180_CcOY90RhRo_edrn5LW</t>
-  </si>
-  <si>
-    <t>2Wf9OrKszAKup6p$id1wc2</t>
-  </si>
-  <si>
-    <t>0TNfhT3YjBqQQGRLEm0r3P</t>
-  </si>
-  <si>
-    <t>1j9HxiFQHDURvbsCXZYHIh</t>
-  </si>
-  <si>
-    <t>0s4LFVICj17gSd$t2SAA28</t>
-  </si>
-  <si>
-    <t>1155, 1156, 1159, 1160, 1161, 1162, 1163</t>
-  </si>
-  <si>
-    <t>1157, 1158, 1164, 1165, 1166, 1167, 1168, 1170, 1171, 1172, 1173, 1174</t>
-  </si>
-  <si>
-    <t>1169, 1175, 1176, 1177, 1178, 1179, 1180, 1185</t>
-  </si>
-  <si>
-    <t>1193, 1194</t>
-  </si>
-  <si>
-    <t>1202, 1203, 1204, 1205</t>
-  </si>
-  <si>
-    <t>1189</t>
-  </si>
-  <si>
-    <t>1190, 1191</t>
-  </si>
-  <si>
-    <t>1196, 1197, 1198</t>
-  </si>
-  <si>
-    <t>1192, 1199, 1200</t>
-  </si>
-  <si>
-    <t>1201</t>
-  </si>
-  <si>
-    <t>1195</t>
-  </si>
-  <si>
-    <t>1181, 1182, 1183, 1184</t>
-  </si>
-  <si>
-    <t>1186</t>
-  </si>
-  <si>
-    <t>1187, 1188</t>
-  </si>
-  <si>
-    <t>1259</t>
-  </si>
-  <si>
-    <t>1260</t>
-  </si>
-  <si>
-    <t>1237</t>
-  </si>
-  <si>
-    <t>1248</t>
-  </si>
-  <si>
-    <t>1241</t>
-  </si>
-  <si>
-    <t>1239, 1240</t>
-  </si>
-  <si>
-    <t>1242</t>
-  </si>
-  <si>
-    <t>1247</t>
-  </si>
-  <si>
-    <t>1243</t>
-  </si>
-  <si>
-    <t>1261</t>
-  </si>
-  <si>
-    <t>1252</t>
-  </si>
-  <si>
-    <t>1251</t>
-  </si>
-  <si>
-    <t>1250</t>
-  </si>
-  <si>
-    <t>1209</t>
-  </si>
-  <si>
-    <t>1206</t>
-  </si>
-  <si>
-    <t>1207, 1208</t>
-  </si>
-  <si>
-    <t>1264, 1267, 1270, 1275, 1277, 1279, 1283, 1284</t>
-  </si>
-  <si>
-    <t>1262, 1263, 1265, 1266, 1268, 1269, 1271, 1272, 1273, 1274, 1276, 1278, 1280, 1281, 1282</t>
-  </si>
-  <si>
-    <t>1229</t>
-  </si>
-  <si>
-    <t>1228</t>
-  </si>
-  <si>
-    <t>1233</t>
-  </si>
-  <si>
-    <t>1232, 1238</t>
-  </si>
-  <si>
-    <t>1225</t>
-  </si>
-  <si>
-    <t>1218</t>
-  </si>
-  <si>
-    <t>1226, 1227</t>
-  </si>
-  <si>
-    <t>1219</t>
-  </si>
-  <si>
-    <t>1223, 1224</t>
-  </si>
-  <si>
-    <t>1230, 1231</t>
-  </si>
-  <si>
-    <t>1215, 1216, 1220</t>
-  </si>
-  <si>
-    <t>1210, 1211, 1212, 1213, 1214, 1217</t>
-  </si>
-  <si>
-    <t>1254, 1255, 1256</t>
-  </si>
-  <si>
-    <t>1249, 1257, 1258</t>
-  </si>
-  <si>
-    <t>1221, 1222</t>
-  </si>
-  <si>
-    <t>1246</t>
-  </si>
-  <si>
-    <t>1244</t>
-  </si>
-  <si>
-    <t>1245</t>
-  </si>
-  <si>
-    <t>1234</t>
-  </si>
-  <si>
-    <t>1235</t>
-  </si>
-  <si>
-    <t>1253</t>
-  </si>
-  <si>
-    <t>1236</t>
+    <t>2SOb_0EcHBFAhHJQiitwuN</t>
+  </si>
+  <si>
+    <t>373OxjQjf6hBVUI6llAAgc, 0JJiPi3RXCO9ynOVGx542l, 0$IltVBAnDHw0ehvsP827Z, 1au9kJihzDJQ60LGSdeyIT, 3FQbCSTafFURYZVIypkXC7, 21xcMaaGbEWO30S6IEmbZ1, 1_qN9rrC59G8MJirXWJEW_, 1Z6X41M2fCWBaro_y2Ffgn, 0UaE6pOpbA$gmjt8$Yulr1, 3$$3buzE1AqeZkmYqD2wXY, 2Lb30_N89CAAUI7IcX5c53</t>
+  </si>
+  <si>
+    <t>010ARtPff8cer7FyabPk6z, 3W83ctd4TEKxV88BqDg4MJ, 0FITj88p114OrQGzkKpP7v, 04Uzb8kTv7HvaW7n3nhn3A, 0NMc1PVV16VuP0JFOjG_gR, 0nomOLG6P8zvVtxQDpoKKk</t>
+  </si>
+  <si>
+    <t>1klwq9mgXA2Pnf5$PcEGmx, 1LE0WgFSrDiQy4yUPaCWTz, 2CazrxtcjC5xCguHq7pd2s, 0OQiOSDH9CVOyp7AK_QCO3, 3qLGLRGQDBwBo4my7t4lNd, 3xIsIidqvAYwhsHi4CyEFx</t>
+  </si>
+  <si>
+    <t>1xkzZfClb1_gZ5PIPr1IUF</t>
+  </si>
+  <si>
+    <t>0PLEphAjLCbhhX6NhOmrBb</t>
+  </si>
+  <si>
+    <t>0IFTs6HRX1Lg9kELSVNX5t</t>
+  </si>
+  <si>
+    <t>1Zm7tmidj2Yup25v6G58tM</t>
+  </si>
+  <si>
+    <t>0aFSmRkOj5D9WafognwfMa, 1cO3c5Tbj7rhGtIdVXqx$I, 2lYFxxjpD4J8$7UQ_eXZ2P</t>
+  </si>
+  <si>
+    <t>11a8qUFLv048qg9ii0V$lk, 1uR4IKwhPEzx6lW4ynAMo0</t>
+  </si>
+  <si>
+    <t>0CavtjoaH2eOGjuVVfKYrS, 3g1NNtR0f02vHkWIwqi9k3</t>
+  </si>
+  <si>
+    <t>3RiQl0IF18AwT9rBqEJjpM</t>
+  </si>
+  <si>
+    <t>35e1ZKd7vCLwlNOY50dRqc, 2tcvNtRiP6kvTd9lsUE1F8, 2jjn63KlfAMgsOKosP_EI_, 35F884YUf1dg7rRpFntpQz, 3LoTR0Swn8eupso6xOEe2$</t>
+  </si>
+  <si>
+    <t>2Wxb4dq194uRG1e6bHYFYT</t>
+  </si>
+  <si>
+    <t>2hSPSDn9XA6O7IrZJay9rL</t>
+  </si>
+  <si>
+    <t>0FJv0vJi9CwuTncMjP58g3</t>
+  </si>
+  <si>
+    <t>3OCAR6aPL8yx$rky1wh3HI</t>
+  </si>
+  <si>
+    <t>3n4atsqUDEuwR5LVRAZIUM</t>
+  </si>
+  <si>
+    <t>2vAcBrBX55qxUDqyLLshoj</t>
+  </si>
+  <si>
+    <t>1aZg7cg9H2oAhX2mhXtA15</t>
+  </si>
+  <si>
+    <t>1XJSd$wIr8Qvuo2Jl77FyY</t>
+  </si>
+  <si>
+    <t>0ZMBkWCVD7GAcxvp9DM8XO</t>
+  </si>
+  <si>
+    <t>2HTpl_x9b3dB0EasU75AxC</t>
+  </si>
+  <si>
+    <t>0w_NSCzrXDwfdo0uU3iuBd, 1GxlKENUH2XgBUCgzeXT5z</t>
+  </si>
+  <si>
+    <t>1hWEm2QUz65eDFHIwLePUr, 1YTp9YYTPBYOKCsENeUOvw</t>
+  </si>
+  <si>
+    <t>1z7t13v4vEwhyTavZiSITD</t>
+  </si>
+  <si>
+    <t>2d5kYyy4P7vwqmK9904kp3, 18F_OGTE9C59yn$OWd0pQK, 1_GisX7FnFAR2J8GOf4dQo</t>
+  </si>
+  <si>
+    <t>3v5_V$tn90IhOwafSgOSH3</t>
+  </si>
+  <si>
+    <t>3sR44HIzT8DOUEjc03NYO6, 2kQAE1i4H4N9Mr_pxTkG37</t>
+  </si>
+  <si>
+    <t>2rVOZq5gLCPf0fH5wPpuPg, 3IPsIUUWf68emm4pfCVbpX, 28g_ClOH9DDgi_d31z8eXu, 0LkkEkBBv30PKDPD3G6gEz, 0in2jvAVb4sgc9Ap5ONtL5, 0oH4AHy593shHaoFpFQZze</t>
+  </si>
+  <si>
+    <t>1GUvmpuf5Eig3EMmCeXkS9, 0OqLgFJ2z11wmSdH_tJlpy, 0CSFLAV3D2mv44HtdJNqzi, 1p_DJROOrAOhvyUMglhmFp, 3tjDulvMX88BK6ml1SjK8c, 2bD8COhRD3iwttNleo$Iza, 0cTMo6wd9D6RvzMT0xSATF, 35M83qhYf5yvOYvMtLWE3X</t>
+  </si>
+  <si>
+    <t>3MAaQiPif1XgKEAn5r4YDL, 293_VdkhDCFhm1FkYmE$Tc, 3HX4IppO16GgPoM3opXLbF, 3gwX9cMB5BGfLW7qO0Ng_b, 0koofZIE54XB90pAyO4v$d, 1NJ3rg5_D8tgaFsyiUzz_1, 2LfDYXrtDFU9cxiHXBUxwX, 0Gmwbupkr7Ru5atypiH9_9, 2ScR0Le0bD6hLJnerucICa, 1wSRdUMePBbQ6coRi1r96U, 192KgtVXX3O9KQ8VeF_Xjc, 2YzKBWmwfBJf$TxoH94R5t, 1pVDVFvCD1vAWv3q3ZD0Rd, 1Dh$x$QnXAkgcLcNz3jFSK, 2hfVtnbpz9x8t49FIJ_FyD, 2az8SBOEv5Nepactu4dKeh, 1wNBd$3S93n9Qc3E4aZdqH, 2nZxD3K_XEChFNV8TIqb8f, 3Y0vGCauf09BIeVHq9iCrz, 1_YAvzrwn6P99A47sy0uUj, 1Es6kWIwPBi9p$2QN2NxEx, 3fS4p$8lv1y8aF9Eank0j_, 1wkG0HN2D2vQpyZR8K81Mv, 1xX_Bvmf14B9qaOBL1V08l, 2fKMMLz8jBHgnbFnCf9Poo, 0ONagcTRn8rgE1bXK3bXhI, 3U2YjlVCLBIuttorOJfOEK, 0SFDM7etL5KQ7N1cVGGnST</t>
+  </si>
+  <si>
+    <t>2etQ8rFDn0n8oZ564hEIMF</t>
+  </si>
+  <si>
+    <t>1BE7j$w_z3DgJrBbxuDcWz</t>
+  </si>
+  <si>
+    <t>11keaiWaX2rfg5YcZ3aBjL</t>
+  </si>
+  <si>
+    <t>3H_IuzY7P7DOF0cjaDsBj9</t>
+  </si>
+  <si>
+    <t>0qTvA5qZL7ivyocOzb1peF, 0ZlaShdb59MRiwkEJ2ipx8</t>
+  </si>
+  <si>
+    <t>0nHnNOyiv1KxVDLOd0epM4</t>
+  </si>
+  <si>
+    <t>0tBvAyEZH9PPLUCzS5SNAA</t>
+  </si>
+  <si>
+    <t>0mQ96AYV1BjexxvP5hOaJq, 3Dn0ZydfnDghhcK5WyPSrM</t>
+  </si>
+  <si>
+    <t>2iZLUbgEv0$QRAUAbpxWRF, 1XHPw0yjf3HR407Tpz4ze_, 22uYGQnmX7o8CZMW773_UL, 2oJhGqpy9ClAmGcOS76FdT</t>
+  </si>
+  <si>
+    <t>1Vk7My3NL99e4SjN_g2VjY</t>
+  </si>
+  <si>
+    <t>1EuZQMWqX8HwKKSurAQMTY, 2bwSLEdUr27hiGydg0cyOL</t>
+  </si>
+  <si>
+    <t>0fmVo1LNj0pOGpYvo5xOTG, 2RKoD8$Jb9vuAmWKUNEBYk</t>
+  </si>
+  <si>
+    <t>1Bk3VHoeT7Qhu1iHMY1DhQ, 1bi98ustr6Xv2V00Hrj6pM</t>
+  </si>
+  <si>
+    <t>0m8Kr9AtzFnhtGIzU5hr$t, 3mTqEEwrT0mPSSZ6bqDKpK, 2AkVFCukv8RwNlwCBpNmPI, 1t0IzLdR5C3B_aRPRqoiPC, 1Y3$J7_01ArQg6f44AH1qz, 1DAFtdCg1CcAoX7oOapHeA</t>
+  </si>
+  <si>
+    <t>18IhWPKrb65AYdLD_Im7b9, 0tDLbT9Dr9J80DN6lerjxY</t>
+  </si>
+  <si>
+    <t>0O5JfWwfX8Xv$OCS5M1sFe, 3rsO$uLjPCOA2_t3fpUlgw</t>
+  </si>
+  <si>
+    <t>2xWjMJ3I5088JXrW8dqF4x, 2h5pNPOrDFUAYLThLcOQNi</t>
+  </si>
+  <si>
+    <t>34PEpJUNT8$AP4XnOS4NbP</t>
+  </si>
+  <si>
+    <t>22olDXyO9F4eiEk9_m4TGj</t>
+  </si>
+  <si>
+    <t>37UZU7LyjDae24BDwc63lz</t>
+  </si>
+  <si>
+    <t>1TaRAKx8DDH8LjySLcenmg</t>
+  </si>
+  <si>
+    <t>05vOMS5EjFHxQUB1lpSO6s</t>
+  </si>
+  <si>
+    <t>016sDhNgT9CRN3U3FoI_Vd</t>
+  </si>
+  <si>
+    <t>371mu4wBPEHfWvS$9s8kn3</t>
+  </si>
+  <si>
+    <t>1434</t>
+  </si>
+  <si>
+    <t>1413, 1414, 1415, 1416, 1417, 1418, 1419, 1420, 1421, 1422, 1423</t>
+  </si>
+  <si>
+    <t>1424, 1425, 1426, 1427, 1428, 1429</t>
+  </si>
+  <si>
+    <t>1430, 1431, 1432, 1433, 1439, 1440</t>
+  </si>
+  <si>
+    <t>1450</t>
+  </si>
+  <si>
+    <t>1451</t>
+  </si>
+  <si>
+    <t>1444</t>
+  </si>
+  <si>
+    <t>1446</t>
+  </si>
+  <si>
+    <t>1447, 1448, 1449</t>
+  </si>
+  <si>
+    <t>1457, 1458</t>
+  </si>
+  <si>
+    <t>1452, 1453</t>
+  </si>
+  <si>
+    <t>1441</t>
+  </si>
+  <si>
+    <t>1435, 1436, 1437, 1438, 1445</t>
+  </si>
+  <si>
+    <t>1442</t>
+  </si>
+  <si>
+    <t>1443</t>
+  </si>
+  <si>
+    <t>1519</t>
+  </si>
+  <si>
+    <t>1520</t>
+  </si>
+  <si>
+    <t>1501</t>
+  </si>
+  <si>
+    <t>1505</t>
+  </si>
+  <si>
+    <t>1507</t>
+  </si>
+  <si>
+    <t>1506</t>
+  </si>
+  <si>
+    <t>1497</t>
+  </si>
+  <si>
+    <t>1504</t>
+  </si>
+  <si>
+    <t>1513, 1518</t>
+  </si>
+  <si>
+    <t>1508, 1509</t>
+  </si>
+  <si>
+    <t>1465</t>
+  </si>
+  <si>
+    <t>1468, 1469, 1470</t>
+  </si>
+  <si>
+    <t>1462</t>
+  </si>
+  <si>
+    <t>1463, 1464</t>
+  </si>
+  <si>
+    <t>1454, 1455, 1456, 1459, 1460, 1461</t>
+  </si>
+  <si>
+    <t>1525, 1529, 1538, 1539, 1540, 1547, 1552, 1556</t>
+  </si>
+  <si>
+    <t>1521, 1522, 1523, 1524, 1526, 1527, 1528, 1530, 1531, 1532, 1533, 1534, 1535, 1536, 1537, 1541, 1542, 1543, 1544, 1545, 1546, 1548, 1549, 1550, 1551, 1553, 1554, 1555</t>
+  </si>
+  <si>
+    <t>1493</t>
+  </si>
+  <si>
+    <t>1494</t>
+  </si>
+  <si>
+    <t>1492</t>
+  </si>
+  <si>
+    <t>1491</t>
+  </si>
+  <si>
+    <t>1496, 1502</t>
+  </si>
+  <si>
+    <t>1487</t>
+  </si>
+  <si>
+    <t>1478</t>
+  </si>
+  <si>
+    <t>1481, 1482</t>
+  </si>
+  <si>
+    <t>1483, 1484, 1485, 1488</t>
+  </si>
+  <si>
+    <t>1471</t>
+  </si>
+  <si>
+    <t>1479, 1480</t>
+  </si>
+  <si>
+    <t>1486, 1490</t>
+  </si>
+  <si>
+    <t>1489, 1495</t>
+  </si>
+  <si>
+    <t>1466, 1467, 1472, 1473, 1474, 1475</t>
+  </si>
+  <si>
+    <t>1514, 1515</t>
+  </si>
+  <si>
+    <t>1516, 1517</t>
+  </si>
+  <si>
+    <t>1476, 1477</t>
+  </si>
+  <si>
+    <t>1503</t>
+  </si>
+  <si>
+    <t>1511</t>
+  </si>
+  <si>
+    <t>1512</t>
+  </si>
+  <si>
+    <t>1498</t>
+  </si>
+  <si>
+    <t>1499</t>
+  </si>
+  <si>
+    <t>1510</t>
+  </si>
+  <si>
+    <t>1500</t>
   </si>
   <si>
     <t>GrossArea</t>
@@ -1490,10 +1493,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z65"/>
+  <dimension ref="A1:Y65"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:26">
+    <row r="1" spans="1:25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1569,263 +1572,302 @@
       <c r="Y1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:25">
+      <c r="A2" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="2" spans="1:26">
-      <c r="A2" t="s">
+      <c r="B2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D2" t="s">
+        <v>154</v>
+      </c>
+      <c r="G2" t="s">
+        <v>160</v>
+      </c>
+      <c r="I2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J2" t="s">
+        <v>222</v>
+      </c>
+      <c r="K2" t="s">
+        <v>239</v>
+      </c>
+      <c r="L2" t="s">
+        <v>154</v>
+      </c>
+      <c r="M2" t="s">
+        <v>147</v>
+      </c>
+      <c r="N2" t="s">
+        <v>256</v>
+      </c>
+      <c r="O2" t="s">
+        <v>260</v>
+      </c>
+      <c r="P2" t="s">
+        <v>316</v>
+      </c>
+      <c r="Q2">
+        <v>1</v>
+      </c>
+      <c r="R2" t="s">
+        <v>160</v>
+      </c>
+      <c r="S2">
+        <v>67.11145399999999</v>
+      </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
+      <c r="U2">
+        <v>0</v>
+      </c>
+      <c r="V2">
+        <v>67.11145399999999</v>
+      </c>
+      <c r="W2">
+        <v>0</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25">
+      <c r="A3" t="s">
         <v>26</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B3" t="s">
         <v>86</v>
       </c>
-      <c r="C2" t="s">
-        <v>148</v>
-      </c>
-      <c r="D2" t="s">
-        <v>155</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="C3" t="s">
+        <v>147</v>
+      </c>
+      <c r="G3" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="3" spans="1:26">
-      <c r="A3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B3" t="s">
-        <v>87</v>
-      </c>
-      <c r="C3" t="s">
-        <v>148</v>
-      </c>
-      <c r="G3" t="s">
-        <v>162</v>
-      </c>
       <c r="I3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J3" t="s">
         <v>223</v>
       </c>
       <c r="K3" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="M3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="N3" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="O3" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="P3" t="s">
         <v>317</v>
       </c>
       <c r="Q3">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="R3" t="s">
+        <v>161</v>
+      </c>
+      <c r="S3">
+        <v>1984.691497</v>
+      </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>450.9674695</v>
+      </c>
+      <c r="V3">
+        <v>450.9674695</v>
+      </c>
+      <c r="W3">
+        <v>180.821619</v>
+      </c>
+      <c r="X3">
+        <v>450.9674695</v>
+      </c>
+      <c r="Y3">
+        <v>450.9674695</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25">
+      <c r="A4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4" t="s">
+        <v>87</v>
+      </c>
+      <c r="C4" t="s">
+        <v>147</v>
+      </c>
+      <c r="D4" t="s">
+        <v>154</v>
+      </c>
+      <c r="G4" t="s">
         <v>162</v>
       </c>
-      <c r="S3">
-        <v>17.6428245</v>
-      </c>
-      <c r="T3">
-        <v>2.5204035</v>
-      </c>
-      <c r="U3">
-        <v>2.5204035</v>
-      </c>
-      <c r="V3">
-        <v>2.5204035</v>
-      </c>
-      <c r="W3">
-        <v>2.5204035</v>
-      </c>
-      <c r="X3">
-        <v>2.5204035</v>
-      </c>
-      <c r="Y3">
-        <v>2.5204035</v>
-      </c>
-      <c r="Z3">
-        <v>2.5204035</v>
-      </c>
-    </row>
-    <row r="4" spans="1:26">
-      <c r="A4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B4" t="s">
-        <v>88</v>
-      </c>
-      <c r="C4" t="s">
-        <v>148</v>
-      </c>
-      <c r="D4" t="s">
-        <v>155</v>
-      </c>
-      <c r="G4" t="s">
-        <v>163</v>
-      </c>
       <c r="I4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J4" t="s">
         <v>224</v>
       </c>
       <c r="K4" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="L4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="M4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="N4" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="O4" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="P4" t="s">
         <v>318</v>
       </c>
       <c r="Q4">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="R4" t="s">
+        <v>162</v>
+      </c>
+      <c r="S4">
+        <v>46.013898</v>
+      </c>
+      <c r="T4">
+        <v>7.668983</v>
+      </c>
+      <c r="U4">
+        <v>7.668983</v>
+      </c>
+      <c r="V4">
+        <v>7.668983</v>
+      </c>
+      <c r="W4">
+        <v>7.668983</v>
+      </c>
+      <c r="X4">
+        <v>7.668983</v>
+      </c>
+      <c r="Y4">
+        <v>7.668983</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25">
+      <c r="A5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" t="s">
+        <v>88</v>
+      </c>
+      <c r="C5" t="s">
+        <v>147</v>
+      </c>
+      <c r="D5" t="s">
+        <v>154</v>
+      </c>
+      <c r="G5" t="s">
         <v>163</v>
       </c>
-      <c r="S4">
-        <v>182.9003195</v>
-      </c>
-      <c r="T4">
-        <v>30.4173945</v>
-      </c>
-      <c r="U4">
-        <v>30.496585</v>
-      </c>
-      <c r="V4">
-        <v>30.496585</v>
-      </c>
-      <c r="W4">
-        <v>30.496585</v>
-      </c>
-      <c r="X4">
-        <v>30.496585</v>
-      </c>
-      <c r="Y4">
-        <v>30.496585</v>
-      </c>
-      <c r="Z4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:26">
-      <c r="A5" t="s">
-        <v>29</v>
-      </c>
-      <c r="B5" t="s">
-        <v>89</v>
-      </c>
-      <c r="C5" t="s">
-        <v>148</v>
-      </c>
-      <c r="D5" t="s">
-        <v>155</v>
-      </c>
-      <c r="G5" t="s">
-        <v>164</v>
-      </c>
       <c r="I5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J5" t="s">
         <v>225</v>
       </c>
       <c r="K5" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="L5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="M5" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="N5" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="O5" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="P5" t="s">
         <v>319</v>
       </c>
       <c r="Q5">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="R5" t="s">
+        <v>163</v>
+      </c>
+      <c r="S5">
+        <v>204.046368</v>
+      </c>
+      <c r="T5">
+        <v>34.7570365</v>
+      </c>
+      <c r="U5">
+        <v>31.4928155</v>
+      </c>
+      <c r="V5">
+        <v>24.102928</v>
+      </c>
+      <c r="W5">
+        <v>41.099854</v>
+      </c>
+      <c r="X5">
+        <v>41.099854</v>
+      </c>
+      <c r="Y5">
+        <v>31.49388</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25">
+      <c r="A6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C6" t="s">
+        <v>147</v>
+      </c>
+      <c r="D6" t="s">
+        <v>154</v>
+      </c>
+      <c r="G6" t="s">
         <v>164</v>
       </c>
-      <c r="S5">
-        <v>62.122086</v>
-      </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
-      <c r="U5">
-        <v>0</v>
-      </c>
-      <c r="V5">
-        <v>5.502205</v>
-      </c>
-      <c r="W5">
-        <v>21.6224945</v>
-      </c>
-      <c r="X5">
-        <v>0</v>
-      </c>
-      <c r="Y5">
-        <v>0</v>
-      </c>
-      <c r="Z5">
-        <v>34.9973865</v>
-      </c>
-    </row>
-    <row r="6" spans="1:26">
-      <c r="A6" t="s">
+    </row>
+    <row r="7" spans="1:25">
+      <c r="A7" t="s">
         <v>30</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B7" t="s">
         <v>90</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C7" t="s">
         <v>148</v>
       </c>
-      <c r="D6" t="s">
-        <v>155</v>
-      </c>
-      <c r="G6" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="7" spans="1:26">
-      <c r="A7" t="s">
-        <v>31</v>
-      </c>
-      <c r="B7" t="s">
-        <v>91</v>
-      </c>
-      <c r="C7" t="s">
-        <v>149</v>
-      </c>
       <c r="D7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E7">
         <v>10.4</v>
@@ -1834,43 +1876,43 @@
         <v>1</v>
       </c>
       <c r="G7" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H7">
         <v>390</v>
       </c>
       <c r="I7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="J7" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="K7" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="L7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M7" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="N7" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="O7" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="P7" t="s">
         <v>320</v>
       </c>
       <c r="Q7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R7" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="S7">
-        <v>571.6080075</v>
+        <v>311.9702625</v>
       </c>
       <c r="T7">
         <v>0</v>
@@ -1879,7 +1921,7 @@
         <v>0</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>311.9702625</v>
       </c>
       <c r="W7">
         <v>0</v>
@@ -1888,24 +1930,21 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>448.0099305</v>
-      </c>
-      <c r="Z7">
-        <v>123.598077</v>
-      </c>
-    </row>
-    <row r="8" spans="1:26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25">
       <c r="A8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C8" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D8" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E8">
         <v>10.4</v>
@@ -1914,285 +1953,222 @@
         <v>1</v>
       </c>
       <c r="G8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H8">
         <v>16</v>
       </c>
       <c r="I8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J8" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="K8" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="L8" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="M8" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="N8" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="O8" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="P8" t="s">
         <v>321</v>
       </c>
       <c r="Q8">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R8" t="s">
+        <v>166</v>
+      </c>
+      <c r="S8">
+        <v>19.749148</v>
+      </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>0</v>
+      </c>
+      <c r="V8">
+        <v>19.749148</v>
+      </c>
+      <c r="W8">
+        <v>0</v>
+      </c>
+      <c r="X8">
+        <v>0</v>
+      </c>
+      <c r="Y8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" t="s">
+        <v>92</v>
+      </c>
+      <c r="C9" t="s">
+        <v>148</v>
+      </c>
+      <c r="D9" t="s">
+        <v>33</v>
+      </c>
+      <c r="G9" t="s">
         <v>167</v>
       </c>
-      <c r="S8">
-        <v>227.2682595</v>
-      </c>
-      <c r="T8">
-        <v>0</v>
-      </c>
-      <c r="U8">
-        <v>0</v>
-      </c>
-      <c r="V8">
-        <v>0</v>
-      </c>
-      <c r="W8">
-        <v>227.2682595</v>
-      </c>
-      <c r="X8">
-        <v>0</v>
-      </c>
-      <c r="Y8">
-        <v>0</v>
-      </c>
-      <c r="Z8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:26">
-      <c r="A9" t="s">
+    </row>
+    <row r="10" spans="1:25">
+      <c r="A10" t="s">
         <v>33</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B10" t="s">
         <v>93</v>
       </c>
-      <c r="C9" t="s">
-        <v>149</v>
-      </c>
-      <c r="D9" t="s">
+      <c r="C10" t="s">
+        <v>148</v>
+      </c>
+      <c r="D10" t="s">
+        <v>33</v>
+      </c>
+      <c r="G10" t="s">
+        <v>168</v>
+      </c>
+      <c r="I10" t="s">
+        <v>33</v>
+      </c>
+      <c r="J10" t="s">
+        <v>222</v>
+      </c>
+      <c r="K10" t="s">
+        <v>239</v>
+      </c>
+      <c r="L10" t="s">
+        <v>33</v>
+      </c>
+      <c r="M10" t="s">
+        <v>148</v>
+      </c>
+      <c r="N10" t="s">
+        <v>257</v>
+      </c>
+      <c r="O10" t="s">
+        <v>266</v>
+      </c>
+      <c r="P10" t="s">
+        <v>322</v>
+      </c>
+      <c r="Q10">
+        <v>1</v>
+      </c>
+      <c r="R10" t="s">
+        <v>168</v>
+      </c>
+      <c r="S10">
+        <v>220.460623</v>
+      </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
+      <c r="U10">
+        <v>0</v>
+      </c>
+      <c r="V10">
+        <v>220.460623</v>
+      </c>
+      <c r="W10">
+        <v>0</v>
+      </c>
+      <c r="X10">
+        <v>0</v>
+      </c>
+      <c r="Y10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25">
+      <c r="A11" t="s">
         <v>34</v>
       </c>
-      <c r="G9" t="s">
-        <v>168</v>
-      </c>
-      <c r="I9" t="s">
+      <c r="B11" t="s">
+        <v>94</v>
+      </c>
+      <c r="C11" t="s">
+        <v>148</v>
+      </c>
+      <c r="G11" t="s">
+        <v>169</v>
+      </c>
+      <c r="I11" t="s">
+        <v>34</v>
+      </c>
+      <c r="J11" t="s">
+        <v>226</v>
+      </c>
+      <c r="K11" t="s">
+        <v>243</v>
+      </c>
+      <c r="M11" t="s">
+        <v>148</v>
+      </c>
+      <c r="N11" t="s">
+        <v>257</v>
+      </c>
+      <c r="O11" t="s">
+        <v>267</v>
+      </c>
+      <c r="P11" t="s">
+        <v>323</v>
+      </c>
+      <c r="Q11">
+        <v>1</v>
+      </c>
+      <c r="R11" t="s">
+        <v>169</v>
+      </c>
+      <c r="S11">
+        <v>191.9765905</v>
+      </c>
+      <c r="T11">
+        <v>0</v>
+      </c>
+      <c r="U11">
+        <v>0</v>
+      </c>
+      <c r="V11">
+        <v>0</v>
+      </c>
+      <c r="W11">
+        <v>0</v>
+      </c>
+      <c r="X11">
+        <v>0</v>
+      </c>
+      <c r="Y11">
+        <v>191.9765905</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25">
+      <c r="A12" t="s">
+        <v>35</v>
+      </c>
+      <c r="B12" t="s">
+        <v>95</v>
+      </c>
+      <c r="C12" t="s">
+        <v>148</v>
+      </c>
+      <c r="D12" t="s">
         <v>33</v>
-      </c>
-      <c r="J9" t="s">
-        <v>227</v>
-      </c>
-      <c r="K9" t="s">
-        <v>245</v>
-      </c>
-      <c r="L9" t="s">
-        <v>34</v>
-      </c>
-      <c r="M9" t="s">
-        <v>149</v>
-      </c>
-      <c r="N9" t="s">
-        <v>260</v>
-      </c>
-      <c r="O9" t="s">
-        <v>268</v>
-      </c>
-      <c r="P9" t="s">
-        <v>322</v>
-      </c>
-      <c r="Q9">
-        <v>1</v>
-      </c>
-      <c r="R9" t="s">
-        <v>168</v>
-      </c>
-      <c r="S9">
-        <v>172.888208</v>
-      </c>
-      <c r="T9">
-        <v>0</v>
-      </c>
-      <c r="U9">
-        <v>0</v>
-      </c>
-      <c r="V9">
-        <v>0</v>
-      </c>
-      <c r="W9">
-        <v>172.888208</v>
-      </c>
-      <c r="X9">
-        <v>0</v>
-      </c>
-      <c r="Y9">
-        <v>0</v>
-      </c>
-      <c r="Z9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:26">
-      <c r="A10" t="s">
-        <v>34</v>
-      </c>
-      <c r="B10" t="s">
-        <v>94</v>
-      </c>
-      <c r="C10" t="s">
-        <v>149</v>
-      </c>
-      <c r="D10" t="s">
-        <v>34</v>
-      </c>
-      <c r="G10" t="s">
-        <v>169</v>
-      </c>
-      <c r="I10" t="s">
-        <v>34</v>
-      </c>
-      <c r="J10" t="s">
-        <v>227</v>
-      </c>
-      <c r="K10" t="s">
-        <v>245</v>
-      </c>
-      <c r="L10" t="s">
-        <v>34</v>
-      </c>
-      <c r="M10" t="s">
-        <v>149</v>
-      </c>
-      <c r="N10" t="s">
-        <v>260</v>
-      </c>
-      <c r="O10" t="s">
-        <v>269</v>
-      </c>
-      <c r="P10" t="s">
-        <v>323</v>
-      </c>
-      <c r="Q10">
-        <v>2</v>
-      </c>
-      <c r="R10" t="s">
-        <v>169</v>
-      </c>
-      <c r="S10">
-        <v>851.0012685</v>
-      </c>
-      <c r="T10">
-        <v>0</v>
-      </c>
-      <c r="U10">
-        <v>0</v>
-      </c>
-      <c r="V10">
-        <v>0</v>
-      </c>
-      <c r="W10">
-        <v>851.0012685</v>
-      </c>
-      <c r="X10">
-        <v>0</v>
-      </c>
-      <c r="Y10">
-        <v>0</v>
-      </c>
-      <c r="Z10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:26">
-      <c r="A11" t="s">
-        <v>35</v>
-      </c>
-      <c r="B11" t="s">
-        <v>95</v>
-      </c>
-      <c r="C11" t="s">
-        <v>149</v>
-      </c>
-      <c r="G11" t="s">
-        <v>170</v>
-      </c>
-      <c r="I11" t="s">
-        <v>35</v>
-      </c>
-      <c r="J11" t="s">
-        <v>228</v>
-      </c>
-      <c r="K11" t="s">
-        <v>246</v>
-      </c>
-      <c r="M11" t="s">
-        <v>149</v>
-      </c>
-      <c r="N11" t="s">
-        <v>260</v>
-      </c>
-      <c r="O11" t="s">
-        <v>270</v>
-      </c>
-      <c r="P11" t="s">
-        <v>324</v>
-      </c>
-      <c r="Q11">
-        <v>3</v>
-      </c>
-      <c r="R11" t="s">
-        <v>170</v>
-      </c>
-      <c r="S11">
-        <v>302.706118</v>
-      </c>
-      <c r="T11">
-        <v>0</v>
-      </c>
-      <c r="U11">
-        <v>0</v>
-      </c>
-      <c r="V11">
-        <v>0</v>
-      </c>
-      <c r="W11">
-        <v>149.781966</v>
-      </c>
-      <c r="X11">
-        <v>152.924152</v>
-      </c>
-      <c r="Y11">
-        <v>0</v>
-      </c>
-      <c r="Z11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:26">
-      <c r="A12" t="s">
-        <v>36</v>
-      </c>
-      <c r="B12" t="s">
-        <v>96</v>
-      </c>
-      <c r="C12" t="s">
-        <v>149</v>
-      </c>
-      <c r="D12" t="s">
-        <v>34</v>
       </c>
       <c r="E12">
         <v>10.8</v>
@@ -2201,155 +2177,149 @@
         <v>1</v>
       </c>
       <c r="G12" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H12">
         <v>400</v>
       </c>
       <c r="I12" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J12" t="s">
         <v>227</v>
       </c>
       <c r="K12" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="L12" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M12" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="N12" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="O12" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="P12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="Q12">
         <v>3</v>
       </c>
       <c r="R12" t="s">
+        <v>170</v>
+      </c>
+      <c r="S12">
+        <v>1198.3615965</v>
+      </c>
+      <c r="T12">
+        <v>0</v>
+      </c>
+      <c r="U12">
+        <v>0</v>
+      </c>
+      <c r="V12">
+        <v>980.1040194999999</v>
+      </c>
+      <c r="W12">
+        <v>0</v>
+      </c>
+      <c r="X12">
+        <v>0</v>
+      </c>
+      <c r="Y12">
+        <v>218.257577</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25">
+      <c r="A13" t="s">
+        <v>36</v>
+      </c>
+      <c r="B13" t="s">
+        <v>96</v>
+      </c>
+      <c r="C13" t="s">
+        <v>148</v>
+      </c>
+      <c r="D13" t="s">
+        <v>156</v>
+      </c>
+      <c r="F13">
+        <v>1</v>
+      </c>
+      <c r="G13" t="s">
         <v>171</v>
-      </c>
-      <c r="S12">
-        <v>1337.123213</v>
-      </c>
-      <c r="T12">
-        <v>0</v>
-      </c>
-      <c r="U12">
-        <v>0</v>
-      </c>
-      <c r="V12">
-        <v>0</v>
-      </c>
-      <c r="W12">
-        <v>1337.123213</v>
-      </c>
-      <c r="X12">
-        <v>0</v>
-      </c>
-      <c r="Y12">
-        <v>0</v>
-      </c>
-      <c r="Z12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:26">
-      <c r="A13" t="s">
-        <v>37</v>
-      </c>
-      <c r="B13" t="s">
-        <v>97</v>
-      </c>
-      <c r="C13" t="s">
-        <v>149</v>
-      </c>
-      <c r="D13" t="s">
-        <v>157</v>
-      </c>
-      <c r="F13">
-        <v>1</v>
-      </c>
-      <c r="G13" t="s">
-        <v>172</v>
       </c>
       <c r="H13">
         <v>54</v>
       </c>
       <c r="I13" t="s">
+        <v>36</v>
+      </c>
+      <c r="J13" t="s">
+        <v>222</v>
+      </c>
+      <c r="K13" t="s">
+        <v>239</v>
+      </c>
+      <c r="L13" t="s">
+        <v>156</v>
+      </c>
+      <c r="M13" t="s">
+        <v>148</v>
+      </c>
+      <c r="N13" t="s">
+        <v>257</v>
+      </c>
+      <c r="O13" t="s">
+        <v>269</v>
+      </c>
+      <c r="P13" t="s">
+        <v>325</v>
+      </c>
+      <c r="Q13">
+        <v>2</v>
+      </c>
+      <c r="R13" t="s">
+        <v>171</v>
+      </c>
+      <c r="S13">
+        <v>70.9364375</v>
+      </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
+      <c r="U13">
+        <v>0</v>
+      </c>
+      <c r="V13">
+        <v>70.9364375</v>
+      </c>
+      <c r="W13">
+        <v>0</v>
+      </c>
+      <c r="X13">
+        <v>0</v>
+      </c>
+      <c r="Y13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25">
+      <c r="A14" t="s">
         <v>37</v>
       </c>
-      <c r="J13" t="s">
-        <v>227</v>
-      </c>
-      <c r="K13" t="s">
-        <v>245</v>
-      </c>
-      <c r="L13" t="s">
-        <v>157</v>
-      </c>
-      <c r="M13" t="s">
-        <v>149</v>
-      </c>
-      <c r="N13" t="s">
-        <v>260</v>
-      </c>
-      <c r="O13" t="s">
-        <v>272</v>
-      </c>
-      <c r="P13" t="s">
-        <v>326</v>
-      </c>
-      <c r="Q13">
-        <v>1</v>
-      </c>
-      <c r="R13" t="s">
-        <v>172</v>
-      </c>
-      <c r="S13">
-        <v>50.0962255</v>
-      </c>
-      <c r="T13">
-        <v>0</v>
-      </c>
-      <c r="U13">
-        <v>0</v>
-      </c>
-      <c r="V13">
-        <v>0</v>
-      </c>
-      <c r="W13">
-        <v>50.0962255</v>
-      </c>
-      <c r="X13">
-        <v>0</v>
-      </c>
-      <c r="Y13">
-        <v>0</v>
-      </c>
-      <c r="Z13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:26">
-      <c r="A14" t="s">
-        <v>38</v>
-      </c>
       <c r="B14" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C14" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D14" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E14">
         <v>10.8</v>
@@ -2358,24 +2328,75 @@
         <v>2</v>
       </c>
       <c r="G14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H14">
         <v>300</v>
       </c>
-    </row>
-    <row r="15" spans="1:26">
+      <c r="I14" t="s">
+        <v>37</v>
+      </c>
+      <c r="J14" t="s">
+        <v>222</v>
+      </c>
+      <c r="K14" t="s">
+        <v>239</v>
+      </c>
+      <c r="L14" t="s">
+        <v>33</v>
+      </c>
+      <c r="M14" t="s">
+        <v>148</v>
+      </c>
+      <c r="N14" t="s">
+        <v>257</v>
+      </c>
+      <c r="O14" t="s">
+        <v>270</v>
+      </c>
+      <c r="P14" t="s">
+        <v>326</v>
+      </c>
+      <c r="Q14">
+        <v>2</v>
+      </c>
+      <c r="R14" t="s">
+        <v>172</v>
+      </c>
+      <c r="S14">
+        <v>303.3064565</v>
+      </c>
+      <c r="T14">
+        <v>0</v>
+      </c>
+      <c r="U14">
+        <v>0</v>
+      </c>
+      <c r="V14">
+        <v>303.3064565</v>
+      </c>
+      <c r="W14">
+        <v>0</v>
+      </c>
+      <c r="X14">
+        <v>0</v>
+      </c>
+      <c r="Y14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25">
       <c r="A15" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B15" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C15" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D15" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E15">
         <v>10.1</v>
@@ -2384,31 +2405,31 @@
         <v>1</v>
       </c>
       <c r="G15" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H15">
         <v>12</v>
       </c>
       <c r="I15" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J15" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="K15" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="L15" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M15" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="N15" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="O15" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="P15" t="s">
         <v>327</v>
@@ -2417,81 +2438,78 @@
         <v>1</v>
       </c>
       <c r="R15" t="s">
+        <v>173</v>
+      </c>
+      <c r="S15">
+        <v>22.2219625</v>
+      </c>
+      <c r="T15">
+        <v>0</v>
+      </c>
+      <c r="U15">
+        <v>0</v>
+      </c>
+      <c r="V15">
+        <v>22.2219625</v>
+      </c>
+      <c r="W15">
+        <v>0</v>
+      </c>
+      <c r="X15">
+        <v>0</v>
+      </c>
+      <c r="Y15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25">
+      <c r="A16" t="s">
+        <v>39</v>
+      </c>
+      <c r="B16" t="s">
+        <v>99</v>
+      </c>
+      <c r="C16" t="s">
+        <v>148</v>
+      </c>
+      <c r="D16" t="s">
+        <v>33</v>
+      </c>
+      <c r="G16" t="s">
         <v>174</v>
       </c>
-      <c r="S15">
-        <v>33.07528</v>
-      </c>
-      <c r="T15">
-        <v>0</v>
-      </c>
-      <c r="U15">
-        <v>0</v>
-      </c>
-      <c r="V15">
-        <v>0</v>
-      </c>
-      <c r="W15">
-        <v>33.07528</v>
-      </c>
-      <c r="X15">
-        <v>0</v>
-      </c>
-      <c r="Y15">
-        <v>0</v>
-      </c>
-      <c r="Z15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:26">
-      <c r="A16" t="s">
-        <v>40</v>
-      </c>
-      <c r="B16" t="s">
-        <v>100</v>
-      </c>
-      <c r="C16" t="s">
-        <v>149</v>
-      </c>
-      <c r="D16" t="s">
-        <v>34</v>
-      </c>
-      <c r="G16" t="s">
-        <v>175</v>
-      </c>
       <c r="I16" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J16" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="K16" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="L16" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M16" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="N16" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="O16" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="P16" t="s">
         <v>328</v>
       </c>
       <c r="Q16">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R16" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="S16">
-        <v>1221.6942635</v>
+        <v>2127.2856325</v>
       </c>
       <c r="T16">
         <v>0</v>
@@ -2500,10 +2518,10 @@
         <v>0</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>2127.2856325</v>
       </c>
       <c r="W16">
-        <v>1221.6942635</v>
+        <v>0</v>
       </c>
       <c r="X16">
         <v>0</v>
@@ -2511,49 +2529,46 @@
       <c r="Y16">
         <v>0</v>
       </c>
-      <c r="Z16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:26">
+    </row>
+    <row r="17" spans="1:25">
       <c r="A17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B17" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C17" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D17" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E17">
         <v>10.1</v>
       </c>
       <c r="G17" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J17" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="K17" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="L17" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M17" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="N17" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="O17" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="P17" t="s">
         <v>329</v>
@@ -2562,10 +2577,10 @@
         <v>1</v>
       </c>
       <c r="R17" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="S17">
-        <v>14.2677885</v>
+        <v>14.752124</v>
       </c>
       <c r="T17">
         <v>0</v>
@@ -2574,10 +2589,10 @@
         <v>0</v>
       </c>
       <c r="V17">
-        <v>0</v>
+        <v>14.752124</v>
       </c>
       <c r="W17">
-        <v>14.2677885</v>
+        <v>0</v>
       </c>
       <c r="X17">
         <v>0</v>
@@ -2585,61 +2600,58 @@
       <c r="Y17">
         <v>0</v>
       </c>
-      <c r="Z17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:26">
+    </row>
+    <row r="18" spans="1:25">
       <c r="A18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B18" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C18" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D18" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E18">
         <v>10.1</v>
       </c>
       <c r="G18" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J18" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="K18" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="L18" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M18" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="N18" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="O18" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="P18" t="s">
         <v>330</v>
       </c>
       <c r="Q18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R18" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="S18">
-        <v>23.4187135</v>
+        <v>13.0044945</v>
       </c>
       <c r="T18">
         <v>0</v>
@@ -2648,10 +2660,10 @@
         <v>0</v>
       </c>
       <c r="V18">
-        <v>0</v>
+        <v>13.0044945</v>
       </c>
       <c r="W18">
-        <v>23.4187135</v>
+        <v>0</v>
       </c>
       <c r="X18">
         <v>0</v>
@@ -2659,22 +2671,19 @@
       <c r="Y18">
         <v>0</v>
       </c>
-      <c r="Z18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:26">
+    </row>
+    <row r="19" spans="1:25">
       <c r="A19" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B19" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C19" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D19" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E19">
         <v>1.2</v>
@@ -2683,31 +2692,31 @@
         <v>1</v>
       </c>
       <c r="G19" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H19">
         <v>72</v>
       </c>
       <c r="I19" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J19" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="K19" t="s">
         <v>245</v>
       </c>
       <c r="L19" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="M19" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="N19" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="O19" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="P19" t="s">
         <v>331</v>
@@ -2716,10 +2725,10 @@
         <v>1</v>
       </c>
       <c r="R19" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="S19">
-        <v>71.92272699999999</v>
+        <v>67.747111</v>
       </c>
       <c r="T19">
         <v>0</v>
@@ -2731,30 +2740,27 @@
         <v>0</v>
       </c>
       <c r="W19">
-        <v>71.92272699999999</v>
+        <v>0</v>
       </c>
       <c r="X19">
-        <v>0</v>
+        <v>67.747111</v>
       </c>
       <c r="Y19">
         <v>0</v>
       </c>
-      <c r="Z19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:26">
+    </row>
+    <row r="20" spans="1:25">
       <c r="A20" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B20" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C20" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D20" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E20">
         <v>1.2</v>
@@ -2763,31 +2769,31 @@
         <v>1</v>
       </c>
       <c r="G20" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H20">
         <v>54</v>
       </c>
       <c r="I20" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J20" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="K20" t="s">
         <v>245</v>
       </c>
       <c r="L20" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="M20" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="N20" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="O20" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="P20" t="s">
         <v>332</v>
@@ -2796,10 +2802,10 @@
         <v>1</v>
       </c>
       <c r="R20" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="S20">
-        <v>53.493458</v>
+        <v>67.74146949999999</v>
       </c>
       <c r="T20">
         <v>0</v>
@@ -2811,30 +2817,27 @@
         <v>0</v>
       </c>
       <c r="W20">
-        <v>53.493458</v>
+        <v>0</v>
       </c>
       <c r="X20">
-        <v>0</v>
+        <v>67.74146949999999</v>
       </c>
       <c r="Y20">
         <v>0</v>
       </c>
-      <c r="Z20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:26">
+    </row>
+    <row r="21" spans="1:25">
       <c r="A21" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B21" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C21" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D21" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E21">
         <v>2.1</v>
@@ -2843,31 +2846,31 @@
         <v>1</v>
       </c>
       <c r="G21" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H21">
         <v>18</v>
       </c>
       <c r="I21" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J21" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="K21" t="s">
         <v>245</v>
       </c>
       <c r="L21" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="M21" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="N21" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="O21" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="P21" t="s">
         <v>333</v>
@@ -2876,10 +2879,10 @@
         <v>1</v>
       </c>
       <c r="R21" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="S21">
-        <v>19.139096</v>
+        <v>17.700787</v>
       </c>
       <c r="T21">
         <v>0</v>
@@ -2891,30 +2894,27 @@
         <v>0</v>
       </c>
       <c r="W21">
-        <v>19.139096</v>
+        <v>0</v>
       </c>
       <c r="X21">
-        <v>0</v>
+        <v>17.700787</v>
       </c>
       <c r="Y21">
         <v>0</v>
       </c>
-      <c r="Z21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:26">
+    </row>
+    <row r="22" spans="1:25">
       <c r="A22" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B22" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C22" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D22" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E22">
         <v>3.8</v>
@@ -2923,31 +2923,31 @@
         <v>1</v>
       </c>
       <c r="G22" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H22">
         <v>55</v>
       </c>
       <c r="I22" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J22" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="K22" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="L22" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="M22" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="N22" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="O22" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="P22" t="s">
         <v>334</v>
@@ -2956,10 +2956,10 @@
         <v>1</v>
       </c>
       <c r="R22" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="S22">
-        <v>41.523624</v>
+        <v>54.279845</v>
       </c>
       <c r="T22">
         <v>0</v>
@@ -2968,10 +2968,10 @@
         <v>0</v>
       </c>
       <c r="V22">
-        <v>0</v>
+        <v>54.279845</v>
       </c>
       <c r="W22">
-        <v>41.523624</v>
+        <v>0</v>
       </c>
       <c r="X22">
         <v>0</v>
@@ -2979,22 +2979,19 @@
       <c r="Y22">
         <v>0</v>
       </c>
-      <c r="Z22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:26">
+    </row>
+    <row r="23" spans="1:25">
       <c r="A23" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B23" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C23" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D23" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E23">
         <v>4.4</v>
@@ -3003,31 +3000,31 @@
         <v>1</v>
       </c>
       <c r="G23" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H23">
         <v>7</v>
       </c>
       <c r="I23" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J23" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="K23" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="L23" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="M23" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="N23" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="O23" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="P23" t="s">
         <v>335</v>
@@ -3036,10 +3033,10 @@
         <v>1</v>
       </c>
       <c r="R23" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="S23">
-        <v>9.140447999999999</v>
+        <v>6.767903</v>
       </c>
       <c r="T23">
         <v>0</v>
@@ -3048,10 +3045,10 @@
         <v>0</v>
       </c>
       <c r="V23">
-        <v>0</v>
+        <v>6.767903</v>
       </c>
       <c r="W23">
-        <v>9.140447999999999</v>
+        <v>0</v>
       </c>
       <c r="X23">
         <v>0</v>
@@ -3059,22 +3056,19 @@
       <c r="Y23">
         <v>0</v>
       </c>
-      <c r="Z23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:26">
+    </row>
+    <row r="24" spans="1:25">
       <c r="A24" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B24" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C24" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D24" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E24">
         <v>4.4</v>
@@ -3083,43 +3077,43 @@
         <v>1</v>
       </c>
       <c r="G24" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H24">
         <v>4</v>
       </c>
       <c r="I24" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J24" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="K24" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="L24" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="M24" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="N24" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="O24" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="P24" t="s">
         <v>336</v>
       </c>
       <c r="Q24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R24" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="S24">
-        <v>26.744253</v>
+        <v>2.70678</v>
       </c>
       <c r="T24">
         <v>0</v>
@@ -3128,10 +3122,10 @@
         <v>0</v>
       </c>
       <c r="V24">
-        <v>0</v>
+        <v>2.70678</v>
       </c>
       <c r="W24">
-        <v>26.744253</v>
+        <v>0</v>
       </c>
       <c r="X24">
         <v>0</v>
@@ -3139,22 +3133,19 @@
       <c r="Y24">
         <v>0</v>
       </c>
-      <c r="Z24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:26">
+    </row>
+    <row r="25" spans="1:25">
       <c r="A25" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B25" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C25" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D25" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E25">
         <v>4.3</v>
@@ -3163,31 +3154,31 @@
         <v>1</v>
       </c>
       <c r="G25" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H25">
         <v>7</v>
       </c>
       <c r="I25" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J25" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="K25" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="L25" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="M25" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="N25" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="O25" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="P25" t="s">
         <v>337</v>
@@ -3196,10 +3187,10 @@
         <v>1</v>
       </c>
       <c r="R25" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="S25">
-        <v>5.483798</v>
+        <v>6.767903</v>
       </c>
       <c r="T25">
         <v>0</v>
@@ -3208,10 +3199,10 @@
         <v>0</v>
       </c>
       <c r="V25">
-        <v>0</v>
+        <v>6.767903</v>
       </c>
       <c r="W25">
-        <v>5.483798</v>
+        <v>0</v>
       </c>
       <c r="X25">
         <v>0</v>
@@ -3219,22 +3210,19 @@
       <c r="Y25">
         <v>0</v>
       </c>
-      <c r="Z25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:26">
+    </row>
+    <row r="26" spans="1:25">
       <c r="A26" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B26" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C26" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D26" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E26">
         <v>1.5</v>
@@ -3243,31 +3231,31 @@
         <v>1</v>
       </c>
       <c r="G26" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H26">
         <v>72</v>
       </c>
       <c r="I26" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J26" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="K26" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="L26" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="M26" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="N26" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="O26" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="P26" t="s">
         <v>338</v>
@@ -3276,10 +3264,10 @@
         <v>1</v>
       </c>
       <c r="R26" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="S26">
-        <v>94.66367</v>
+        <v>69.685627</v>
       </c>
       <c r="T26">
         <v>0</v>
@@ -3288,10 +3276,10 @@
         <v>0</v>
       </c>
       <c r="V26">
-        <v>0</v>
+        <v>69.685627</v>
       </c>
       <c r="W26">
-        <v>94.66367</v>
+        <v>0</v>
       </c>
       <c r="X26">
         <v>0</v>
@@ -3299,22 +3287,19 @@
       <c r="Y26">
         <v>0</v>
       </c>
-      <c r="Z26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:26">
+    </row>
+    <row r="27" spans="1:25">
       <c r="A27" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B27" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C27" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D27" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E27">
         <v>7.1</v>
@@ -3323,78 +3308,24 @@
         <v>1</v>
       </c>
       <c r="G27" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H27">
         <v>1</v>
       </c>
-      <c r="I27" t="s">
+    </row>
+    <row r="28" spans="1:25">
+      <c r="A28" t="s">
         <v>51</v>
       </c>
-      <c r="J27" t="s">
-        <v>227</v>
-      </c>
-      <c r="K27" t="s">
-        <v>245</v>
-      </c>
-      <c r="L27" t="s">
-        <v>159</v>
-      </c>
-      <c r="M27" t="s">
-        <v>150</v>
-      </c>
-      <c r="N27" t="s">
-        <v>259</v>
-      </c>
-      <c r="O27" t="s">
-        <v>285</v>
-      </c>
-      <c r="P27" t="s">
-        <v>339</v>
-      </c>
-      <c r="Q27">
-        <v>1</v>
-      </c>
-      <c r="R27" t="s">
-        <v>186</v>
-      </c>
-      <c r="S27">
-        <v>1.0004045</v>
-      </c>
-      <c r="T27">
-        <v>0</v>
-      </c>
-      <c r="U27">
-        <v>0</v>
-      </c>
-      <c r="V27">
-        <v>0</v>
-      </c>
-      <c r="W27">
-        <v>1.0004045</v>
-      </c>
-      <c r="X27">
-        <v>0</v>
-      </c>
-      <c r="Y27">
-        <v>0</v>
-      </c>
-      <c r="Z27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:26">
-      <c r="A28" t="s">
-        <v>52</v>
-      </c>
       <c r="B28" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C28" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D28" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E28">
         <v>7.2</v>
@@ -3403,43 +3334,43 @@
         <v>1</v>
       </c>
       <c r="G28" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H28">
         <v>108</v>
       </c>
       <c r="I28" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J28" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="K28" t="s">
         <v>245</v>
       </c>
       <c r="L28" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="M28" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="N28" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="O28" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="P28" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="Q28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R28" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="S28">
-        <v>107.9399345</v>
+        <v>109.7670735</v>
       </c>
       <c r="T28">
         <v>0</v>
@@ -3451,30 +3382,27 @@
         <v>0</v>
       </c>
       <c r="W28">
-        <v>107.9399345</v>
+        <v>0</v>
       </c>
       <c r="X28">
-        <v>0</v>
+        <v>109.7670735</v>
       </c>
       <c r="Y28">
         <v>0</v>
       </c>
-      <c r="Z28">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:26">
+    </row>
+    <row r="29" spans="1:25">
       <c r="A29" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B29" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C29" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D29" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E29">
         <v>7.1</v>
@@ -3483,78 +3411,24 @@
         <v>1</v>
       </c>
       <c r="G29" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H29">
         <v>2.5</v>
       </c>
-      <c r="I29" t="s">
+    </row>
+    <row r="30" spans="1:25">
+      <c r="A30" t="s">
         <v>53</v>
       </c>
-      <c r="J29" t="s">
-        <v>227</v>
-      </c>
-      <c r="K29" t="s">
-        <v>245</v>
-      </c>
-      <c r="L29" t="s">
-        <v>159</v>
-      </c>
-      <c r="M29" t="s">
-        <v>150</v>
-      </c>
-      <c r="N29" t="s">
-        <v>259</v>
-      </c>
-      <c r="O29" t="s">
-        <v>287</v>
-      </c>
-      <c r="P29" t="s">
-        <v>341</v>
-      </c>
-      <c r="Q29">
-        <v>1</v>
-      </c>
-      <c r="R29" t="s">
-        <v>188</v>
-      </c>
-      <c r="S29">
-        <v>2.937966</v>
-      </c>
-      <c r="T29">
-        <v>0</v>
-      </c>
-      <c r="U29">
-        <v>0</v>
-      </c>
-      <c r="V29">
-        <v>0</v>
-      </c>
-      <c r="W29">
-        <v>2.937966</v>
-      </c>
-      <c r="X29">
-        <v>0</v>
-      </c>
-      <c r="Y29">
-        <v>0</v>
-      </c>
-      <c r="Z29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:26">
-      <c r="A30" t="s">
-        <v>54</v>
-      </c>
       <c r="B30" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C30" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D30" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E30">
         <v>7.1</v>
@@ -3563,78 +3437,24 @@
         <v>1</v>
       </c>
       <c r="G30" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H30">
         <v>2.5</v>
       </c>
-      <c r="I30" t="s">
+    </row>
+    <row r="31" spans="1:25">
+      <c r="A31" t="s">
         <v>54</v>
       </c>
-      <c r="J30" t="s">
-        <v>227</v>
-      </c>
-      <c r="K30" t="s">
-        <v>245</v>
-      </c>
-      <c r="L30" t="s">
-        <v>159</v>
-      </c>
-      <c r="M30" t="s">
-        <v>150</v>
-      </c>
-      <c r="N30" t="s">
-        <v>259</v>
-      </c>
-      <c r="O30" t="s">
-        <v>288</v>
-      </c>
-      <c r="P30" t="s">
-        <v>342</v>
-      </c>
-      <c r="Q30">
-        <v>1</v>
-      </c>
-      <c r="R30" t="s">
-        <v>189</v>
-      </c>
-      <c r="S30">
-        <v>3.351134</v>
-      </c>
-      <c r="T30">
-        <v>0</v>
-      </c>
-      <c r="U30">
-        <v>0</v>
-      </c>
-      <c r="V30">
-        <v>0</v>
-      </c>
-      <c r="W30">
-        <v>3.351134</v>
-      </c>
-      <c r="X30">
-        <v>0</v>
-      </c>
-      <c r="Y30">
-        <v>0</v>
-      </c>
-      <c r="Z30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:26">
-      <c r="A31" t="s">
-        <v>55</v>
-      </c>
       <c r="B31" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C31" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D31" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E31">
         <v>7.1</v>
@@ -3643,24 +3463,24 @@
         <v>1</v>
       </c>
       <c r="G31" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H31">
         <v>2.5</v>
       </c>
     </row>
-    <row r="32" spans="1:26">
+    <row r="32" spans="1:25">
       <c r="A32" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B32" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C32" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D32" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E32">
         <v>7.1</v>
@@ -3669,24 +3489,24 @@
         <v>1</v>
       </c>
       <c r="G32" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H32">
         <v>2.5</v>
       </c>
     </row>
-    <row r="33" spans="1:26">
+    <row r="33" spans="1:25">
       <c r="A33" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B33" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C33" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D33" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E33">
         <v>7.1</v>
@@ -3695,78 +3515,75 @@
         <v>1</v>
       </c>
       <c r="G33" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H33">
         <v>3</v>
       </c>
       <c r="I33" t="s">
+        <v>56</v>
+      </c>
+      <c r="J33" t="s">
+        <v>229</v>
+      </c>
+      <c r="K33" t="s">
+        <v>246</v>
+      </c>
+      <c r="L33" t="s">
+        <v>158</v>
+      </c>
+      <c r="M33" t="s">
+        <v>149</v>
+      </c>
+      <c r="N33" t="s">
+        <v>256</v>
+      </c>
+      <c r="O33" t="s">
+        <v>284</v>
+      </c>
+      <c r="P33" t="s">
+        <v>340</v>
+      </c>
+      <c r="Q33">
+        <v>2</v>
+      </c>
+      <c r="R33" t="s">
+        <v>191</v>
+      </c>
+      <c r="S33">
+        <v>9.900791999999999</v>
+      </c>
+      <c r="T33">
+        <v>0</v>
+      </c>
+      <c r="U33">
+        <v>0</v>
+      </c>
+      <c r="V33">
+        <v>4.950396</v>
+      </c>
+      <c r="W33">
+        <v>0</v>
+      </c>
+      <c r="X33">
+        <v>4.950396</v>
+      </c>
+      <c r="Y33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:25">
+      <c r="A34" t="s">
         <v>57</v>
       </c>
-      <c r="J33" t="s">
-        <v>227</v>
-      </c>
-      <c r="K33" t="s">
-        <v>245</v>
-      </c>
-      <c r="L33" t="s">
+      <c r="B34" t="s">
+        <v>117</v>
+      </c>
+      <c r="C34" t="s">
+        <v>150</v>
+      </c>
+      <c r="D34" t="s">
         <v>159</v>
-      </c>
-      <c r="M33" t="s">
-        <v>150</v>
-      </c>
-      <c r="N33" t="s">
-        <v>259</v>
-      </c>
-      <c r="O33" t="s">
-        <v>289</v>
-      </c>
-      <c r="P33" t="s">
-        <v>343</v>
-      </c>
-      <c r="Q33">
-        <v>1</v>
-      </c>
-      <c r="R33" t="s">
-        <v>192</v>
-      </c>
-      <c r="S33">
-        <v>4.265736</v>
-      </c>
-      <c r="T33">
-        <v>0</v>
-      </c>
-      <c r="U33">
-        <v>0</v>
-      </c>
-      <c r="V33">
-        <v>0</v>
-      </c>
-      <c r="W33">
-        <v>4.265736</v>
-      </c>
-      <c r="X33">
-        <v>0</v>
-      </c>
-      <c r="Y33">
-        <v>0</v>
-      </c>
-      <c r="Z33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:26">
-      <c r="A34" t="s">
-        <v>58</v>
-      </c>
-      <c r="B34" t="s">
-        <v>118</v>
-      </c>
-      <c r="C34" t="s">
-        <v>151</v>
-      </c>
-      <c r="D34" t="s">
-        <v>160</v>
       </c>
       <c r="E34">
         <v>8.300000000000001</v>
@@ -3775,78 +3592,75 @@
         <v>1</v>
       </c>
       <c r="G34" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H34">
         <v>25</v>
       </c>
       <c r="I34" t="s">
+        <v>57</v>
+      </c>
+      <c r="J34" t="s">
+        <v>226</v>
+      </c>
+      <c r="K34" t="s">
+        <v>243</v>
+      </c>
+      <c r="L34" t="s">
+        <v>159</v>
+      </c>
+      <c r="M34" t="s">
+        <v>150</v>
+      </c>
+      <c r="N34" t="s">
+        <v>256</v>
+      </c>
+      <c r="O34" t="s">
+        <v>285</v>
+      </c>
+      <c r="P34" t="s">
+        <v>341</v>
+      </c>
+      <c r="Q34">
+        <v>1</v>
+      </c>
+      <c r="R34" t="s">
+        <v>192</v>
+      </c>
+      <c r="S34">
+        <v>23.101259</v>
+      </c>
+      <c r="T34">
+        <v>0</v>
+      </c>
+      <c r="U34">
+        <v>0</v>
+      </c>
+      <c r="V34">
+        <v>0</v>
+      </c>
+      <c r="W34">
+        <v>0</v>
+      </c>
+      <c r="X34">
+        <v>0</v>
+      </c>
+      <c r="Y34">
+        <v>23.101259</v>
+      </c>
+    </row>
+    <row r="35" spans="1:25">
+      <c r="A35" t="s">
         <v>58</v>
       </c>
-      <c r="J34" t="s">
-        <v>229</v>
-      </c>
-      <c r="K34" t="s">
-        <v>247</v>
-      </c>
-      <c r="L34" t="s">
-        <v>160</v>
-      </c>
-      <c r="M34" t="s">
-        <v>151</v>
-      </c>
-      <c r="N34" t="s">
-        <v>259</v>
-      </c>
-      <c r="O34" t="s">
-        <v>290</v>
-      </c>
-      <c r="P34" t="s">
-        <v>344</v>
-      </c>
-      <c r="Q34">
-        <v>1</v>
-      </c>
-      <c r="R34" t="s">
-        <v>193</v>
-      </c>
-      <c r="S34">
-        <v>20.9008205</v>
-      </c>
-      <c r="T34">
-        <v>0</v>
-      </c>
-      <c r="U34">
-        <v>0</v>
-      </c>
-      <c r="V34">
-        <v>20.9008205</v>
-      </c>
-      <c r="W34">
-        <v>0</v>
-      </c>
-      <c r="X34">
-        <v>0</v>
-      </c>
-      <c r="Y34">
-        <v>0</v>
-      </c>
-      <c r="Z34">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:26">
-      <c r="A35" t="s">
-        <v>59</v>
-      </c>
       <c r="B35" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C35" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D35" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E35">
         <v>8.5</v>
@@ -3855,78 +3669,75 @@
         <v>2</v>
       </c>
       <c r="G35" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H35">
         <v>90</v>
       </c>
       <c r="I35" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="J35" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="K35" t="s">
         <v>247</v>
       </c>
       <c r="L35" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M35" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="N35" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="O35" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="P35" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="Q35">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R35" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="S35">
-        <v>69.464913</v>
+        <v>95.4517385</v>
       </c>
       <c r="T35">
         <v>0</v>
       </c>
       <c r="U35">
-        <v>0</v>
+        <v>21.903017</v>
       </c>
       <c r="V35">
-        <v>69.464913</v>
+        <v>0</v>
       </c>
       <c r="W35">
-        <v>0</v>
+        <v>54.9468675</v>
       </c>
       <c r="X35">
         <v>0</v>
       </c>
       <c r="Y35">
-        <v>0</v>
-      </c>
-      <c r="Z35">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:26">
+        <v>18.601854</v>
+      </c>
+    </row>
+    <row r="36" spans="1:25">
       <c r="A36" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B36" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C36" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D36" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E36">
         <v>8.1</v>
@@ -3935,55 +3746,55 @@
         <v>1</v>
       </c>
       <c r="G36" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H36">
         <v>150</v>
       </c>
       <c r="I36" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="J36" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K36" t="s">
         <v>248</v>
       </c>
       <c r="L36" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M36" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="N36" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="O36" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="P36" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="Q36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R36" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="S36">
-        <v>164.742147</v>
+        <v>150.7393595</v>
       </c>
       <c r="T36">
-        <v>82.37107349999999</v>
+        <v>0</v>
       </c>
       <c r="U36">
         <v>0</v>
       </c>
       <c r="V36">
-        <v>82.37107349999999</v>
+        <v>0</v>
       </c>
       <c r="W36">
-        <v>0</v>
+        <v>150.7393595</v>
       </c>
       <c r="X36">
         <v>0</v>
@@ -3991,22 +3802,19 @@
       <c r="Y36">
         <v>0</v>
       </c>
-      <c r="Z36">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:26">
+    </row>
+    <row r="37" spans="1:25">
       <c r="A37" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B37" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C37" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D37" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E37">
         <v>8.300000000000001</v>
@@ -4015,141 +3823,237 @@
         <v>1</v>
       </c>
       <c r="G37" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H37">
         <v>40</v>
       </c>
-    </row>
-    <row r="38" spans="1:26">
+      <c r="I37" t="s">
+        <v>60</v>
+      </c>
+      <c r="J37" t="s">
+        <v>232</v>
+      </c>
+      <c r="K37" t="s">
+        <v>249</v>
+      </c>
+      <c r="L37" t="s">
+        <v>159</v>
+      </c>
+      <c r="M37" t="s">
+        <v>150</v>
+      </c>
+      <c r="N37" t="s">
+        <v>256</v>
+      </c>
+      <c r="O37" t="s">
+        <v>288</v>
+      </c>
+      <c r="P37" t="s">
+        <v>344</v>
+      </c>
+      <c r="Q37">
+        <v>2</v>
+      </c>
+      <c r="R37" t="s">
+        <v>195</v>
+      </c>
+      <c r="S37">
+        <v>52.38678899999999</v>
+      </c>
+      <c r="T37">
+        <v>0</v>
+      </c>
+      <c r="U37">
+        <v>9.300903999999999</v>
+      </c>
+      <c r="V37">
+        <v>0</v>
+      </c>
+      <c r="W37">
+        <v>0</v>
+      </c>
+      <c r="X37">
+        <v>0</v>
+      </c>
+      <c r="Y37">
+        <v>43.085885</v>
+      </c>
+    </row>
+    <row r="38" spans="1:25">
       <c r="A38" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B38" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C38" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D38" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F38">
         <v>1</v>
       </c>
       <c r="G38" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="H38">
         <v>0</v>
       </c>
-    </row>
-    <row r="39" spans="1:26">
+      <c r="I38" t="s">
+        <v>61</v>
+      </c>
+      <c r="J38" t="s">
+        <v>233</v>
+      </c>
+      <c r="K38" t="s">
+        <v>250</v>
+      </c>
+      <c r="L38" t="s">
+        <v>159</v>
+      </c>
+      <c r="M38" t="s">
+        <v>150</v>
+      </c>
+      <c r="N38" t="s">
+        <v>256</v>
+      </c>
+      <c r="O38" t="s">
+        <v>289</v>
+      </c>
+      <c r="P38" t="s">
+        <v>345</v>
+      </c>
+      <c r="Q38">
+        <v>6</v>
+      </c>
+      <c r="R38" t="s">
+        <v>196</v>
+      </c>
+      <c r="S38">
+        <v>10.799496</v>
+      </c>
+      <c r="T38">
+        <v>1.799916</v>
+      </c>
+      <c r="U38">
+        <v>1.799916</v>
+      </c>
+      <c r="V38">
+        <v>1.799916</v>
+      </c>
+      <c r="W38">
+        <v>1.799916</v>
+      </c>
+      <c r="X38">
+        <v>1.799916</v>
+      </c>
+      <c r="Y38">
+        <v>1.799916</v>
+      </c>
+    </row>
+    <row r="39" spans="1:25">
       <c r="J39" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="K39" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="N39" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="O39" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="P39" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="Q39">
         <v>8</v>
       </c>
       <c r="R39" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="S39">
-        <v>2181.369833</v>
+        <v>5263.2228385</v>
       </c>
       <c r="T39">
-        <v>284.876903</v>
+        <v>668.711952</v>
       </c>
       <c r="U39">
-        <v>284.8295915</v>
+        <v>668.729957</v>
       </c>
       <c r="V39">
-        <v>284.8295915</v>
+        <v>1079.216896</v>
       </c>
       <c r="W39">
-        <v>880.652547</v>
+        <v>1088.901692</v>
       </c>
       <c r="X39">
-        <v>186.689211</v>
+        <v>1088.9323845</v>
       </c>
       <c r="Y39">
-        <v>187.699108</v>
-      </c>
-      <c r="Z39">
-        <v>71.79288099999999</v>
-      </c>
-    </row>
-    <row r="40" spans="1:26">
+        <v>668.729957</v>
+      </c>
+    </row>
+    <row r="40" spans="1:25">
       <c r="J40" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="K40" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="N40" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="O40" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="P40" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="Q40">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="R40" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="S40">
-        <v>3374.428398</v>
+        <v>8889.786702999998</v>
       </c>
       <c r="T40">
-        <v>569.7538060000001</v>
+        <v>1358.810224</v>
       </c>
       <c r="U40">
-        <v>562.9398815</v>
+        <v>1169.7603525</v>
       </c>
       <c r="V40">
-        <v>291.660685</v>
+        <v>2027.005781</v>
       </c>
       <c r="W40">
-        <v>1481.112364</v>
+        <v>1370.8139285</v>
       </c>
       <c r="X40">
-        <v>186.689211</v>
+        <v>1793.6360645</v>
       </c>
       <c r="Y40">
-        <v>187.699108</v>
-      </c>
-      <c r="Z40">
-        <v>94.5733425</v>
-      </c>
-    </row>
-    <row r="41" spans="1:26">
+        <v>1169.7603525</v>
+      </c>
+    </row>
+    <row r="41" spans="1:25">
       <c r="A41" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B41" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C41" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D41" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E41">
         <v>4.1</v>
@@ -4158,24 +4062,75 @@
         <v>1</v>
       </c>
       <c r="G41" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H41">
         <v>20</v>
       </c>
-    </row>
-    <row r="42" spans="1:26">
+      <c r="I41" t="s">
+        <v>62</v>
+      </c>
+      <c r="J41" t="s">
+        <v>222</v>
+      </c>
+      <c r="K41" t="s">
+        <v>239</v>
+      </c>
+      <c r="L41" t="s">
+        <v>158</v>
+      </c>
+      <c r="M41" t="s">
+        <v>151</v>
+      </c>
+      <c r="N41" t="s">
+        <v>256</v>
+      </c>
+      <c r="O41" t="s">
+        <v>292</v>
+      </c>
+      <c r="P41" t="s">
+        <v>348</v>
+      </c>
+      <c r="Q41">
+        <v>1</v>
+      </c>
+      <c r="R41" t="s">
+        <v>197</v>
+      </c>
+      <c r="S41">
+        <v>18.5514615</v>
+      </c>
+      <c r="T41">
+        <v>0</v>
+      </c>
+      <c r="U41">
+        <v>0</v>
+      </c>
+      <c r="V41">
+        <v>18.5514615</v>
+      </c>
+      <c r="W41">
+        <v>0</v>
+      </c>
+      <c r="X41">
+        <v>0</v>
+      </c>
+      <c r="Y41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:25">
       <c r="A42" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B42" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C42" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D42" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E42">
         <v>7.3</v>
@@ -4184,31 +4139,31 @@
         <v>1</v>
       </c>
       <c r="G42" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H42">
         <v>12</v>
       </c>
       <c r="I42" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J42" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="K42" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="L42" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="M42" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="N42" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="O42" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="P42" t="s">
         <v>349</v>
@@ -4217,10 +4172,10 @@
         <v>1</v>
       </c>
       <c r="R42" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="S42">
-        <v>12.083717</v>
+        <v>14.8354155</v>
       </c>
       <c r="T42">
         <v>0</v>
@@ -4229,10 +4184,10 @@
         <v>0</v>
       </c>
       <c r="V42">
-        <v>0</v>
+        <v>14.8354155</v>
       </c>
       <c r="W42">
-        <v>12.083717</v>
+        <v>0</v>
       </c>
       <c r="X42">
         <v>0</v>
@@ -4240,22 +4195,19 @@
       <c r="Y42">
         <v>0</v>
       </c>
-      <c r="Z42">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:26">
+    </row>
+    <row r="43" spans="1:25">
       <c r="A43" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B43" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C43" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D43" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E43">
         <v>7.2</v>
@@ -4264,31 +4216,31 @@
         <v>1</v>
       </c>
       <c r="G43" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H43">
         <v>12</v>
       </c>
       <c r="I43" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J43" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="K43" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="L43" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="M43" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="N43" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="O43" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="P43" t="s">
         <v>350</v>
@@ -4297,10 +4249,10 @@
         <v>1</v>
       </c>
       <c r="R43" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="S43">
-        <v>12.426955</v>
+        <v>9.300903999999999</v>
       </c>
       <c r="T43">
         <v>0</v>
@@ -4318,24 +4270,21 @@
         <v>0</v>
       </c>
       <c r="Y43">
-        <v>12.426955</v>
-      </c>
-      <c r="Z43">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:26">
+        <v>9.300903999999999</v>
+      </c>
+    </row>
+    <row r="44" spans="1:25">
       <c r="A44" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B44" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C44" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D44" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E44">
         <v>7.1</v>
@@ -4344,31 +4293,31 @@
         <v>1</v>
       </c>
       <c r="G44" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H44">
         <v>25</v>
       </c>
       <c r="I44" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="J44" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="K44" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="L44" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="M44" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="N44" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="O44" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="P44" t="s">
         <v>351</v>
@@ -4377,10 +4326,10 @@
         <v>1</v>
       </c>
       <c r="R44" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="S44">
-        <v>22.924388</v>
+        <v>21.903017</v>
       </c>
       <c r="T44">
         <v>0</v>
@@ -4389,7 +4338,7 @@
         <v>0</v>
       </c>
       <c r="V44">
-        <v>22.924388</v>
+        <v>0</v>
       </c>
       <c r="W44">
         <v>0</v>
@@ -4398,24 +4347,21 @@
         <v>0</v>
       </c>
       <c r="Y44">
-        <v>0</v>
-      </c>
-      <c r="Z44">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:26">
+        <v>21.903017</v>
+      </c>
+    </row>
+    <row r="45" spans="1:25">
       <c r="A45" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B45" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C45" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D45" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E45">
         <v>7.1</v>
@@ -4424,31 +4370,31 @@
         <v>3</v>
       </c>
       <c r="G45" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H45">
         <v>18</v>
       </c>
       <c r="I45" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J45" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K45" t="s">
         <v>251</v>
       </c>
       <c r="L45" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="M45" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="N45" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="O45" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="P45" t="s">
         <v>352</v>
@@ -4457,45 +4403,42 @@
         <v>2</v>
       </c>
       <c r="R45" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="S45">
-        <v>8.626246500000001</v>
+        <v>8.397899000000001</v>
       </c>
       <c r="T45">
         <v>0</v>
       </c>
       <c r="U45">
-        <v>4.625061</v>
+        <v>0</v>
       </c>
       <c r="V45">
-        <v>0</v>
+        <v>4.1989495</v>
       </c>
       <c r="W45">
-        <v>4.0011855</v>
+        <v>0</v>
       </c>
       <c r="X45">
-        <v>0</v>
+        <v>4.1989495</v>
       </c>
       <c r="Y45">
         <v>0</v>
       </c>
-      <c r="Z45">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:26">
+    </row>
+    <row r="46" spans="1:25">
       <c r="A46" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B46" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C46" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D46" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E46">
         <v>4.1</v>
@@ -4504,31 +4447,31 @@
         <v>1</v>
       </c>
       <c r="G46" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H46">
         <v>15</v>
       </c>
       <c r="I46" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J46" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="K46" t="s">
-        <v>252</v>
+        <v>239</v>
       </c>
       <c r="L46" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="M46" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="N46" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="O46" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="P46" t="s">
         <v>353</v>
@@ -4537,10 +4480,10 @@
         <v>1</v>
       </c>
       <c r="R46" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="S46">
-        <v>16.1315865</v>
+        <v>15.901342</v>
       </c>
       <c r="T46">
         <v>0</v>
@@ -4549,7 +4492,7 @@
         <v>0</v>
       </c>
       <c r="V46">
-        <v>0</v>
+        <v>15.901342</v>
       </c>
       <c r="W46">
         <v>0</v>
@@ -4560,22 +4503,19 @@
       <c r="Y46">
         <v>0</v>
       </c>
-      <c r="Z46">
-        <v>16.1315865</v>
-      </c>
-    </row>
-    <row r="47" spans="1:26">
+    </row>
+    <row r="47" spans="1:25">
       <c r="A47" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B47" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C47" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D47" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E47">
         <v>9.1</v>
@@ -4584,31 +4524,31 @@
         <v>1</v>
       </c>
       <c r="G47" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H47">
         <v>30</v>
       </c>
       <c r="I47" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J47" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="K47" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="L47" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="M47" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="N47" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="O47" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="P47" t="s">
         <v>354</v>
@@ -4617,10 +4557,10 @@
         <v>1</v>
       </c>
       <c r="R47" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="S47">
-        <v>39.962052</v>
+        <v>36.532104</v>
       </c>
       <c r="T47">
         <v>0</v>
@@ -4629,10 +4569,10 @@
         <v>0</v>
       </c>
       <c r="V47">
-        <v>0</v>
+        <v>36.532104</v>
       </c>
       <c r="W47">
-        <v>39.962052</v>
+        <v>0</v>
       </c>
       <c r="X47">
         <v>0</v>
@@ -4640,22 +4580,19 @@
       <c r="Y47">
         <v>0</v>
       </c>
-      <c r="Z47">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:26">
+    </row>
+    <row r="48" spans="1:25">
       <c r="A48" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B48" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C48" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D48" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E48">
         <v>7.2</v>
@@ -4664,31 +4601,31 @@
         <v>2</v>
       </c>
       <c r="G48" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H48">
         <v>32</v>
       </c>
       <c r="I48" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J48" t="s">
         <v>235</v>
       </c>
       <c r="K48" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="L48" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="M48" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="N48" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="O48" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="P48" t="s">
         <v>355</v>
@@ -4697,45 +4634,42 @@
         <v>2</v>
       </c>
       <c r="R48" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="S48">
-        <v>34.070832</v>
+        <v>32.402292</v>
       </c>
       <c r="T48">
-        <v>0</v>
+        <v>16.201146</v>
       </c>
       <c r="U48">
-        <v>17.789979</v>
+        <v>0</v>
       </c>
       <c r="V48">
         <v>0</v>
       </c>
       <c r="W48">
-        <v>0</v>
+        <v>16.201146</v>
       </c>
       <c r="X48">
         <v>0</v>
       </c>
       <c r="Y48">
-        <v>16.280853</v>
-      </c>
-      <c r="Z48">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:25">
       <c r="A49" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B49" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C49" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D49" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E49">
         <v>7.2</v>
@@ -4744,24 +4678,75 @@
         <v>4</v>
       </c>
       <c r="G49" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H49">
         <v>180</v>
       </c>
-    </row>
-    <row r="50" spans="1:26">
+      <c r="I49" t="s">
+        <v>70</v>
+      </c>
+      <c r="J49" t="s">
+        <v>236</v>
+      </c>
+      <c r="K49" t="s">
+        <v>253</v>
+      </c>
+      <c r="L49" t="s">
+        <v>158</v>
+      </c>
+      <c r="M49" t="s">
+        <v>152</v>
+      </c>
+      <c r="N49" t="s">
+        <v>256</v>
+      </c>
+      <c r="O49" t="s">
+        <v>300</v>
+      </c>
+      <c r="P49" t="s">
+        <v>356</v>
+      </c>
+      <c r="Q49">
+        <v>4</v>
+      </c>
+      <c r="R49" t="s">
+        <v>205</v>
+      </c>
+      <c r="S49">
+        <v>169.572424</v>
+      </c>
+      <c r="T49">
+        <v>0</v>
+      </c>
+      <c r="U49">
+        <v>84.78621200000001</v>
+      </c>
+      <c r="V49">
+        <v>0</v>
+      </c>
+      <c r="W49">
+        <v>0</v>
+      </c>
+      <c r="X49">
+        <v>84.78621200000001</v>
+      </c>
+      <c r="Y49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:25">
       <c r="A50" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B50" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C50" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D50" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E50">
         <v>2.1</v>
@@ -4770,78 +4755,75 @@
         <v>1</v>
       </c>
       <c r="G50" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H50">
         <v>12</v>
       </c>
       <c r="I50" t="s">
+        <v>71</v>
+      </c>
+      <c r="J50" t="s">
+        <v>222</v>
+      </c>
+      <c r="K50" t="s">
+        <v>239</v>
+      </c>
+      <c r="L50" t="s">
+        <v>157</v>
+      </c>
+      <c r="M50" t="s">
+        <v>152</v>
+      </c>
+      <c r="N50" t="s">
+        <v>256</v>
+      </c>
+      <c r="O50" t="s">
+        <v>301</v>
+      </c>
+      <c r="P50" t="s">
+        <v>357</v>
+      </c>
+      <c r="Q50">
+        <v>1</v>
+      </c>
+      <c r="R50" t="s">
+        <v>206</v>
+      </c>
+      <c r="S50">
+        <v>15.9015285</v>
+      </c>
+      <c r="T50">
+        <v>0</v>
+      </c>
+      <c r="U50">
+        <v>0</v>
+      </c>
+      <c r="V50">
+        <v>15.9015285</v>
+      </c>
+      <c r="W50">
+        <v>0</v>
+      </c>
+      <c r="X50">
+        <v>0</v>
+      </c>
+      <c r="Y50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:25">
+      <c r="A51" t="s">
         <v>72</v>
       </c>
-      <c r="J50" t="s">
-        <v>232</v>
-      </c>
-      <c r="K50" t="s">
-        <v>250</v>
-      </c>
-      <c r="L50" t="s">
+      <c r="B51" t="s">
+        <v>132</v>
+      </c>
+      <c r="C51" t="s">
+        <v>152</v>
+      </c>
+      <c r="D51" t="s">
         <v>158</v>
-      </c>
-      <c r="M50" t="s">
-        <v>153</v>
-      </c>
-      <c r="N50" t="s">
-        <v>259</v>
-      </c>
-      <c r="O50" t="s">
-        <v>302</v>
-      </c>
-      <c r="P50" t="s">
-        <v>356</v>
-      </c>
-      <c r="Q50">
-        <v>1</v>
-      </c>
-      <c r="R50" t="s">
-        <v>207</v>
-      </c>
-      <c r="S50">
-        <v>12.426955</v>
-      </c>
-      <c r="T50">
-        <v>0</v>
-      </c>
-      <c r="U50">
-        <v>0</v>
-      </c>
-      <c r="V50">
-        <v>0</v>
-      </c>
-      <c r="W50">
-        <v>0</v>
-      </c>
-      <c r="X50">
-        <v>0</v>
-      </c>
-      <c r="Y50">
-        <v>12.426955</v>
-      </c>
-      <c r="Z50">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:26">
-      <c r="A51" t="s">
-        <v>73</v>
-      </c>
-      <c r="B51" t="s">
-        <v>133</v>
-      </c>
-      <c r="C51" t="s">
-        <v>153</v>
-      </c>
-      <c r="D51" t="s">
-        <v>159</v>
       </c>
       <c r="E51">
         <v>7.1</v>
@@ -4850,46 +4832,46 @@
         <v>1</v>
       </c>
       <c r="G51" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H51">
         <v>10</v>
       </c>
       <c r="I51" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J51" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="K51" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="L51" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="M51" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="N51" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="O51" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P51" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q51">
         <v>2</v>
       </c>
       <c r="R51" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="S51">
-        <v>18.594724</v>
+        <v>18.909581</v>
       </c>
       <c r="T51">
-        <v>9.297362</v>
+        <v>9.300903999999999</v>
       </c>
       <c r="U51">
         <v>0</v>
@@ -4898,30 +4880,27 @@
         <v>0</v>
       </c>
       <c r="W51">
-        <v>0</v>
+        <v>9.608677</v>
       </c>
       <c r="X51">
-        <v>9.297362</v>
+        <v>0</v>
       </c>
       <c r="Y51">
         <v>0</v>
       </c>
-      <c r="Z51">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:26">
+    </row>
+    <row r="52" spans="1:25">
       <c r="A52" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B52" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C52" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D52" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E52">
         <v>4.1</v>
@@ -4930,46 +4909,46 @@
         <v>2</v>
       </c>
       <c r="G52" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H52">
         <v>180</v>
       </c>
       <c r="I52" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J52" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="K52" t="s">
         <v>254</v>
       </c>
       <c r="L52" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="M52" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="N52" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="O52" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="P52" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q52">
         <v>2</v>
       </c>
       <c r="R52" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="S52">
-        <v>179.818916</v>
+        <v>176.529522</v>
       </c>
       <c r="T52">
-        <v>89.909458</v>
+        <v>88.26476099999999</v>
       </c>
       <c r="U52">
         <v>0</v>
@@ -4978,30 +4957,27 @@
         <v>0</v>
       </c>
       <c r="W52">
-        <v>0</v>
+        <v>88.26476099999999</v>
       </c>
       <c r="X52">
-        <v>89.909458</v>
+        <v>0</v>
       </c>
       <c r="Y52">
         <v>0</v>
       </c>
-      <c r="Z52">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="1:26">
+    </row>
+    <row r="53" spans="1:25">
       <c r="A53" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B53" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C53" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D53" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E53">
         <v>5.5</v>
@@ -5010,24 +4986,75 @@
         <v>2</v>
       </c>
       <c r="G53" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H53">
         <v>896</v>
       </c>
-    </row>
-    <row r="54" spans="1:26">
+      <c r="I53" t="s">
+        <v>74</v>
+      </c>
+      <c r="J53" t="s">
+        <v>237</v>
+      </c>
+      <c r="K53" t="s">
+        <v>254</v>
+      </c>
+      <c r="L53" t="s">
+        <v>157</v>
+      </c>
+      <c r="M53" t="s">
+        <v>152</v>
+      </c>
+      <c r="N53" t="s">
+        <v>256</v>
+      </c>
+      <c r="O53" t="s">
+        <v>304</v>
+      </c>
+      <c r="P53" t="s">
+        <v>360</v>
+      </c>
+      <c r="Q53">
+        <v>2</v>
+      </c>
+      <c r="R53" t="s">
+        <v>209</v>
+      </c>
+      <c r="S53">
+        <v>895.985321</v>
+      </c>
+      <c r="T53">
+        <v>447.9926605</v>
+      </c>
+      <c r="U53">
+        <v>0</v>
+      </c>
+      <c r="V53">
+        <v>0</v>
+      </c>
+      <c r="W53">
+        <v>447.9926605</v>
+      </c>
+      <c r="X53">
+        <v>0</v>
+      </c>
+      <c r="Y53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:25">
       <c r="A54" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B54" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C54" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D54" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E54">
         <v>9.1</v>
@@ -5036,155 +5063,98 @@
         <v>2</v>
       </c>
       <c r="G54" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H54">
         <v>10</v>
       </c>
-      <c r="I54" t="s">
+    </row>
+    <row r="55" spans="1:25">
+      <c r="A55" t="s">
         <v>76</v>
       </c>
-      <c r="J54" t="s">
-        <v>237</v>
-      </c>
-      <c r="K54" t="s">
-        <v>255</v>
-      </c>
-      <c r="L54" t="s">
-        <v>155</v>
-      </c>
-      <c r="M54" t="s">
-        <v>153</v>
-      </c>
-      <c r="N54" t="s">
-        <v>259</v>
-      </c>
-      <c r="O54" t="s">
-        <v>305</v>
-      </c>
-      <c r="P54" t="s">
-        <v>359</v>
-      </c>
-      <c r="Q54">
-        <v>3</v>
-      </c>
-      <c r="R54" t="s">
+      <c r="B55" t="s">
+        <v>136</v>
+      </c>
+      <c r="C55" t="s">
+        <v>152</v>
+      </c>
+      <c r="D55" t="s">
+        <v>154</v>
+      </c>
+      <c r="F55">
+        <v>1</v>
+      </c>
+      <c r="G55" t="s">
         <v>211</v>
-      </c>
-      <c r="S54">
-        <v>45.331011</v>
-      </c>
-      <c r="T54">
-        <v>11.612208</v>
-      </c>
-      <c r="U54">
-        <v>0</v>
-      </c>
-      <c r="V54">
-        <v>0</v>
-      </c>
-      <c r="W54">
-        <v>0</v>
-      </c>
-      <c r="X54">
-        <v>11.612208</v>
-      </c>
-      <c r="Y54">
-        <v>22.106595</v>
-      </c>
-      <c r="Z54">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="1:26">
-      <c r="A55" t="s">
-        <v>77</v>
-      </c>
-      <c r="B55" t="s">
-        <v>137</v>
-      </c>
-      <c r="C55" t="s">
-        <v>153</v>
-      </c>
-      <c r="D55" t="s">
-        <v>155</v>
-      </c>
-      <c r="F55">
-        <v>1</v>
-      </c>
-      <c r="G55" t="s">
-        <v>212</v>
       </c>
       <c r="H55">
         <v>8</v>
       </c>
       <c r="I55" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J55" t="s">
         <v>238</v>
       </c>
       <c r="K55" t="s">
+        <v>255</v>
+      </c>
+      <c r="L55" t="s">
+        <v>154</v>
+      </c>
+      <c r="M55" t="s">
+        <v>152</v>
+      </c>
+      <c r="N55" t="s">
         <v>256</v>
       </c>
-      <c r="L55" t="s">
-        <v>155</v>
-      </c>
-      <c r="M55" t="s">
-        <v>153</v>
-      </c>
-      <c r="N55" t="s">
-        <v>259</v>
-      </c>
       <c r="O55" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="P55" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Q55">
         <v>6</v>
       </c>
       <c r="R55" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="S55">
-        <v>27.004809</v>
+        <v>48.60424799999999</v>
       </c>
       <c r="T55">
-        <v>4.5008015</v>
+        <v>8.100707999999999</v>
       </c>
       <c r="U55">
-        <v>4.5008015</v>
+        <v>8.100707999999999</v>
       </c>
       <c r="V55">
-        <v>4.5008015</v>
+        <v>8.100707999999999</v>
       </c>
       <c r="W55">
-        <v>4.5008015</v>
+        <v>8.100707999999999</v>
       </c>
       <c r="X55">
-        <v>4.5008015</v>
+        <v>8.100707999999999</v>
       </c>
       <c r="Y55">
-        <v>4.5008015</v>
-      </c>
-      <c r="Z55">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:26">
+        <v>8.100707999999999</v>
+      </c>
+    </row>
+    <row r="56" spans="1:25">
       <c r="A56" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C56" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D56" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E56">
         <v>7.1</v>
@@ -5193,78 +5163,75 @@
         <v>2</v>
       </c>
       <c r="G56" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H56">
         <v>5</v>
       </c>
       <c r="I56" t="s">
+        <v>54</v>
+      </c>
+      <c r="J56" t="s">
+        <v>229</v>
+      </c>
+      <c r="K56" t="s">
+        <v>246</v>
+      </c>
+      <c r="L56" t="s">
+        <v>158</v>
+      </c>
+      <c r="M56" t="s">
+        <v>152</v>
+      </c>
+      <c r="N56" t="s">
+        <v>256</v>
+      </c>
+      <c r="O56" t="s">
+        <v>306</v>
+      </c>
+      <c r="P56" t="s">
+        <v>362</v>
+      </c>
+      <c r="Q56">
+        <v>2</v>
+      </c>
+      <c r="R56" t="s">
+        <v>212</v>
+      </c>
+      <c r="S56">
+        <v>12.597506</v>
+      </c>
+      <c r="T56">
+        <v>0</v>
+      </c>
+      <c r="U56">
+        <v>0</v>
+      </c>
+      <c r="V56">
+        <v>6.298753</v>
+      </c>
+      <c r="W56">
+        <v>0</v>
+      </c>
+      <c r="X56">
+        <v>6.298753</v>
+      </c>
+      <c r="Y56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:25">
+      <c r="A57" t="s">
         <v>55</v>
       </c>
-      <c r="J56" t="s">
-        <v>239</v>
-      </c>
-      <c r="K56" t="s">
-        <v>257</v>
-      </c>
-      <c r="L56" t="s">
-        <v>159</v>
-      </c>
-      <c r="M56" t="s">
-        <v>153</v>
-      </c>
-      <c r="N56" t="s">
-        <v>259</v>
-      </c>
-      <c r="O56" t="s">
-        <v>307</v>
-      </c>
-      <c r="P56" t="s">
-        <v>361</v>
-      </c>
-      <c r="Q56">
-        <v>3</v>
-      </c>
-      <c r="R56" t="s">
-        <v>213</v>
-      </c>
-      <c r="S56">
-        <v>6.37128</v>
-      </c>
-      <c r="T56">
-        <v>2.119164</v>
-      </c>
-      <c r="U56">
-        <v>0</v>
-      </c>
-      <c r="V56">
-        <v>0</v>
-      </c>
-      <c r="W56">
-        <v>2.132952</v>
-      </c>
-      <c r="X56">
-        <v>2.119164</v>
-      </c>
-      <c r="Y56">
-        <v>0</v>
-      </c>
-      <c r="Z56">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:26">
-      <c r="A57" t="s">
-        <v>56</v>
-      </c>
       <c r="B57" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C57" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D57" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E57">
         <v>7.1</v>
@@ -5273,78 +5240,75 @@
         <v>2</v>
       </c>
       <c r="G57" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H57">
         <v>5</v>
       </c>
       <c r="I57" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="J57" t="s">
-        <v>240</v>
+        <v>229</v>
       </c>
       <c r="K57" t="s">
-        <v>258</v>
+        <v>246</v>
       </c>
       <c r="L57" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="M57" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="N57" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="O57" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="P57" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q57">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R57" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="S57">
-        <v>6.379761</v>
+        <v>12.301826</v>
       </c>
       <c r="T57">
-        <v>2.1238705</v>
+        <v>0</v>
       </c>
       <c r="U57">
         <v>0</v>
       </c>
       <c r="V57">
-        <v>0</v>
+        <v>6.150913</v>
       </c>
       <c r="W57">
-        <v>2.13202</v>
+        <v>0</v>
       </c>
       <c r="X57">
-        <v>2.1238705</v>
+        <v>6.150913</v>
       </c>
       <c r="Y57">
         <v>0</v>
       </c>
-      <c r="Z57">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:26">
+    </row>
+    <row r="58" spans="1:25">
       <c r="A58" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B58" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C58" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D58" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E58">
         <v>7.1</v>
@@ -5353,46 +5317,46 @@
         <v>2</v>
       </c>
       <c r="G58" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H58">
         <v>10</v>
       </c>
       <c r="I58" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="J58" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="K58" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="L58" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="M58" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="N58" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="O58" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="P58" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Q58">
         <v>2</v>
       </c>
       <c r="R58" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="S58">
-        <v>9.031836</v>
+        <v>10.8024105</v>
       </c>
       <c r="T58">
-        <v>4.515918</v>
+        <v>5.401281</v>
       </c>
       <c r="U58">
         <v>0</v>
@@ -5401,30 +5365,27 @@
         <v>0</v>
       </c>
       <c r="W58">
-        <v>0</v>
+        <v>5.4011295</v>
       </c>
       <c r="X58">
-        <v>4.515918</v>
+        <v>0</v>
       </c>
       <c r="Y58">
         <v>0</v>
       </c>
-      <c r="Z58">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="1:26">
+    </row>
+    <row r="59" spans="1:25">
       <c r="A59" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B59" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C59" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D59" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E59">
         <v>2.1</v>
@@ -5433,78 +5394,75 @@
         <v>1</v>
       </c>
       <c r="G59" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H59">
         <v>18</v>
       </c>
       <c r="I59" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J59" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="K59" t="s">
         <v>245</v>
       </c>
       <c r="L59" t="s">
+        <v>157</v>
+      </c>
+      <c r="M59" t="s">
+        <v>153</v>
+      </c>
+      <c r="N59" t="s">
+        <v>256</v>
+      </c>
+      <c r="O59" t="s">
+        <v>309</v>
+      </c>
+      <c r="P59" t="s">
+        <v>365</v>
+      </c>
+      <c r="Q59">
+        <v>1</v>
+      </c>
+      <c r="R59" t="s">
+        <v>215</v>
+      </c>
+      <c r="S59">
+        <v>17.700787</v>
+      </c>
+      <c r="T59">
+        <v>0</v>
+      </c>
+      <c r="U59">
+        <v>0</v>
+      </c>
+      <c r="V59">
+        <v>0</v>
+      </c>
+      <c r="W59">
+        <v>0</v>
+      </c>
+      <c r="X59">
+        <v>17.700787</v>
+      </c>
+      <c r="Y59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:25">
+      <c r="A60" t="s">
+        <v>79</v>
+      </c>
+      <c r="B60" t="s">
+        <v>141</v>
+      </c>
+      <c r="C60" t="s">
+        <v>153</v>
+      </c>
+      <c r="D60" t="s">
         <v>158</v>
-      </c>
-      <c r="M59" t="s">
-        <v>154</v>
-      </c>
-      <c r="N59" t="s">
-        <v>259</v>
-      </c>
-      <c r="O59" t="s">
-        <v>310</v>
-      </c>
-      <c r="P59" t="s">
-        <v>364</v>
-      </c>
-      <c r="Q59">
-        <v>1</v>
-      </c>
-      <c r="R59" t="s">
-        <v>216</v>
-      </c>
-      <c r="S59">
-        <v>19.372062</v>
-      </c>
-      <c r="T59">
-        <v>0</v>
-      </c>
-      <c r="U59">
-        <v>0</v>
-      </c>
-      <c r="V59">
-        <v>0</v>
-      </c>
-      <c r="W59">
-        <v>19.372062</v>
-      </c>
-      <c r="X59">
-        <v>0</v>
-      </c>
-      <c r="Y59">
-        <v>0</v>
-      </c>
-      <c r="Z59">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="1:26">
-      <c r="A60" t="s">
-        <v>80</v>
-      </c>
-      <c r="B60" t="s">
-        <v>142</v>
-      </c>
-      <c r="C60" t="s">
-        <v>154</v>
-      </c>
-      <c r="D60" t="s">
-        <v>159</v>
       </c>
       <c r="E60">
         <v>4.1</v>
@@ -5513,78 +5471,75 @@
         <v>1</v>
       </c>
       <c r="G60" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H60">
         <v>20</v>
       </c>
       <c r="I60" t="s">
+        <v>79</v>
+      </c>
+      <c r="J60" t="s">
+        <v>222</v>
+      </c>
+      <c r="K60" t="s">
+        <v>239</v>
+      </c>
+      <c r="L60" t="s">
+        <v>158</v>
+      </c>
+      <c r="M60" t="s">
+        <v>153</v>
+      </c>
+      <c r="N60" t="s">
+        <v>256</v>
+      </c>
+      <c r="O60" t="s">
+        <v>310</v>
+      </c>
+      <c r="P60" t="s">
+        <v>366</v>
+      </c>
+      <c r="Q60">
+        <v>1</v>
+      </c>
+      <c r="R60" t="s">
+        <v>216</v>
+      </c>
+      <c r="S60">
+        <v>16.2518945</v>
+      </c>
+      <c r="T60">
+        <v>0</v>
+      </c>
+      <c r="U60">
+        <v>0</v>
+      </c>
+      <c r="V60">
+        <v>16.2518945</v>
+      </c>
+      <c r="W60">
+        <v>0</v>
+      </c>
+      <c r="X60">
+        <v>0</v>
+      </c>
+      <c r="Y60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:25">
+      <c r="A61" t="s">
         <v>80</v>
       </c>
-      <c r="J60" t="s">
-        <v>227</v>
-      </c>
-      <c r="K60" t="s">
-        <v>245</v>
-      </c>
-      <c r="L60" t="s">
-        <v>159</v>
-      </c>
-      <c r="M60" t="s">
-        <v>154</v>
-      </c>
-      <c r="N60" t="s">
-        <v>259</v>
-      </c>
-      <c r="O60" t="s">
-        <v>311</v>
-      </c>
-      <c r="P60" t="s">
-        <v>365</v>
-      </c>
-      <c r="Q60">
-        <v>1</v>
-      </c>
-      <c r="R60" t="s">
-        <v>217</v>
-      </c>
-      <c r="S60">
-        <v>21.2656055</v>
-      </c>
-      <c r="T60">
-        <v>0</v>
-      </c>
-      <c r="U60">
-        <v>0</v>
-      </c>
-      <c r="V60">
-        <v>0</v>
-      </c>
-      <c r="W60">
-        <v>21.2656055</v>
-      </c>
-      <c r="X60">
-        <v>0</v>
-      </c>
-      <c r="Y60">
-        <v>0</v>
-      </c>
-      <c r="Z60">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="1:26">
-      <c r="A61" t="s">
-        <v>81</v>
-      </c>
       <c r="B61" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C61" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D61" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E61">
         <v>5.3</v>
@@ -5593,43 +5548,43 @@
         <v>1</v>
       </c>
       <c r="G61" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H61">
         <v>36</v>
       </c>
       <c r="I61" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="J61" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="K61" t="s">
         <v>245</v>
       </c>
       <c r="L61" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="M61" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="N61" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="O61" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="P61" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Q61">
         <v>1</v>
       </c>
       <c r="R61" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="S61">
-        <v>40.629621</v>
+        <v>52.8061575</v>
       </c>
       <c r="T61">
         <v>0</v>
@@ -5641,30 +5596,27 @@
         <v>0</v>
       </c>
       <c r="W61">
-        <v>40.629621</v>
+        <v>0</v>
       </c>
       <c r="X61">
-        <v>0</v>
+        <v>52.8061575</v>
       </c>
       <c r="Y61">
         <v>0</v>
       </c>
-      <c r="Z61">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="1:26">
+    </row>
+    <row r="62" spans="1:25">
       <c r="A62" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B62" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C62" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D62" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E62">
         <v>5.2</v>
@@ -5673,78 +5625,75 @@
         <v>1</v>
       </c>
       <c r="G62" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H62">
         <v>18</v>
       </c>
       <c r="I62" t="s">
+        <v>81</v>
+      </c>
+      <c r="J62" t="s">
+        <v>222</v>
+      </c>
+      <c r="K62" t="s">
+        <v>239</v>
+      </c>
+      <c r="L62" t="s">
+        <v>157</v>
+      </c>
+      <c r="M62" t="s">
+        <v>153</v>
+      </c>
+      <c r="N62" t="s">
+        <v>256</v>
+      </c>
+      <c r="O62" t="s">
+        <v>312</v>
+      </c>
+      <c r="P62" t="s">
+        <v>368</v>
+      </c>
+      <c r="Q62">
+        <v>1</v>
+      </c>
+      <c r="R62" t="s">
+        <v>218</v>
+      </c>
+      <c r="S62">
+        <v>18.291863</v>
+      </c>
+      <c r="T62">
+        <v>0</v>
+      </c>
+      <c r="U62">
+        <v>0</v>
+      </c>
+      <c r="V62">
+        <v>18.291863</v>
+      </c>
+      <c r="W62">
+        <v>0</v>
+      </c>
+      <c r="X62">
+        <v>0</v>
+      </c>
+      <c r="Y62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:25">
+      <c r="A63" t="s">
         <v>82</v>
       </c>
-      <c r="J62" t="s">
-        <v>227</v>
-      </c>
-      <c r="K62" t="s">
-        <v>245</v>
-      </c>
-      <c r="L62" t="s">
-        <v>158</v>
-      </c>
-      <c r="M62" t="s">
-        <v>154</v>
-      </c>
-      <c r="N62" t="s">
-        <v>259</v>
-      </c>
-      <c r="O62" t="s">
-        <v>313</v>
-      </c>
-      <c r="P62" t="s">
-        <v>367</v>
-      </c>
-      <c r="Q62">
-        <v>1</v>
-      </c>
-      <c r="R62" t="s">
-        <v>219</v>
-      </c>
-      <c r="S62">
-        <v>20.7914845</v>
-      </c>
-      <c r="T62">
-        <v>0</v>
-      </c>
-      <c r="U62">
-        <v>0</v>
-      </c>
-      <c r="V62">
-        <v>0</v>
-      </c>
-      <c r="W62">
-        <v>20.7914845</v>
-      </c>
-      <c r="X62">
-        <v>0</v>
-      </c>
-      <c r="Y62">
-        <v>0</v>
-      </c>
-      <c r="Z62">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="1:26">
-      <c r="A63" t="s">
-        <v>83</v>
-      </c>
       <c r="B63" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C63" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D63" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E63">
         <v>5.2</v>
@@ -5753,78 +5702,75 @@
         <v>1</v>
       </c>
       <c r="G63" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H63">
         <v>36</v>
       </c>
       <c r="I63" t="s">
+        <v>82</v>
+      </c>
+      <c r="J63" t="s">
+        <v>222</v>
+      </c>
+      <c r="K63" t="s">
+        <v>239</v>
+      </c>
+      <c r="L63" t="s">
+        <v>157</v>
+      </c>
+      <c r="M63" t="s">
+        <v>153</v>
+      </c>
+      <c r="N63" t="s">
+        <v>256</v>
+      </c>
+      <c r="O63" t="s">
+        <v>313</v>
+      </c>
+      <c r="P63" t="s">
+        <v>369</v>
+      </c>
+      <c r="Q63">
+        <v>1</v>
+      </c>
+      <c r="R63" t="s">
+        <v>219</v>
+      </c>
+      <c r="S63">
+        <v>36.003191</v>
+      </c>
+      <c r="T63">
+        <v>0</v>
+      </c>
+      <c r="U63">
+        <v>0</v>
+      </c>
+      <c r="V63">
+        <v>36.003191</v>
+      </c>
+      <c r="W63">
+        <v>0</v>
+      </c>
+      <c r="X63">
+        <v>0</v>
+      </c>
+      <c r="Y63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:25">
+      <c r="A64" t="s">
         <v>83</v>
       </c>
-      <c r="J63" t="s">
-        <v>227</v>
-      </c>
-      <c r="K63" t="s">
-        <v>245</v>
-      </c>
-      <c r="L63" t="s">
-        <v>158</v>
-      </c>
-      <c r="M63" t="s">
-        <v>154</v>
-      </c>
-      <c r="N63" t="s">
-        <v>259</v>
-      </c>
-      <c r="O63" t="s">
-        <v>314</v>
-      </c>
-      <c r="P63" t="s">
-        <v>368</v>
-      </c>
-      <c r="Q63">
-        <v>1</v>
-      </c>
-      <c r="R63" t="s">
-        <v>220</v>
-      </c>
-      <c r="S63">
-        <v>43.1989775</v>
-      </c>
-      <c r="T63">
-        <v>0</v>
-      </c>
-      <c r="U63">
-        <v>0</v>
-      </c>
-      <c r="V63">
-        <v>0</v>
-      </c>
-      <c r="W63">
-        <v>43.1989775</v>
-      </c>
-      <c r="X63">
-        <v>0</v>
-      </c>
-      <c r="Y63">
-        <v>0</v>
-      </c>
-      <c r="Z63">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="1:26">
-      <c r="A64" t="s">
-        <v>84</v>
-      </c>
       <c r="B64" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C64" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D64" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E64">
         <v>5.6</v>
@@ -5833,78 +5779,75 @@
         <v>1</v>
       </c>
       <c r="G64" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H64">
         <v>90</v>
       </c>
       <c r="I64" t="s">
+        <v>83</v>
+      </c>
+      <c r="J64" t="s">
+        <v>222</v>
+      </c>
+      <c r="K64" t="s">
+        <v>239</v>
+      </c>
+      <c r="L64" t="s">
+        <v>157</v>
+      </c>
+      <c r="M64" t="s">
+        <v>153</v>
+      </c>
+      <c r="N64" t="s">
+        <v>256</v>
+      </c>
+      <c r="O64" t="s">
+        <v>314</v>
+      </c>
+      <c r="P64" t="s">
+        <v>370</v>
+      </c>
+      <c r="Q64">
+        <v>1</v>
+      </c>
+      <c r="R64" t="s">
+        <v>220</v>
+      </c>
+      <c r="S64">
+        <v>88.93452600000001</v>
+      </c>
+      <c r="T64">
+        <v>0</v>
+      </c>
+      <c r="U64">
+        <v>0</v>
+      </c>
+      <c r="V64">
+        <v>88.93452600000001</v>
+      </c>
+      <c r="W64">
+        <v>0</v>
+      </c>
+      <c r="X64">
+        <v>0</v>
+      </c>
+      <c r="Y64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:25">
+      <c r="A65" t="s">
         <v>84</v>
       </c>
-      <c r="J64" t="s">
-        <v>227</v>
-      </c>
-      <c r="K64" t="s">
-        <v>245</v>
-      </c>
-      <c r="L64" t="s">
-        <v>158</v>
-      </c>
-      <c r="M64" t="s">
-        <v>154</v>
-      </c>
-      <c r="N64" t="s">
-        <v>259</v>
-      </c>
-      <c r="O64" t="s">
-        <v>315</v>
-      </c>
-      <c r="P64" t="s">
-        <v>369</v>
-      </c>
-      <c r="Q64">
-        <v>1</v>
-      </c>
-      <c r="R64" t="s">
-        <v>221</v>
-      </c>
-      <c r="S64">
-        <v>89.981465</v>
-      </c>
-      <c r="T64">
-        <v>0</v>
-      </c>
-      <c r="U64">
-        <v>0</v>
-      </c>
-      <c r="V64">
-        <v>0</v>
-      </c>
-      <c r="W64">
-        <v>89.981465</v>
-      </c>
-      <c r="X64">
-        <v>0</v>
-      </c>
-      <c r="Y64">
-        <v>0</v>
-      </c>
-      <c r="Z64">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="1:26">
-      <c r="A65" t="s">
-        <v>85</v>
-      </c>
       <c r="B65" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C65" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D65" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E65">
         <v>2.1</v>
@@ -5913,43 +5856,43 @@
         <v>1</v>
       </c>
       <c r="G65" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H65">
         <v>54</v>
       </c>
       <c r="I65" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J65" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="K65" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="L65" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="M65" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="N65" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="O65" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="P65" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="Q65">
         <v>1</v>
       </c>
       <c r="R65" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="S65">
-        <v>55.876581</v>
+        <v>52.8061575</v>
       </c>
       <c r="T65">
         <v>0</v>
@@ -5964,12 +5907,9 @@
         <v>0</v>
       </c>
       <c r="X65">
-        <v>0</v>
+        <v>52.8061575</v>
       </c>
       <c r="Y65">
-        <v>55.876581</v>
-      </c>
-      <c r="Z65">
         <v>0</v>
       </c>
     </row>

--- a/merged_df.xlsx
+++ b/merged_df.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="718" uniqueCount="335">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="842" uniqueCount="380">
   <si>
     <t>Kürzel (LongName)_target</t>
   </si>
@@ -73,16 +73,22 @@
     <t>sum_Qto_SpaceBaseQuantities.NetFloorArea_actual</t>
   </si>
   <si>
-    <t>__pivot_-8.0_actual</t>
-  </si>
-  <si>
-    <t>__pivot_-4.0_actual</t>
-  </si>
-  <si>
-    <t>__pivot_0.0_actual</t>
-  </si>
-  <si>
-    <t>__pivot_4.0_actual</t>
+    <t>__pivot_-0.5_actual</t>
+  </si>
+  <si>
+    <t>__pivot_-4.5_actual</t>
+  </si>
+  <si>
+    <t>__pivot_14.9_actual</t>
+  </si>
+  <si>
+    <t>__pivot_3.0_actual</t>
+  </si>
+  <si>
+    <t>__pivot_6.4_actual</t>
+  </si>
+  <si>
+    <t>__pivot_9.3_actual</t>
   </si>
   <si>
     <t>KOR</t>
@@ -700,55 +706,94 @@
     <t>Unterricht_TAR</t>
   </si>
   <si>
-    <t>KUE - KUL - KUW - RKU</t>
-  </si>
-  <si>
-    <t>Floor, Basement, Groundfloor, Basement 2</t>
-  </si>
-  <si>
-    <t>Floor</t>
-  </si>
-  <si>
-    <t>Groundfloor</t>
-  </si>
-  <si>
-    <t>Groundfloor, Floor</t>
-  </si>
-  <si>
-    <t>Basement</t>
-  </si>
-  <si>
-    <t>Basement 2, Basement, Groundfloor, Floor</t>
-  </si>
-  <si>
-    <t>Basement 2, Basement</t>
-  </si>
-  <si>
-    <t>Basement 2</t>
-  </si>
-  <si>
-    <t>4.0, -4.0, 0.0, -8.0</t>
-  </si>
-  <si>
-    <t>4.0</t>
-  </si>
-  <si>
-    <t>0.0</t>
-  </si>
-  <si>
-    <t>0.0, 4.0</t>
-  </si>
-  <si>
-    <t>-4.0</t>
-  </si>
-  <si>
-    <t>-8.0, -4.0, 0.0, 4.0</t>
-  </si>
-  <si>
-    <t>-8.0, -4.0</t>
-  </si>
-  <si>
-    <t>-8.0</t>
+    <t>-1. Geschoss, 1. Geschoss</t>
+  </si>
+  <si>
+    <t>EG</t>
+  </si>
+  <si>
+    <t>1. Geschoss</t>
+  </si>
+  <si>
+    <t>1. Geschoss, 3.OG</t>
+  </si>
+  <si>
+    <t>-1. Geschoss</t>
+  </si>
+  <si>
+    <t>-1. Geschoss, EG</t>
+  </si>
+  <si>
+    <t>4. Geschoss</t>
+  </si>
+  <si>
+    <t>-1. Geschoss, 1. Geschoss, 2.OG, 3.OG, 4. Geschoss, EG</t>
+  </si>
+  <si>
+    <t>-1. Geschoss, 1. Geschoss, 2.OG, 3.OG, EG</t>
+  </si>
+  <si>
+    <t>1. Geschoss, 2.OG, 3.OG</t>
+  </si>
+  <si>
+    <t>-1. Geschoss, 2.OG</t>
+  </si>
+  <si>
+    <t>2.OG</t>
+  </si>
+  <si>
+    <t>-1. Geschoss, 1. Geschoss, 3.OG</t>
+  </si>
+  <si>
+    <t>1. Geschoss, 2.OG, EG</t>
+  </si>
+  <si>
+    <t>3.OG</t>
+  </si>
+  <si>
+    <t>-4.5, 3.0</t>
+  </si>
+  <si>
+    <t>-0.5</t>
+  </si>
+  <si>
+    <t>3.0</t>
+  </si>
+  <si>
+    <t>3.0, 9.3</t>
+  </si>
+  <si>
+    <t>-4.5</t>
+  </si>
+  <si>
+    <t>-0.5, -4.5</t>
+  </si>
+  <si>
+    <t>14.9</t>
+  </si>
+  <si>
+    <t>-0.5, -4.5, 14.9, 3.0, 6.4, 9.3</t>
+  </si>
+  <si>
+    <t>-0.5, -4.5, 3.0, 6.4, 9.3</t>
+  </si>
+  <si>
+    <t>3.0, 6.4, 9.3</t>
+  </si>
+  <si>
+    <t>-4.5, 6.4</t>
+  </si>
+  <si>
+    <t>6.4</t>
+  </si>
+  <si>
+    <t>-4.5, 3.0, 9.3</t>
+  </si>
+  <si>
+    <t>-0.5, 3.0, 6.4</t>
+  </si>
+  <si>
+    <t>9.3</t>
   </si>
   <si>
     <t>INTERNAL</t>
@@ -763,262 +808,352 @@
     <t>USERDEFINED</t>
   </si>
   <si>
-    <t>3FJla_fc5AowlVR7K0V9Jn, 0Ox5WtWrHCdvUeqlAzpmsA, 2KzcsUtHfBYemvn9UyzE81, 2s0L327tr6VRsn315VFcv4, 3ape7LX1X19Pl3XG73pAjv, 1qyhUqqr5EOARgC$yiuTqD, 2bBI1elkj0Oek9cmG$Q3Ma</t>
-  </si>
-  <si>
-    <t>0Qq$waI0D4tgESdrUp3c1O, 12gKHTtNfFmekuay$mdDom</t>
-  </si>
-  <si>
-    <t>1y7wXEg0X4jefW$q9l4Sws, 1PK9Ey0Zn5ivXyO02tNPnE, 1PGhHlbO9DiepinQf6hwYs, 2bQtO28tjCYgFpzLJoIk5N, 25xRd4zeb6FQai$4dR8fLo</t>
-  </si>
-  <si>
-    <t>33c9HIJ6n9FOg9jQ10e7XW</t>
-  </si>
-  <si>
-    <t>0h1Q_MKjL9qhO9xPZHQEC0, 2SYYV19HfFMg$eemP5gsSh, 3DvTiD3qjCGQNIzPLShWzK</t>
-  </si>
-  <si>
-    <t>0emDOihfX32QTN4LjMxx$8</t>
-  </si>
-  <si>
-    <t>3p6Crgcl11owBHhQgVm2dt</t>
-  </si>
-  <si>
-    <t>1j9ARi4v99MOAXxrEKQnIY, 0mQ1OQ2KbCoe4O8U7o7ZGC, 1c0iJwEOv0axC7QIHzNVe4, 0E7k058g59EPHY8fcst31G, 2Y3tOWW6rAHQictn8s8MM1, 095A0lJ1b0POgbye2cXhbz, 1m5RyVkwD45uqUi5nGK8Om, 0T04Yc55TAz9Ex6LYJ5ttH</t>
-  </si>
-  <si>
-    <t>3GA2fBeGn3QxvfaWJ4nNbE</t>
-  </si>
-  <si>
-    <t>0OmUU7RRTBVOUuHb_tcrS8</t>
-  </si>
-  <si>
-    <t>2Pk7nRyp98sP$yjORrs$b2</t>
-  </si>
-  <si>
-    <t>3loFfwTqb4YOQ9Wj6CnMQT</t>
-  </si>
-  <si>
-    <t>1t1lbS9dr2XheriClmXJFP</t>
-  </si>
-  <si>
-    <t>2AD3ezC5T7OfiQqUeNinT_</t>
-  </si>
-  <si>
-    <t>0ojKeiJj18hQAeKsi3MCUz</t>
-  </si>
-  <si>
-    <t>08oscw6nX9IPLbM6vUne$H</t>
-  </si>
-  <si>
-    <t>1UvvnA5DLAd8fqE7Om3NFZ</t>
-  </si>
-  <si>
-    <t>1WNqKfJ7f4fg0RlNTYk9rK, 32NtxuewD39fPwhjc9G7eh, 1RFHFul31DC8qTzrd9evSS, 3aq0p0uGDAjBIR7qH9wVOd, 3v6IM9aIvFKOBlWhGX2vX8, 0Apkm4xBn9tRUr_fB_H6Lb, 3w$H7yTfXDeuHQIh$eqjLR, 09V2p$ADT3k87hS8HnQXg5</t>
-  </si>
-  <si>
-    <t>2LFkdj2QnCduMSHvYtBipx, 1PFzIrJErEG84kwBn$OxXw, 0euxUbDfP52Qc_j3rPztSY, 31VZCub5f7XAYMvBGmRa5R, 0$_Sn4eLfFGA$RreVOUGOn, 2h5TsfB6rCe9bDQwyy1rq1, 3c_NATrkH3xB08nykkf1Lp, 3XaHP2zmrA3vDOSMe7Irpy, 1eGXVG4HX18uWobSy1k1CA, 0JaBps47PAgPOMaWJ0meX6, 0zE$h5Uhv1PuMt9aKeH0dj, 3v1q2JbnbEqRpjcqWTGNDb, 07dmsc3UH1DAxq9qZltZyB, 2MHNF1f5P0ixnGPhqeigZs, 2lZvvG_1r7Xfo0Vce_7ZXd, 1DXdSaBCbDqA0q8AMlEGVL</t>
-  </si>
-  <si>
-    <t>3otq55wJT9YgG0D8Q2B8_2</t>
-  </si>
-  <si>
-    <t>1mx6e_dIr8_uSnqKdiufRK</t>
-  </si>
-  <si>
-    <t>1ht0JSji12JRAqLAuzG0Zp</t>
-  </si>
-  <si>
-    <t>0RzL8$X8L06gFg8eO$_Qsh, 3rV0oQhib3YgzVr4_uUQ6a</t>
-  </si>
-  <si>
-    <t>3N8W7vx_5DmOt4Avylvrgn</t>
-  </si>
-  <si>
-    <t>1j_jbAQEPEpAcj1Xi8a79K</t>
-  </si>
-  <si>
-    <t>290YmwkjP5aQCW4Epq0Pza, 3OWT1c0sTFxOwz95LItwwg</t>
-  </si>
-  <si>
-    <t>0BpaR0hHz7VAcCz87UWf1K, 0z1SwaP1HC9R$loNNu$fXb, 316WPdNFDAwRWNuCi6Dhu5, 1_XORWbpXEAvr3naAPATha</t>
-  </si>
-  <si>
-    <t>2we13nKQzDmPaBLsZSFqB4</t>
-  </si>
-  <si>
-    <t>2U9ujtpOn898Rdakz4pgW4, 31rDDfYQL5G9RbBbj2wsQ2</t>
-  </si>
-  <si>
-    <t>19pgcqrjD5I8VmiiLq8sbk, 28vkS$9e5FMAxNzs8GvhIy</t>
-  </si>
-  <si>
-    <t>2w$DxGPXrCFAsMbQs2MCJk, 1L9ZCkaHDE6wCgAr7Iq7Xh</t>
-  </si>
-  <si>
-    <t>0iYUGTNL9BKeBLvk3nj8TR, 1idjNrKPv26Pz0EyIGwstp</t>
-  </si>
-  <si>
-    <t>1IVWxSbyD22fC6Q9EoQ8Y8</t>
-  </si>
-  <si>
-    <t>2VHM8Espn8duFOS$g8X3S4</t>
-  </si>
-  <si>
-    <t>2QUDBoj296Cvg94FJb02hF, 0MyIb3f256A9MTle5rK9tm</t>
-  </si>
-  <si>
-    <t>26sl1kLDDBMvf3KDMedOa9</t>
-  </si>
-  <si>
-    <t>3hQqkNfLH9gg4u7ntjHcbj</t>
-  </si>
-  <si>
-    <t>3mrWJ5d_DCSOTp9ongMy5V</t>
-  </si>
-  <si>
-    <t>2cMoz_61HBjRfJFK9Xuq2q</t>
-  </si>
-  <si>
-    <t>3ptVibDCT3s8$BeVgkWauO</t>
-  </si>
-  <si>
-    <t>304DRh$Br1bB8wCYHm8mJe</t>
-  </si>
-  <si>
-    <t>1qvE8w_nP6g8gbxkltALhk</t>
-  </si>
-  <si>
-    <t>976, 979, 980, 981, 982, 983, 986</t>
-  </si>
-  <si>
-    <t>1035, 1043</t>
-  </si>
-  <si>
-    <t>1030, 1031, 1032, 1033, 1038</t>
-  </si>
-  <si>
-    <t>1039</t>
-  </si>
-  <si>
-    <t>1040, 1041, 1042</t>
-  </si>
-  <si>
-    <t>1044</t>
-  </si>
-  <si>
-    <t>1036</t>
-  </si>
-  <si>
-    <t>1020, 1021, 1025, 1026, 1027, 1028, 1029, 1034</t>
-  </si>
-  <si>
-    <t>1037</t>
-  </si>
-  <si>
-    <t>1022</t>
-  </si>
-  <si>
-    <t>1023</t>
-  </si>
-  <si>
-    <t>1008</t>
-  </si>
-  <si>
-    <t>1014</t>
-  </si>
-  <si>
-    <t>1013</t>
-  </si>
-  <si>
-    <t>1017</t>
-  </si>
-  <si>
-    <t>985</t>
-  </si>
-  <si>
-    <t>984</t>
-  </si>
-  <si>
-    <t>1047, 1050, 1058, 1059, 1060, 1067, 1068, 1069</t>
-  </si>
-  <si>
-    <t>1045, 1046, 1048, 1049, 1052, 1053, 1054, 1055, 1056, 1057, 1061, 1062, 1063, 1064, 1065, 1066</t>
-  </si>
-  <si>
-    <t>1009</t>
-  </si>
-  <si>
-    <t>1010</t>
-  </si>
-  <si>
-    <t>1051</t>
-  </si>
-  <si>
-    <t>977, 978</t>
-  </si>
-  <si>
-    <t>997</t>
-  </si>
-  <si>
-    <t>987</t>
-  </si>
-  <si>
-    <t>995, 996</t>
-  </si>
-  <si>
-    <t>998, 999, 1000, 1001</t>
-  </si>
-  <si>
-    <t>988</t>
-  </si>
-  <si>
-    <t>993, 994</t>
-  </si>
-  <si>
-    <t>1002, 1003</t>
-  </si>
-  <si>
-    <t>1004, 1005</t>
-  </si>
-  <si>
-    <t>989, 990</t>
-  </si>
-  <si>
-    <t>1024</t>
-  </si>
-  <si>
-    <t>1016</t>
-  </si>
-  <si>
-    <t>991, 992</t>
-  </si>
-  <si>
-    <t>1012</t>
-  </si>
-  <si>
-    <t>1019</t>
-  </si>
-  <si>
-    <t>1011</t>
-  </si>
-  <si>
-    <t>1015</t>
-  </si>
-  <si>
-    <t>1006</t>
-  </si>
-  <si>
-    <t>1018</t>
-  </si>
-  <si>
-    <t>1007</t>
+    <t>EXTERNAL, INTERNAL</t>
+  </si>
+  <si>
+    <t>0p1lENSoT5JfYmbpsgfmRt, 0wCAq0jgHCYvksd553QSn5, 2TNi1nxkfFkABCIp_dod2V, 304Yc6LEnBPxWhkwUFRLGQ, 3_y_gVstb83QpahCzBUnsB</t>
+  </si>
+  <si>
+    <t>3xa830HAf5gu6oBd5CywNb</t>
+  </si>
+  <si>
+    <t>1iHyFgYW1BChl1fRzC2TFE</t>
+  </si>
+  <si>
+    <t>2NmoQFhlLD3RtSI7q$w3ip, 2fahcaiuj46uE3P_8bkPKG, 2ibyAWWwH8Ch2C7vVRPEvR</t>
+  </si>
+  <si>
+    <t>17TJN44C5AZPctiYS36OpO, 2FvWFmZEf8RfbMTC$V5m2H, 2yAKVjTsn0uxY4GHs5XEAc</t>
+  </si>
+  <si>
+    <t>0YKJ_UpPP6xAH7MASML2$y, 0kqhWa_T5A6QEWEt6g4nBS, 0vb4Up$vH6wPRM89uVviTL, 0wcPYvVLf1QRz72KfUk8C$, 1kUVSVJcb4PuHgCLOTTMNJ, 2as_cWSvj95QK73E_XtxJV</t>
+  </si>
+  <si>
+    <t>2V_ryaK7X7IQY8rAvTbMfZ</t>
+  </si>
+  <si>
+    <t>07IJJjJ0f7PhT6cQSEphQc, 0V7fc2fYLADwg3MDcCyASr</t>
+  </si>
+  <si>
+    <t>2WDktp3XT3JPFqlt$OaNaD, 2esnaMxAP7E8qRqN1wi0Qs</t>
+  </si>
+  <si>
+    <t>1_Nf_eVonClhcXh6bUIhI2, 35Hx_9doD7z9n_QX4p0J6E</t>
+  </si>
+  <si>
+    <t>3IGPSzI1D26OYVbQL8QXmx</t>
+  </si>
+  <si>
+    <t>3CVAz3qE5DZ8zKmeIUfmRY</t>
+  </si>
+  <si>
+    <t>07MMNyWPrBlvnheniAZbN0</t>
+  </si>
+  <si>
+    <t>2jrhBrM6b21wRrLKuK8w_l</t>
+  </si>
+  <si>
+    <t>07zVYpgibF1xUBmaROh$$F</t>
+  </si>
+  <si>
+    <t>1AQfPYknD0fvgE2OJ203Fd</t>
+  </si>
+  <si>
+    <t>0AiGclYXf2pR$I_JJBUEUK, 38JS_x8w53sAtZB3$O_E_I</t>
+  </si>
+  <si>
+    <t>375_S0Hb9BpO4Vb$kT7hv0</t>
+  </si>
+  <si>
+    <t>2$C3Bg_6v41BNFh4tE9iWE, 2bKvu8opn3aeaaHo3FCTYQ, 3aWIBLmun8xQwDeDkCsms8</t>
+  </si>
+  <si>
+    <t>1XEpW$cvD4BBIrutknz0Li</t>
+  </si>
+  <si>
+    <t>05ck$tPxf0ug8iCmNvdD42</t>
+  </si>
+  <si>
+    <t>1iMEAALTb7a84z5vd4yHSE</t>
+  </si>
+  <si>
+    <t>1A5PyTdLvFggyb7IseXr0g</t>
+  </si>
+  <si>
+    <t>1glaB34_X70u5uIK$zAIc2, 3lCvbxxlz0nvI4eYtaPNct</t>
+  </si>
+  <si>
+    <t>2_gmJsxJvCHAXbuuMm6MAf</t>
+  </si>
+  <si>
+    <t>26RDUdXLv59OaQSt7VWZGn</t>
+  </si>
+  <si>
+    <t>0uTdmZpQr689WLzyXoMPMw, 1MLcl8cWjE5fgGs30NdXgm, 2YtsbQ_8PBxAhEA067Et6q, 2xdqNP89f4ke2gkmAWzexq, 3A4uoXqxb5C91V0WTvsCXp, 3WQ5Nxw0TBu9NFehsPLqKO</t>
+  </si>
+  <si>
+    <t>0_bL9xRaL4E9haNI6$mny2, 1$SeO2fG98Jw2$_k3rvGgs, 1PZjNBwQrATR5Ih0UsqcP1, 1qcJDz_NbC5xuvMS8lIPUZ, 1tZBONVL1FFO0MgvG2xgWX, 2CmITZ0rX67gi8x8F0uM$W, 2Incpf6HvFPAp1ExMHJbHv, 2Iy9Hsskj46eQBgw77zsKk, 2S_2Kp2xXEEuNbwtOqdEUQ, 3Mb8fsOC19hhhkphmma5V_, 3WEQyxX5zCtRZzJcbMN6iH, 3gjySlsG181Byy84Ytg2R8, 3pGch8Bez9f8VMc$i961qz</t>
+  </si>
+  <si>
+    <t>2s6_0aRv9889e59zmDeZ6l</t>
+  </si>
+  <si>
+    <t>0$p2yq41j9ruEy6V6tIh2v</t>
+  </si>
+  <si>
+    <t>2KAYYodpPD29Ui4SHOaqvV</t>
+  </si>
+  <si>
+    <t>18ovLmE_v59vE2MWqJWWlV</t>
+  </si>
+  <si>
+    <t>0LTQh8B7X7SvC7KUiiThMD, 1PjFG3xAD0yvsi1rpU5$if</t>
+  </si>
+  <si>
+    <t>1cqwfrVO10XAAQoHwMWBY0</t>
+  </si>
+  <si>
+    <t>0Qt0xbz210ePk1ETgcTRAe</t>
+  </si>
+  <si>
+    <t>0A1FPOLpbDSRZQHbgifANJ, 0ggfX4ROvE$gn9oI2po6hs, 0iyXO7t2zBVAjFehekF44y, 0sYvMtXFvFog3SsZPbibSv, 0zaeuovYj4HxUQbxNDVVuv, 17H4UtdcH30x2aVWwiHzpl, 19yOQyJEn8wh5sF2LlSO8h, 1Cv_QD$SL3tAYxgT$2d4ki, 2MUujldmDF_hf6Kl51X1Hd, 2Vr3mF39f16Oqo$Lzh1x82, 3bqSUryV57I8lezJPgz9RY, 3fVc5k8UXBUuj626Ve2F8S</t>
+  </si>
+  <si>
+    <t>2ShMSTKej0vRXTBV2HRvE9, 2cphe79ET2RP1zKGpM43B$, 3vS9$ioef8ev_qzyK6NV6L</t>
+  </si>
+  <si>
+    <t>1ziUsWhzn78fM8rbtgkP3T, 3zEfxnCBj6sAxTBWhy8ur3</t>
+  </si>
+  <si>
+    <t>0Q9ijkiQX4WhhnplWe_zdJ</t>
+  </si>
+  <si>
+    <t>3KAORRhsnAKwP86D6sr$3l</t>
+  </si>
+  <si>
+    <t>0SsV_3mGL8jQnkPuwroY3_, 3TcJ$990X3ivnq$qgRm$vO</t>
+  </si>
+  <si>
+    <t>003gYzC8LEduA338bYwucG, 0TisxChxjEBOUhNCGFPe5W, 0_BHgmglj3egU7C5xU9ViK, 0oObqa8CrBxRX_rInOt3c9, 0tWf2kC1586uZ0sri7zb1n, 1I7IP$U65BCfKTkdnLbcd2, 1VzOtYuMDEhAu6QSpNDCN5, 1d8yru8NX6o90r$HjR_aRA, 1dFOwotOTCfAsAhSMBtTej, 1pD1pQ8dvCURhHWak1nEUO, 1w$b_g_$93zPxspdDWnPhI, 2ADk9oWpT7Ah0MjwZ8QsOz, 2v1Xk0MT1048VGbEtULKUb, 3$y1RDlEH0RRtkBIhMh7P2, 3GGqNyT7T26Qo_U3sVoYMy, 3JsInGZFTBEPodl2bEFnyx</t>
+  </si>
+  <si>
+    <t>2Xs6SIZyn3xvF3_RRaA6Fa</t>
+  </si>
+  <si>
+    <t>0M206jXKP8eAaUepdqB7iE, 3V9sbZj5LCafTPex$waLzL</t>
+  </si>
+  <si>
+    <t>0W4yXqkDzB5O81QntMj9c5, 280x3tfED1EOT34xdRY2ZA</t>
+  </si>
+  <si>
+    <t>1$RYaSg8X0JxDf6yNcAH30</t>
+  </si>
+  <si>
+    <t>1_HXy1qTTDahuLTlluTa95, 3gGcyYuafEPhCroukrmjZ7, 3iPsvIziH3_AeEtdPN$vau</t>
+  </si>
+  <si>
+    <t>0mqAnSSW1EmO318nABjLZj, 1TryAnXErCXw_zBNYqupuU, 3AFAWlkE99MgdF$DN0_GFR</t>
+  </si>
+  <si>
+    <t>0qfC$pra906wRpgxs$S$Wk, 1PUaeZ3ZrBmxeXjNjnOnHd</t>
+  </si>
+  <si>
+    <t>0vGnRSDojASeua7XxAW1bb</t>
+  </si>
+  <si>
+    <t>3mdc60Mwv2tPnYFvWNhknL</t>
+  </si>
+  <si>
+    <t>0f1Ttarxj3$OA$lHODYeRs</t>
+  </si>
+  <si>
+    <t>0s$ynE1pz43grKFhHey8dX</t>
+  </si>
+  <si>
+    <t>2UkroYiVTF1hfZ3bDpwLnM</t>
+  </si>
+  <si>
+    <t>39NjWXkNLEHOv8CGOj4lg8</t>
+  </si>
+  <si>
+    <t>0f1Q$uOUP7ovO4kZkr7IW_</t>
+  </si>
+  <si>
+    <t>1542, 1548, 1549, 1550, 1551</t>
+  </si>
+  <si>
+    <t>1634</t>
+  </si>
+  <si>
+    <t>1644</t>
+  </si>
+  <si>
+    <t>1623, 1629, 1630</t>
+  </si>
+  <si>
+    <t>1635, 1636, 1642</t>
+  </si>
+  <si>
+    <t>1631, 1632, 1633, 1637, 1638, 1639</t>
+  </si>
+  <si>
+    <t>1643</t>
+  </si>
+  <si>
+    <t>1640, 1641</t>
+  </si>
+  <si>
+    <t>1624, 1625</t>
+  </si>
+  <si>
+    <t>1620, 1621</t>
+  </si>
+  <si>
+    <t>1622</t>
+  </si>
+  <si>
+    <t>1593</t>
+  </si>
+  <si>
+    <t>1595</t>
+  </si>
+  <si>
+    <t>1597</t>
+  </si>
+  <si>
+    <t>1596</t>
+  </si>
+  <si>
+    <t>1598</t>
+  </si>
+  <si>
+    <t>1602, 1603</t>
+  </si>
+  <si>
+    <t>1599</t>
+  </si>
+  <si>
+    <t>1613, 1614, 1615</t>
+  </si>
+  <si>
+    <t>1606</t>
+  </si>
+  <si>
+    <t>1605</t>
+  </si>
+  <si>
+    <t>1604</t>
+  </si>
+  <si>
+    <t>1554</t>
+  </si>
+  <si>
+    <t>1557, 1558</t>
+  </si>
+  <si>
+    <t>1552</t>
+  </si>
+  <si>
+    <t>1553</t>
+  </si>
+  <si>
+    <t>1649, 1655, 1657, 1659, 1662, 1665</t>
+  </si>
+  <si>
+    <t>1646, 1647, 1648, 1651, 1652, 1653, 1654, 1656, 1658, 1660, 1661, 1663, 1664</t>
+  </si>
+  <si>
+    <t>1586</t>
+  </si>
+  <si>
+    <t>1587</t>
+  </si>
+  <si>
+    <t>1585</t>
+  </si>
+  <si>
+    <t>1584</t>
+  </si>
+  <si>
+    <t>1589, 1594</t>
+  </si>
+  <si>
+    <t>1645</t>
+  </si>
+  <si>
+    <t>1650</t>
+  </si>
+  <si>
+    <t>1535, 1536, 1537, 1538, 1539, 1540, 1541, 1543, 1544, 1545, 1546, 1547</t>
+  </si>
+  <si>
+    <t>1626, 1627, 1628</t>
+  </si>
+  <si>
+    <t>1618, 1619</t>
+  </si>
+  <si>
+    <t>1578</t>
+  </si>
+  <si>
+    <t>1555</t>
+  </si>
+  <si>
+    <t>1562, 1563</t>
+  </si>
+  <si>
+    <t>1565, 1566, 1567, 1568, 1569, 1570, 1571, 1572, 1573, 1574, 1575, 1576, 1577, 1579, 1580, 1581</t>
+  </si>
+  <si>
+    <t>1556</t>
+  </si>
+  <si>
+    <t>1561, 1564</t>
+  </si>
+  <si>
+    <t>1582, 1583</t>
+  </si>
+  <si>
+    <t>1588</t>
+  </si>
+  <si>
+    <t>1609, 1616, 1617</t>
+  </si>
+  <si>
+    <t>1610, 1611, 1612</t>
+  </si>
+  <si>
+    <t>1559, 1560</t>
+  </si>
+  <si>
+    <t>1601</t>
+  </si>
+  <si>
+    <t>1608</t>
+  </si>
+  <si>
+    <t>1600</t>
+  </si>
+  <si>
+    <t>1590</t>
+  </si>
+  <si>
+    <t>1591</t>
+  </si>
+  <si>
+    <t>1607</t>
+  </si>
+  <si>
+    <t>1592</t>
   </si>
   <si>
     <t>GrossArea</t>
   </si>
   <si>
     <t>GrossVolume</t>
+  </si>
+  <si>
+    <t>IfcSpace</t>
   </si>
 </sst>
 </file>
@@ -1376,10 +1511,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:W69"/>
+  <dimension ref="A1:Y70"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:23">
+    <row r="1" spans="1:25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1449,132 +1584,144 @@
       <c r="W1" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="2" spans="1:23">
+      <c r="X1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:25">
       <c r="A2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="G2" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="3" spans="1:23">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25">
       <c r="A3" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D3" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="G3" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="4" spans="1:23">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25">
       <c r="A4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B4" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C4" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D4" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="G4" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="I4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J4" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="K4" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="L4" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="M4" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="N4" t="s">
-        <v>245</v>
+        <v>260</v>
       </c>
       <c r="O4" t="s">
-        <v>249</v>
+        <v>265</v>
       </c>
       <c r="P4" t="s">
-        <v>291</v>
+        <v>321</v>
       </c>
       <c r="Q4">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="R4" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="S4">
-        <v>224.5725255</v>
+        <v>80.0549015</v>
       </c>
       <c r="T4">
-        <v>44.5051765</v>
+        <v>0</v>
       </c>
       <c r="U4">
-        <v>89.90167199999999</v>
+        <v>36.1246745</v>
       </c>
       <c r="V4">
-        <v>29.57241</v>
+        <v>0</v>
       </c>
       <c r="W4">
-        <v>60.593267</v>
-      </c>
-    </row>
-    <row r="5" spans="1:23">
+        <v>43.930227</v>
+      </c>
+      <c r="X4">
+        <v>0</v>
+      </c>
+      <c r="Y4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25">
       <c r="A5" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C5" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D5" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="G5" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="6" spans="1:23">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25">
       <c r="A6" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B6" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C6" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E6">
         <v>10.4</v>
@@ -1583,69 +1730,75 @@
         <v>1</v>
       </c>
       <c r="G6" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="H6">
         <v>390</v>
       </c>
       <c r="I6" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K6" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="L6" t="s">
+        <v>32</v>
+      </c>
+      <c r="M6" t="s">
+        <v>153</v>
+      </c>
+      <c r="N6" t="s">
+        <v>261</v>
+      </c>
+      <c r="O6" t="s">
+        <v>266</v>
+      </c>
+      <c r="P6" t="s">
+        <v>322</v>
+      </c>
+      <c r="Q6">
+        <v>1</v>
+      </c>
+      <c r="R6" t="s">
+        <v>169</v>
+      </c>
+      <c r="S6">
+        <v>311.9691595</v>
+      </c>
+      <c r="T6">
+        <v>311.9691595</v>
+      </c>
+      <c r="U6">
+        <v>0</v>
+      </c>
+      <c r="V6">
+        <v>0</v>
+      </c>
+      <c r="W6">
+        <v>0</v>
+      </c>
+      <c r="X6">
+        <v>0</v>
+      </c>
+      <c r="Y6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25">
+      <c r="A7" t="s">
         <v>30</v>
       </c>
-      <c r="M6" t="s">
-        <v>151</v>
-      </c>
-      <c r="N6" t="s">
-        <v>246</v>
-      </c>
-      <c r="O6" t="s">
-        <v>250</v>
-      </c>
-      <c r="P6" t="s">
-        <v>292</v>
-      </c>
-      <c r="Q6">
-        <v>2</v>
-      </c>
-      <c r="R6" t="s">
-        <v>167</v>
-      </c>
-      <c r="S6">
-        <v>517.6972254999999</v>
-      </c>
-      <c r="T6">
-        <v>0</v>
-      </c>
-      <c r="U6">
-        <v>0</v>
-      </c>
-      <c r="V6">
-        <v>0</v>
-      </c>
-      <c r="W6">
-        <v>517.6972254999999</v>
-      </c>
-    </row>
-    <row r="7" spans="1:23">
-      <c r="A7" t="s">
-        <v>28</v>
-      </c>
       <c r="B7" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C7" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D7" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E7">
         <v>10.4</v>
@@ -1654,165 +1807,228 @@
         <v>1</v>
       </c>
       <c r="G7" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="H7">
         <v>16</v>
       </c>
-    </row>
-    <row r="8" spans="1:23">
+      <c r="I7" t="s">
+        <v>30</v>
+      </c>
+      <c r="J7" t="s">
+        <v>231</v>
+      </c>
+      <c r="K7" t="s">
+        <v>246</v>
+      </c>
+      <c r="L7" t="s">
+        <v>67</v>
+      </c>
+      <c r="M7" t="s">
+        <v>153</v>
+      </c>
+      <c r="N7" t="s">
+        <v>261</v>
+      </c>
+      <c r="O7" t="s">
+        <v>267</v>
+      </c>
+      <c r="P7" t="s">
+        <v>323</v>
+      </c>
+      <c r="Q7">
+        <v>1</v>
+      </c>
+      <c r="R7" t="s">
+        <v>170</v>
+      </c>
+      <c r="S7">
+        <v>51.829968</v>
+      </c>
+      <c r="T7">
+        <v>51.829968</v>
+      </c>
+      <c r="U7">
+        <v>0</v>
+      </c>
+      <c r="V7">
+        <v>0</v>
+      </c>
+      <c r="W7">
+        <v>0</v>
+      </c>
+      <c r="X7">
+        <v>0</v>
+      </c>
+      <c r="Y7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25">
       <c r="A8" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B8" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C8" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D8" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G8" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="9" spans="1:23">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25">
       <c r="A9" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B9" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C9" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D9" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G9" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="I9" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J9" t="s">
         <v>231</v>
       </c>
       <c r="K9" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="L9" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="M9" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="N9" t="s">
-        <v>246</v>
+        <v>261</v>
       </c>
       <c r="O9" t="s">
-        <v>251</v>
+        <v>268</v>
       </c>
       <c r="P9" t="s">
-        <v>293</v>
+        <v>324</v>
       </c>
       <c r="Q9">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R9" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="S9">
-        <v>1700.4758295</v>
+        <v>424.5565245</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>424.5565245</v>
       </c>
       <c r="U9">
         <v>0</v>
       </c>
       <c r="V9">
-        <v>1700.4758295</v>
+        <v>0</v>
       </c>
       <c r="W9">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:23">
+      <c r="X9">
+        <v>0</v>
+      </c>
+      <c r="Y9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25">
       <c r="A10" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B10" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C10" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D10" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G10" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="I10" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J10" t="s">
         <v>231</v>
       </c>
       <c r="K10" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="L10" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="M10" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="N10" t="s">
-        <v>246</v>
+        <v>261</v>
       </c>
       <c r="O10" t="s">
-        <v>252</v>
+        <v>269</v>
       </c>
       <c r="P10" t="s">
-        <v>294</v>
+        <v>325</v>
       </c>
       <c r="Q10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R10" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="S10">
-        <v>149.781966</v>
+        <v>438.508773</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>438.508773</v>
       </c>
       <c r="U10">
         <v>0</v>
       </c>
       <c r="V10">
-        <v>149.781966</v>
+        <v>0</v>
       </c>
       <c r="W10">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:23">
+      <c r="X10">
+        <v>0</v>
+      </c>
+      <c r="Y10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25">
       <c r="A11" t="s">
+        <v>34</v>
+      </c>
+      <c r="B11" t="s">
+        <v>96</v>
+      </c>
+      <c r="C11" t="s">
+        <v>153</v>
+      </c>
+      <c r="D11" t="s">
         <v>32</v>
-      </c>
-      <c r="B11" t="s">
-        <v>94</v>
-      </c>
-      <c r="C11" t="s">
-        <v>151</v>
-      </c>
-      <c r="D11" t="s">
-        <v>30</v>
       </c>
       <c r="E11">
         <v>10.8</v>
@@ -1821,92 +2037,149 @@
         <v>1</v>
       </c>
       <c r="G11" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="H11">
         <v>400</v>
       </c>
       <c r="I11" t="s">
+        <v>34</v>
+      </c>
+      <c r="J11" t="s">
+        <v>231</v>
+      </c>
+      <c r="K11" t="s">
+        <v>246</v>
+      </c>
+      <c r="L11" t="s">
         <v>32</v>
       </c>
-      <c r="J11" t="s">
-        <v>232</v>
-      </c>
-      <c r="K11" t="s">
-        <v>240</v>
-      </c>
-      <c r="L11" t="s">
-        <v>30</v>
-      </c>
       <c r="M11" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="N11" t="s">
-        <v>246</v>
+        <v>261</v>
       </c>
       <c r="O11" t="s">
-        <v>253</v>
+        <v>270</v>
       </c>
       <c r="P11" t="s">
-        <v>295</v>
+        <v>326</v>
       </c>
       <c r="Q11">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R11" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="S11">
-        <v>1405.3773035</v>
+        <v>1503.512742</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>1503.512742</v>
       </c>
       <c r="U11">
         <v>0</v>
       </c>
       <c r="V11">
-        <v>1105.1280485</v>
+        <v>0</v>
       </c>
       <c r="W11">
-        <v>300.249255</v>
-      </c>
-    </row>
-    <row r="12" spans="1:23">
+        <v>0</v>
+      </c>
+      <c r="X11">
+        <v>0</v>
+      </c>
+      <c r="Y11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25">
       <c r="A12" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B12" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C12" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D12" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="F12">
         <v>1</v>
       </c>
       <c r="G12" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H12">
         <v>54</v>
       </c>
-    </row>
-    <row r="13" spans="1:23">
+      <c r="I12" t="s">
+        <v>35</v>
+      </c>
+      <c r="J12" t="s">
+        <v>231</v>
+      </c>
+      <c r="K12" t="s">
+        <v>246</v>
+      </c>
+      <c r="L12" t="s">
+        <v>161</v>
+      </c>
+      <c r="M12" t="s">
+        <v>153</v>
+      </c>
+      <c r="N12" t="s">
+        <v>261</v>
+      </c>
+      <c r="O12" t="s">
+        <v>271</v>
+      </c>
+      <c r="P12" t="s">
+        <v>327</v>
+      </c>
+      <c r="Q12">
+        <v>1</v>
+      </c>
+      <c r="R12" t="s">
+        <v>175</v>
+      </c>
+      <c r="S12">
+        <v>73.743488</v>
+      </c>
+      <c r="T12">
+        <v>73.743488</v>
+      </c>
+      <c r="U12">
+        <v>0</v>
+      </c>
+      <c r="V12">
+        <v>0</v>
+      </c>
+      <c r="W12">
+        <v>0</v>
+      </c>
+      <c r="X12">
+        <v>0</v>
+      </c>
+      <c r="Y12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25">
       <c r="A13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B13" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C13" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D13" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E13">
         <v>10.8</v>
@@ -1915,46 +2188,46 @@
         <v>2</v>
       </c>
       <c r="G13" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="H13">
         <v>300</v>
       </c>
       <c r="I13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J13" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K13" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="L13" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="M13" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="N13" t="s">
-        <v>246</v>
+        <v>261</v>
       </c>
       <c r="O13" t="s">
-        <v>254</v>
+        <v>272</v>
       </c>
       <c r="P13" t="s">
-        <v>296</v>
+        <v>328</v>
       </c>
       <c r="Q13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R13" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="S13">
-        <v>192.714786</v>
+        <v>450.5657505</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>450.5657505</v>
       </c>
       <c r="U13">
         <v>0</v>
@@ -1963,21 +2236,27 @@
         <v>0</v>
       </c>
       <c r="W13">
-        <v>192.714786</v>
-      </c>
-    </row>
-    <row r="14" spans="1:23">
+        <v>0</v>
+      </c>
+      <c r="X13">
+        <v>0</v>
+      </c>
+      <c r="Y13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25">
       <c r="A14" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B14" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C14" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D14" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E14">
         <v>10.1</v>
@@ -1986,216 +2265,132 @@
         <v>1</v>
       </c>
       <c r="G14" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="H14">
         <v>12</v>
       </c>
-      <c r="I14" t="s">
-        <v>35</v>
-      </c>
-      <c r="J14" t="s">
-        <v>231</v>
-      </c>
-      <c r="K14" t="s">
-        <v>239</v>
-      </c>
-      <c r="L14" t="s">
-        <v>30</v>
-      </c>
-      <c r="M14" t="s">
-        <v>151</v>
-      </c>
-      <c r="N14" t="s">
-        <v>246</v>
-      </c>
-      <c r="O14" t="s">
-        <v>255</v>
-      </c>
-      <c r="P14" t="s">
-        <v>297</v>
-      </c>
-      <c r="Q14">
-        <v>1</v>
-      </c>
-      <c r="R14" t="s">
-        <v>175</v>
-      </c>
-      <c r="S14">
-        <v>12.501687</v>
-      </c>
-      <c r="T14">
-        <v>0</v>
-      </c>
-      <c r="U14">
-        <v>0</v>
-      </c>
-      <c r="V14">
-        <v>12.501687</v>
-      </c>
-      <c r="W14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:23">
+    </row>
+    <row r="15" spans="1:25">
       <c r="A15" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B15" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C15" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D15" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G15" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="I15" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J15" t="s">
         <v>231</v>
       </c>
       <c r="K15" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="L15" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="M15" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="N15" t="s">
-        <v>246</v>
+        <v>261</v>
       </c>
       <c r="O15" t="s">
-        <v>256</v>
+        <v>273</v>
       </c>
       <c r="P15" t="s">
-        <v>298</v>
+        <v>329</v>
       </c>
       <c r="Q15">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="R15" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="S15">
-        <v>1624.359665</v>
+        <v>1079.9930175</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>1079.9930175</v>
       </c>
       <c r="U15">
         <v>0</v>
       </c>
       <c r="V15">
-        <v>1624.359665</v>
+        <v>0</v>
       </c>
       <c r="W15">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:23">
+      <c r="X15">
+        <v>0</v>
+      </c>
+      <c r="Y15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25">
       <c r="A16" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B16" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C16" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D16" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E16">
         <v>10.1</v>
       </c>
       <c r="G16" t="s">
-        <v>177</v>
-      </c>
-      <c r="I16" t="s">
-        <v>37</v>
-      </c>
-      <c r="J16" t="s">
-        <v>231</v>
-      </c>
-      <c r="K16" t="s">
-        <v>239</v>
-      </c>
-      <c r="L16" t="s">
-        <v>30</v>
-      </c>
-      <c r="M16" t="s">
-        <v>151</v>
-      </c>
-      <c r="N16" t="s">
-        <v>246</v>
-      </c>
-      <c r="O16" t="s">
-        <v>257</v>
-      </c>
-      <c r="P16" t="s">
-        <v>299</v>
-      </c>
-      <c r="Q16">
-        <v>1</v>
-      </c>
-      <c r="R16" t="s">
-        <v>177</v>
-      </c>
-      <c r="S16">
-        <v>6.683796</v>
-      </c>
-      <c r="T16">
-        <v>0</v>
-      </c>
-      <c r="U16">
-        <v>0</v>
-      </c>
-      <c r="V16">
-        <v>6.683796</v>
-      </c>
-      <c r="W16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:23">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="17" spans="1:25">
       <c r="A17" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B17" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C17" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D17" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E17">
         <v>10.1</v>
       </c>
       <c r="G17" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="18" spans="1:23">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="18" spans="1:25">
       <c r="A18" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B18" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C18" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D18" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E18">
         <v>1.2</v>
@@ -2204,43 +2399,43 @@
         <v>1</v>
       </c>
       <c r="G18" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="H18">
         <v>72</v>
       </c>
       <c r="I18" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="J18" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="K18" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="L18" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="M18" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="N18" t="s">
-        <v>245</v>
+        <v>260</v>
       </c>
       <c r="O18" t="s">
-        <v>258</v>
+        <v>274</v>
       </c>
       <c r="P18" t="s">
-        <v>300</v>
+        <v>330</v>
       </c>
       <c r="Q18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R18" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="S18">
-        <v>69.21536450000001</v>
+        <v>97.30420100000001</v>
       </c>
       <c r="T18">
         <v>0</v>
@@ -2249,24 +2444,30 @@
         <v>0</v>
       </c>
       <c r="V18">
-        <v>69.21536450000001</v>
+        <v>0</v>
       </c>
       <c r="W18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:23">
+        <v>97.30420100000001</v>
+      </c>
+      <c r="X18">
+        <v>0</v>
+      </c>
+      <c r="Y18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:25">
       <c r="A19" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B19" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C19" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D19" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E19">
         <v>1.2</v>
@@ -2275,43 +2476,43 @@
         <v>1</v>
       </c>
       <c r="G19" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="H19">
         <v>54</v>
       </c>
       <c r="I19" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J19" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="K19" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="L19" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="M19" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="N19" t="s">
-        <v>245</v>
+        <v>260</v>
       </c>
       <c r="O19" t="s">
-        <v>259</v>
+        <v>275</v>
       </c>
       <c r="P19" t="s">
-        <v>301</v>
+        <v>331</v>
       </c>
       <c r="Q19">
         <v>1</v>
       </c>
       <c r="R19" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="S19">
-        <v>58.270363</v>
+        <v>48.652963</v>
       </c>
       <c r="T19">
         <v>0</v>
@@ -2320,24 +2521,30 @@
         <v>0</v>
       </c>
       <c r="V19">
-        <v>58.270363</v>
+        <v>0</v>
       </c>
       <c r="W19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:23">
+        <v>48.652963</v>
+      </c>
+      <c r="X19">
+        <v>0</v>
+      </c>
+      <c r="Y19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:25">
       <c r="A20" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B20" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C20" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D20" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E20">
         <v>2.1</v>
@@ -2346,43 +2553,43 @@
         <v>1</v>
       </c>
       <c r="G20" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="H20">
         <v>18</v>
       </c>
       <c r="I20" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="J20" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="K20" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="L20" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="M20" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="N20" t="s">
-        <v>245</v>
+        <v>260</v>
       </c>
       <c r="O20" t="s">
-        <v>260</v>
+        <v>276</v>
       </c>
       <c r="P20" t="s">
-        <v>302</v>
+        <v>332</v>
       </c>
       <c r="Q20">
         <v>1</v>
       </c>
       <c r="R20" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="S20">
-        <v>19.561439</v>
+        <v>18.100976</v>
       </c>
       <c r="T20">
         <v>0</v>
@@ -2391,24 +2598,30 @@
         <v>0</v>
       </c>
       <c r="V20">
-        <v>19.561439</v>
+        <v>0</v>
       </c>
       <c r="W20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:23">
+        <v>18.100976</v>
+      </c>
+      <c r="X20">
+        <v>0</v>
+      </c>
+      <c r="Y20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:25">
       <c r="A21" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C21" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D21" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E21">
         <v>3.8</v>
@@ -2417,43 +2630,43 @@
         <v>1</v>
       </c>
       <c r="G21" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="H21">
         <v>55</v>
       </c>
       <c r="I21" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J21" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="K21" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="L21" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="M21" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="N21" t="s">
-        <v>245</v>
+        <v>260</v>
       </c>
       <c r="O21" t="s">
-        <v>261</v>
+        <v>277</v>
       </c>
       <c r="P21" t="s">
-        <v>303</v>
+        <v>333</v>
       </c>
       <c r="Q21">
         <v>1</v>
       </c>
       <c r="R21" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="S21">
-        <v>47.7329045</v>
+        <v>52.0864025</v>
       </c>
       <c r="T21">
         <v>0</v>
@@ -2462,24 +2675,30 @@
         <v>0</v>
       </c>
       <c r="V21">
-        <v>47.7329045</v>
+        <v>0</v>
       </c>
       <c r="W21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:23">
+        <v>52.0864025</v>
+      </c>
+      <c r="X21">
+        <v>0</v>
+      </c>
+      <c r="Y21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:25">
       <c r="A22" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B22" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C22" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D22" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E22">
         <v>4.4</v>
@@ -2488,24 +2707,75 @@
         <v>1</v>
       </c>
       <c r="G22" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="H22">
         <v>7</v>
       </c>
-    </row>
-    <row r="23" spans="1:23">
+      <c r="I22" t="s">
+        <v>45</v>
+      </c>
+      <c r="J22" t="s">
+        <v>232</v>
+      </c>
+      <c r="K22" t="s">
+        <v>247</v>
+      </c>
+      <c r="L22" t="s">
+        <v>162</v>
+      </c>
+      <c r="M22" t="s">
+        <v>154</v>
+      </c>
+      <c r="N22" t="s">
+        <v>260</v>
+      </c>
+      <c r="O22" t="s">
+        <v>278</v>
+      </c>
+      <c r="P22" t="s">
+        <v>334</v>
+      </c>
+      <c r="Q22">
+        <v>1</v>
+      </c>
+      <c r="R22" t="s">
+        <v>185</v>
+      </c>
+      <c r="S22">
+        <v>7.1488355</v>
+      </c>
+      <c r="T22">
+        <v>0</v>
+      </c>
+      <c r="U22">
+        <v>0</v>
+      </c>
+      <c r="V22">
+        <v>0</v>
+      </c>
+      <c r="W22">
+        <v>7.1488355</v>
+      </c>
+      <c r="X22">
+        <v>0</v>
+      </c>
+      <c r="Y22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:25">
       <c r="A23" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B23" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C23" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D23" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E23">
         <v>4.4</v>
@@ -2514,24 +2784,75 @@
         <v>1</v>
       </c>
       <c r="G23" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="H23">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="1:23">
+      <c r="I23" t="s">
+        <v>46</v>
+      </c>
+      <c r="J23" t="s">
+        <v>232</v>
+      </c>
+      <c r="K23" t="s">
+        <v>247</v>
+      </c>
+      <c r="L23" t="s">
+        <v>162</v>
+      </c>
+      <c r="M23" t="s">
+        <v>154</v>
+      </c>
+      <c r="N23" t="s">
+        <v>260</v>
+      </c>
+      <c r="O23" t="s">
+        <v>279</v>
+      </c>
+      <c r="P23" t="s">
+        <v>335</v>
+      </c>
+      <c r="Q23">
+        <v>1</v>
+      </c>
+      <c r="R23" t="s">
+        <v>186</v>
+      </c>
+      <c r="S23">
+        <v>5.3788925</v>
+      </c>
+      <c r="T23">
+        <v>0</v>
+      </c>
+      <c r="U23">
+        <v>0</v>
+      </c>
+      <c r="V23">
+        <v>0</v>
+      </c>
+      <c r="W23">
+        <v>5.3788925</v>
+      </c>
+      <c r="X23">
+        <v>0</v>
+      </c>
+      <c r="Y23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:25">
       <c r="A24" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B24" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C24" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D24" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E24">
         <v>4.3</v>
@@ -2540,24 +2861,75 @@
         <v>1</v>
       </c>
       <c r="G24" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="H24">
         <v>7</v>
       </c>
-    </row>
-    <row r="25" spans="1:23">
+      <c r="I24" t="s">
+        <v>47</v>
+      </c>
+      <c r="J24" t="s">
+        <v>232</v>
+      </c>
+      <c r="K24" t="s">
+        <v>247</v>
+      </c>
+      <c r="L24" t="s">
+        <v>162</v>
+      </c>
+      <c r="M24" t="s">
+        <v>154</v>
+      </c>
+      <c r="N24" t="s">
+        <v>260</v>
+      </c>
+      <c r="O24" t="s">
+        <v>280</v>
+      </c>
+      <c r="P24" t="s">
+        <v>336</v>
+      </c>
+      <c r="Q24">
+        <v>1</v>
+      </c>
+      <c r="R24" t="s">
+        <v>187</v>
+      </c>
+      <c r="S24">
+        <v>6.7310435</v>
+      </c>
+      <c r="T24">
+        <v>0</v>
+      </c>
+      <c r="U24">
+        <v>0</v>
+      </c>
+      <c r="V24">
+        <v>0</v>
+      </c>
+      <c r="W24">
+        <v>6.7310435</v>
+      </c>
+      <c r="X24">
+        <v>0</v>
+      </c>
+      <c r="Y24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:25">
       <c r="A25" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B25" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C25" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D25" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E25">
         <v>1.5</v>
@@ -2566,43 +2938,43 @@
         <v>1</v>
       </c>
       <c r="G25" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="H25">
         <v>72</v>
       </c>
       <c r="I25" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="J25" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="K25" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="L25" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="M25" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="N25" t="s">
-        <v>245</v>
+        <v>260</v>
       </c>
       <c r="O25" t="s">
-        <v>262</v>
+        <v>281</v>
       </c>
       <c r="P25" t="s">
-        <v>304</v>
+        <v>337</v>
       </c>
       <c r="Q25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R25" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="S25">
-        <v>77.20383200000001</v>
+        <v>120.5809505</v>
       </c>
       <c r="T25">
         <v>0</v>
@@ -2611,24 +2983,30 @@
         <v>0</v>
       </c>
       <c r="V25">
-        <v>77.20383200000001</v>
+        <v>0</v>
       </c>
       <c r="W25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:23">
+        <v>37.01257</v>
+      </c>
+      <c r="X25">
+        <v>0</v>
+      </c>
+      <c r="Y25">
+        <v>83.5683805</v>
+      </c>
+    </row>
+    <row r="26" spans="1:25">
       <c r="A26" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B26" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C26" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D26" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E26">
         <v>7.1</v>
@@ -2637,24 +3015,75 @@
         <v>1</v>
       </c>
       <c r="G26" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="H26">
         <v>1</v>
       </c>
-    </row>
-    <row r="27" spans="1:23">
+      <c r="I26" t="s">
+        <v>49</v>
+      </c>
+      <c r="J26" t="s">
+        <v>232</v>
+      </c>
+      <c r="K26" t="s">
+        <v>247</v>
+      </c>
+      <c r="L26" t="s">
+        <v>163</v>
+      </c>
+      <c r="M26" t="s">
+        <v>154</v>
+      </c>
+      <c r="N26" t="s">
+        <v>260</v>
+      </c>
+      <c r="O26" t="s">
+        <v>282</v>
+      </c>
+      <c r="P26" t="s">
+        <v>338</v>
+      </c>
+      <c r="Q26">
+        <v>1</v>
+      </c>
+      <c r="R26" t="s">
+        <v>189</v>
+      </c>
+      <c r="S26">
+        <v>6.217429</v>
+      </c>
+      <c r="T26">
+        <v>0</v>
+      </c>
+      <c r="U26">
+        <v>0</v>
+      </c>
+      <c r="V26">
+        <v>0</v>
+      </c>
+      <c r="W26">
+        <v>6.217429</v>
+      </c>
+      <c r="X26">
+        <v>0</v>
+      </c>
+      <c r="Y26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:25">
       <c r="A27" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B27" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C27" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D27" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E27">
         <v>7.2</v>
@@ -2663,24 +3092,75 @@
         <v>1</v>
       </c>
       <c r="G27" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="H27">
         <v>108</v>
       </c>
-    </row>
-    <row r="28" spans="1:23">
+      <c r="I27" t="s">
+        <v>50</v>
+      </c>
+      <c r="J27" t="s">
+        <v>232</v>
+      </c>
+      <c r="K27" t="s">
+        <v>247</v>
+      </c>
+      <c r="L27" t="s">
+        <v>163</v>
+      </c>
+      <c r="M27" t="s">
+        <v>154</v>
+      </c>
+      <c r="N27" t="s">
+        <v>260</v>
+      </c>
+      <c r="O27" t="s">
+        <v>283</v>
+      </c>
+      <c r="P27" t="s">
+        <v>339</v>
+      </c>
+      <c r="Q27">
+        <v>3</v>
+      </c>
+      <c r="R27" t="s">
+        <v>190</v>
+      </c>
+      <c r="S27">
+        <v>113.1970605</v>
+      </c>
+      <c r="T27">
+        <v>0</v>
+      </c>
+      <c r="U27">
+        <v>0</v>
+      </c>
+      <c r="V27">
+        <v>0</v>
+      </c>
+      <c r="W27">
+        <v>113.1970605</v>
+      </c>
+      <c r="X27">
+        <v>0</v>
+      </c>
+      <c r="Y27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:25">
       <c r="A28" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B28" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C28" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D28" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E28">
         <v>7.1</v>
@@ -2689,24 +3169,75 @@
         <v>1</v>
       </c>
       <c r="G28" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="H28">
         <v>2.5</v>
       </c>
-    </row>
-    <row r="29" spans="1:23">
+      <c r="I28" t="s">
+        <v>51</v>
+      </c>
+      <c r="J28" t="s">
+        <v>232</v>
+      </c>
+      <c r="K28" t="s">
+        <v>247</v>
+      </c>
+      <c r="L28" t="s">
+        <v>163</v>
+      </c>
+      <c r="M28" t="s">
+        <v>154</v>
+      </c>
+      <c r="N28" t="s">
+        <v>260</v>
+      </c>
+      <c r="O28" t="s">
+        <v>284</v>
+      </c>
+      <c r="P28" t="s">
+        <v>340</v>
+      </c>
+      <c r="Q28">
+        <v>1</v>
+      </c>
+      <c r="R28" t="s">
+        <v>191</v>
+      </c>
+      <c r="S28">
+        <v>6.3144375</v>
+      </c>
+      <c r="T28">
+        <v>0</v>
+      </c>
+      <c r="U28">
+        <v>0</v>
+      </c>
+      <c r="V28">
+        <v>0</v>
+      </c>
+      <c r="W28">
+        <v>6.3144375</v>
+      </c>
+      <c r="X28">
+        <v>0</v>
+      </c>
+      <c r="Y28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:25">
       <c r="A29" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B29" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C29" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D29" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E29">
         <v>7.1</v>
@@ -2715,24 +3246,75 @@
         <v>1</v>
       </c>
       <c r="G29" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="H29">
         <v>2.5</v>
       </c>
-    </row>
-    <row r="30" spans="1:23">
+      <c r="I29" t="s">
+        <v>52</v>
+      </c>
+      <c r="J29" t="s">
+        <v>232</v>
+      </c>
+      <c r="K29" t="s">
+        <v>247</v>
+      </c>
+      <c r="L29" t="s">
+        <v>163</v>
+      </c>
+      <c r="M29" t="s">
+        <v>154</v>
+      </c>
+      <c r="N29" t="s">
+        <v>260</v>
+      </c>
+      <c r="O29" t="s">
+        <v>285</v>
+      </c>
+      <c r="P29" t="s">
+        <v>341</v>
+      </c>
+      <c r="Q29">
+        <v>1</v>
+      </c>
+      <c r="R29" t="s">
+        <v>192</v>
+      </c>
+      <c r="S29">
+        <v>6.54133</v>
+      </c>
+      <c r="T29">
+        <v>0</v>
+      </c>
+      <c r="U29">
+        <v>0</v>
+      </c>
+      <c r="V29">
+        <v>0</v>
+      </c>
+      <c r="W29">
+        <v>6.54133</v>
+      </c>
+      <c r="X29">
+        <v>0</v>
+      </c>
+      <c r="Y29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:25">
       <c r="A30" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B30" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C30" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D30" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E30">
         <v>7.1</v>
@@ -2741,24 +3323,24 @@
         <v>1</v>
       </c>
       <c r="G30" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="H30">
         <v>2.5</v>
       </c>
     </row>
-    <row r="31" spans="1:23">
+    <row r="31" spans="1:25">
       <c r="A31" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B31" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C31" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D31" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E31">
         <v>7.1</v>
@@ -2767,24 +3349,24 @@
         <v>1</v>
       </c>
       <c r="G31" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H31">
         <v>2.5</v>
       </c>
     </row>
-    <row r="32" spans="1:23">
+    <row r="32" spans="1:25">
       <c r="A32" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B32" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C32" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D32" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E32">
         <v>7.1</v>
@@ -2793,43 +3375,43 @@
         <v>1</v>
       </c>
       <c r="G32" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="H32">
         <v>3</v>
       </c>
       <c r="I32" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="J32" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="K32" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="L32" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="M32" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="N32" t="s">
-        <v>245</v>
+        <v>260</v>
       </c>
       <c r="O32" t="s">
-        <v>263</v>
+        <v>286</v>
       </c>
       <c r="P32" t="s">
-        <v>305</v>
+        <v>342</v>
       </c>
       <c r="Q32">
         <v>1</v>
       </c>
       <c r="R32" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="S32">
-        <v>9.490406999999999</v>
+        <v>3.356215</v>
       </c>
       <c r="T32">
         <v>0</v>
@@ -2838,24 +3420,30 @@
         <v>0</v>
       </c>
       <c r="V32">
-        <v>9.490406999999999</v>
+        <v>0</v>
       </c>
       <c r="W32">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:23">
+        <v>3.356215</v>
+      </c>
+      <c r="X32">
+        <v>0</v>
+      </c>
+      <c r="Y32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:25">
       <c r="A33" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B33" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C33" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D33" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="E33">
         <v>8.300000000000001</v>
@@ -2864,49 +3452,49 @@
         <v>1</v>
       </c>
       <c r="G33" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="H33">
         <v>25</v>
       </c>
       <c r="I33" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="J33" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K33" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="L33" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="M33" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="N33" t="s">
-        <v>245</v>
+        <v>260</v>
       </c>
       <c r="O33" t="s">
-        <v>264</v>
+        <v>287</v>
       </c>
       <c r="P33" t="s">
-        <v>306</v>
+        <v>343</v>
       </c>
       <c r="Q33">
         <v>1</v>
       </c>
       <c r="R33" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="S33">
-        <v>60.963572</v>
+        <v>21.840469</v>
       </c>
       <c r="T33">
         <v>0</v>
       </c>
       <c r="U33">
-        <v>60.963572</v>
+        <v>21.840469</v>
       </c>
       <c r="V33">
         <v>0</v>
@@ -2914,19 +3502,25 @@
       <c r="W33">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="1:23">
+      <c r="X33">
+        <v>0</v>
+      </c>
+      <c r="Y33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:25">
       <c r="A34" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B34" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C34" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D34" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="E34">
         <v>8.5</v>
@@ -2935,24 +3529,75 @@
         <v>2</v>
       </c>
       <c r="G34" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="H34">
         <v>90</v>
       </c>
-    </row>
-    <row r="35" spans="1:23">
+      <c r="I34" t="s">
+        <v>57</v>
+      </c>
+      <c r="J34" t="s">
+        <v>235</v>
+      </c>
+      <c r="K34" t="s">
+        <v>250</v>
+      </c>
+      <c r="L34" t="s">
+        <v>164</v>
+      </c>
+      <c r="M34" t="s">
+        <v>155</v>
+      </c>
+      <c r="N34" t="s">
+        <v>260</v>
+      </c>
+      <c r="O34" t="s">
+        <v>288</v>
+      </c>
+      <c r="P34" t="s">
+        <v>344</v>
+      </c>
+      <c r="Q34">
+        <v>2</v>
+      </c>
+      <c r="R34" t="s">
+        <v>197</v>
+      </c>
+      <c r="S34">
+        <v>64.9122115</v>
+      </c>
+      <c r="T34">
+        <v>45.3332775</v>
+      </c>
+      <c r="U34">
+        <v>19.578934</v>
+      </c>
+      <c r="V34">
+        <v>0</v>
+      </c>
+      <c r="W34">
+        <v>0</v>
+      </c>
+      <c r="X34">
+        <v>0</v>
+      </c>
+      <c r="Y34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:25">
       <c r="A35" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B35" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C35" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D35" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="E35">
         <v>8.1</v>
@@ -2961,43 +3606,43 @@
         <v>1</v>
       </c>
       <c r="G35" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="H35">
         <v>150</v>
       </c>
       <c r="I35" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="J35" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="K35" t="s">
-        <v>238</v>
+        <v>251</v>
       </c>
       <c r="L35" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="M35" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="N35" t="s">
-        <v>245</v>
+        <v>260</v>
       </c>
       <c r="O35" t="s">
-        <v>265</v>
+        <v>289</v>
       </c>
       <c r="P35" t="s">
-        <v>307</v>
+        <v>345</v>
       </c>
       <c r="Q35">
         <v>1</v>
       </c>
       <c r="R35" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="S35">
-        <v>15.56272</v>
+        <v>108.9698425</v>
       </c>
       <c r="T35">
         <v>0</v>
@@ -3006,24 +3651,30 @@
         <v>0</v>
       </c>
       <c r="V35">
-        <v>0</v>
+        <v>108.9698425</v>
       </c>
       <c r="W35">
-        <v>15.56272</v>
-      </c>
-    </row>
-    <row r="36" spans="1:23">
+        <v>0</v>
+      </c>
+      <c r="X35">
+        <v>0</v>
+      </c>
+      <c r="Y35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:25">
       <c r="A36" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B36" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C36" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D36" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="E36">
         <v>8.300000000000001</v>
@@ -3032,123 +3683,186 @@
         <v>1</v>
       </c>
       <c r="G36" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="H36">
         <v>40</v>
       </c>
-    </row>
-    <row r="37" spans="1:23">
+      <c r="I36" t="s">
+        <v>59</v>
+      </c>
+      <c r="J36" t="s">
+        <v>231</v>
+      </c>
+      <c r="K36" t="s">
+        <v>246</v>
+      </c>
+      <c r="L36" t="s">
+        <v>164</v>
+      </c>
+      <c r="M36" t="s">
+        <v>155</v>
+      </c>
+      <c r="N36" t="s">
+        <v>260</v>
+      </c>
+      <c r="O36" t="s">
+        <v>290</v>
+      </c>
+      <c r="P36" t="s">
+        <v>346</v>
+      </c>
+      <c r="Q36">
+        <v>1</v>
+      </c>
+      <c r="R36" t="s">
+        <v>199</v>
+      </c>
+      <c r="S36">
+        <v>49.6842235</v>
+      </c>
+      <c r="T36">
+        <v>49.6842235</v>
+      </c>
+      <c r="U36">
+        <v>0</v>
+      </c>
+      <c r="V36">
+        <v>0</v>
+      </c>
+      <c r="W36">
+        <v>0</v>
+      </c>
+      <c r="X36">
+        <v>0</v>
+      </c>
+      <c r="Y36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:25">
       <c r="A37" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B37" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C37" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D37" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="F37">
         <v>1</v>
       </c>
       <c r="G37" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="H37">
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:23">
+    <row r="38" spans="1:25">
       <c r="J38" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="K38" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="N38" t="s">
-        <v>247</v>
+        <v>262</v>
       </c>
       <c r="O38" t="s">
-        <v>266</v>
+        <v>291</v>
       </c>
       <c r="P38" t="s">
-        <v>308</v>
+        <v>347</v>
       </c>
       <c r="Q38">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="R38" t="s">
-        <v>333</v>
+        <v>377</v>
       </c>
       <c r="S38">
-        <v>3509.7219105</v>
+        <v>3955.6860015</v>
       </c>
       <c r="T38">
-        <v>1212.806694</v>
+        <v>776.0154415</v>
       </c>
       <c r="U38">
-        <v>1357.0385225</v>
+        <v>842.3266265</v>
       </c>
       <c r="V38">
-        <v>829.1200164999999</v>
+        <v>124.129938</v>
       </c>
       <c r="W38">
-        <v>110.7566775</v>
-      </c>
-    </row>
-    <row r="39" spans="1:23">
+        <v>743.6416495</v>
+      </c>
+      <c r="X38">
+        <v>741.0075265</v>
+      </c>
+      <c r="Y38">
+        <v>728.5648195</v>
+      </c>
+    </row>
+    <row r="39" spans="1:25">
       <c r="J39" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="K39" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="N39" t="s">
-        <v>248</v>
+        <v>263</v>
       </c>
       <c r="O39" t="s">
-        <v>267</v>
+        <v>292</v>
       </c>
       <c r="P39" t="s">
-        <v>309</v>
+        <v>348</v>
       </c>
       <c r="Q39">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="R39" t="s">
-        <v>334</v>
+        <v>378</v>
       </c>
       <c r="S39">
-        <v>5148.04254</v>
+        <v>5742.9247415</v>
       </c>
       <c r="T39">
-        <v>2425.613388</v>
+        <v>782.9935634999999</v>
       </c>
       <c r="U39">
-        <v>1501.2657815</v>
+        <v>2492.593737</v>
       </c>
       <c r="V39">
-        <v>1092.1129905</v>
+        <v>248.252202</v>
       </c>
       <c r="W39">
-        <v>129.05038</v>
-      </c>
-    </row>
-    <row r="40" spans="1:23">
+        <v>743.6416495</v>
+      </c>
+      <c r="X39">
+        <v>741.0075265</v>
+      </c>
+      <c r="Y39">
+        <v>734.436063</v>
+      </c>
+    </row>
+    <row r="40" spans="1:25">
       <c r="A40" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B40" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C40" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D40" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E40">
         <v>4.1</v>
@@ -3157,69 +3871,75 @@
         <v>1</v>
       </c>
       <c r="G40" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="H40">
         <v>20</v>
       </c>
       <c r="I40" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="J40" t="s">
         <v>231</v>
       </c>
       <c r="K40" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="L40" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="M40" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="N40" t="s">
-        <v>245</v>
+        <v>260</v>
       </c>
       <c r="O40" t="s">
-        <v>268</v>
+        <v>293</v>
       </c>
       <c r="P40" t="s">
-        <v>310</v>
+        <v>349</v>
       </c>
       <c r="Q40">
         <v>1</v>
       </c>
       <c r="R40" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="S40">
-        <v>16.94712</v>
+        <v>13.877304</v>
       </c>
       <c r="T40">
-        <v>0</v>
+        <v>13.877304</v>
       </c>
       <c r="U40">
         <v>0</v>
       </c>
       <c r="V40">
-        <v>16.94712</v>
+        <v>0</v>
       </c>
       <c r="W40">
         <v>0</v>
       </c>
-    </row>
-    <row r="41" spans="1:23">
+      <c r="X40">
+        <v>0</v>
+      </c>
+      <c r="Y40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:25">
       <c r="A41" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B41" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C41" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D41" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E41">
         <v>7.3</v>
@@ -3228,69 +3948,75 @@
         <v>1</v>
       </c>
       <c r="G41" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="H41">
         <v>12</v>
       </c>
       <c r="I41" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="J41" t="s">
         <v>231</v>
       </c>
       <c r="K41" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="L41" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="M41" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="N41" t="s">
-        <v>245</v>
+        <v>260</v>
       </c>
       <c r="O41" t="s">
-        <v>269</v>
+        <v>294</v>
       </c>
       <c r="P41" t="s">
-        <v>311</v>
+        <v>350</v>
       </c>
       <c r="Q41">
         <v>1</v>
       </c>
       <c r="R41" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="S41">
-        <v>9.108307999999999</v>
+        <v>11.656106</v>
       </c>
       <c r="T41">
-        <v>0</v>
+        <v>11.656106</v>
       </c>
       <c r="U41">
         <v>0</v>
       </c>
       <c r="V41">
-        <v>9.108307999999999</v>
+        <v>0</v>
       </c>
       <c r="W41">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="1:23">
+      <c r="X41">
+        <v>0</v>
+      </c>
+      <c r="Y41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:25">
       <c r="A42" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B42" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C42" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D42" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E42">
         <v>7.2</v>
@@ -3299,24 +4025,75 @@
         <v>1</v>
       </c>
       <c r="G42" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="H42">
         <v>12</v>
       </c>
-    </row>
-    <row r="43" spans="1:23">
+      <c r="I42" t="s">
+        <v>63</v>
+      </c>
+      <c r="J42" t="s">
+        <v>232</v>
+      </c>
+      <c r="K42" t="s">
+        <v>247</v>
+      </c>
+      <c r="L42" t="s">
+        <v>163</v>
+      </c>
+      <c r="M42" t="s">
+        <v>156</v>
+      </c>
+      <c r="N42" t="s">
+        <v>260</v>
+      </c>
+      <c r="O42" t="s">
+        <v>295</v>
+      </c>
+      <c r="P42" t="s">
+        <v>351</v>
+      </c>
+      <c r="Q42">
+        <v>1</v>
+      </c>
+      <c r="R42" t="s">
+        <v>203</v>
+      </c>
+      <c r="S42">
+        <v>12.8353175</v>
+      </c>
+      <c r="T42">
+        <v>0</v>
+      </c>
+      <c r="U42">
+        <v>0</v>
+      </c>
+      <c r="V42">
+        <v>0</v>
+      </c>
+      <c r="W42">
+        <v>12.8353175</v>
+      </c>
+      <c r="X42">
+        <v>0</v>
+      </c>
+      <c r="Y42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:25">
       <c r="A43" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B43" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C43" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D43" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E43">
         <v>7.1</v>
@@ -3325,24 +4102,75 @@
         <v>1</v>
       </c>
       <c r="G43" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="H43">
         <v>25</v>
       </c>
-    </row>
-    <row r="44" spans="1:23">
+      <c r="I43" t="s">
+        <v>64</v>
+      </c>
+      <c r="J43" t="s">
+        <v>231</v>
+      </c>
+      <c r="K43" t="s">
+        <v>246</v>
+      </c>
+      <c r="L43" t="s">
+        <v>163</v>
+      </c>
+      <c r="M43" t="s">
+        <v>156</v>
+      </c>
+      <c r="N43" t="s">
+        <v>260</v>
+      </c>
+      <c r="O43" t="s">
+        <v>296</v>
+      </c>
+      <c r="P43" t="s">
+        <v>352</v>
+      </c>
+      <c r="Q43">
+        <v>1</v>
+      </c>
+      <c r="R43" t="s">
+        <v>204</v>
+      </c>
+      <c r="S43">
+        <v>25.036691</v>
+      </c>
+      <c r="T43">
+        <v>25.036691</v>
+      </c>
+      <c r="U43">
+        <v>0</v>
+      </c>
+      <c r="V43">
+        <v>0</v>
+      </c>
+      <c r="W43">
+        <v>0</v>
+      </c>
+      <c r="X43">
+        <v>0</v>
+      </c>
+      <c r="Y43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:25">
       <c r="A44" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B44" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C44" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D44" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E44">
         <v>7.1</v>
@@ -3351,371 +4179,512 @@
         <v>3</v>
       </c>
       <c r="G44" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="H44">
         <v>18</v>
       </c>
-    </row>
-    <row r="45" spans="1:23">
-      <c r="I45" t="s">
-        <v>228</v>
-      </c>
+      <c r="I44" t="s">
+        <v>65</v>
+      </c>
+      <c r="J44" t="s">
+        <v>233</v>
+      </c>
+      <c r="K44" t="s">
+        <v>248</v>
+      </c>
+      <c r="L44" t="s">
+        <v>163</v>
+      </c>
+      <c r="M44" t="s">
+        <v>156</v>
+      </c>
+      <c r="N44" t="s">
+        <v>260</v>
+      </c>
+      <c r="O44" t="s">
+        <v>297</v>
+      </c>
+      <c r="P44" t="s">
+        <v>353</v>
+      </c>
+      <c r="Q44">
+        <v>2</v>
+      </c>
+      <c r="R44" t="s">
+        <v>205</v>
+      </c>
+      <c r="S44">
+        <v>12.527038</v>
+      </c>
+      <c r="T44">
+        <v>0</v>
+      </c>
+      <c r="U44">
+        <v>0</v>
+      </c>
+      <c r="V44">
+        <v>0</v>
+      </c>
+      <c r="W44">
+        <v>6.5319785</v>
+      </c>
+      <c r="X44">
+        <v>0</v>
+      </c>
+      <c r="Y44">
+        <v>5.9950595</v>
+      </c>
+    </row>
+    <row r="45" spans="1:25">
       <c r="J45" t="s">
+        <v>234</v>
+      </c>
+      <c r="K45" t="s">
+        <v>249</v>
+      </c>
+      <c r="N45" t="s">
+        <v>260</v>
+      </c>
+      <c r="O45" t="s">
+        <v>298</v>
+      </c>
+      <c r="P45" t="s">
+        <v>354</v>
+      </c>
+      <c r="Q45">
+        <v>1</v>
+      </c>
+      <c r="R45" t="s">
+        <v>379</v>
+      </c>
+      <c r="S45">
+        <v>482.7840085</v>
+      </c>
+      <c r="T45">
+        <v>0</v>
+      </c>
+      <c r="U45">
+        <v>482.7840085</v>
+      </c>
+      <c r="V45">
+        <v>0</v>
+      </c>
+      <c r="W45">
+        <v>0</v>
+      </c>
+      <c r="X45">
+        <v>0</v>
+      </c>
+      <c r="Y45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:25">
+      <c r="J46" t="s">
         <v>231</v>
       </c>
-      <c r="K45" t="s">
+      <c r="K46" t="s">
+        <v>246</v>
+      </c>
+      <c r="N46" t="s">
+        <v>260</v>
+      </c>
+      <c r="O46" t="s">
+        <v>299</v>
+      </c>
+      <c r="P46" t="s">
+        <v>355</v>
+      </c>
+      <c r="Q46">
+        <v>1</v>
+      </c>
+      <c r="R46" t="s">
+        <v>66</v>
+      </c>
+      <c r="S46">
+        <v>462.949212</v>
+      </c>
+      <c r="T46">
+        <v>462.949212</v>
+      </c>
+      <c r="U46">
+        <v>0</v>
+      </c>
+      <c r="V46">
+        <v>0</v>
+      </c>
+      <c r="W46">
+        <v>0</v>
+      </c>
+      <c r="X46">
+        <v>0</v>
+      </c>
+      <c r="Y46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:25">
+      <c r="A47" t="s">
+        <v>66</v>
+      </c>
+      <c r="B47" t="s">
+        <v>128</v>
+      </c>
+      <c r="C47" t="s">
+        <v>128</v>
+      </c>
+      <c r="D47" t="s">
+        <v>128</v>
+      </c>
+      <c r="G47" t="s">
+        <v>206</v>
+      </c>
+      <c r="I47" t="s">
+        <v>66</v>
+      </c>
+      <c r="J47" t="s">
+        <v>238</v>
+      </c>
+      <c r="K47" t="s">
+        <v>253</v>
+      </c>
+      <c r="L47" t="s">
+        <v>128</v>
+      </c>
+      <c r="M47" t="s">
+        <v>128</v>
+      </c>
+      <c r="N47" t="s">
+        <v>264</v>
+      </c>
+      <c r="O47" t="s">
+        <v>300</v>
+      </c>
+      <c r="P47" t="s">
+        <v>356</v>
+      </c>
+      <c r="Q47">
+        <v>12</v>
+      </c>
+      <c r="R47" t="s">
+        <v>206</v>
+      </c>
+      <c r="S47">
+        <v>618.5320614999998</v>
+      </c>
+      <c r="T47">
+        <v>7.00499</v>
+      </c>
+      <c r="U47">
+        <v>127.5777285</v>
+      </c>
+      <c r="V47">
+        <v>0</v>
+      </c>
+      <c r="W47">
+        <v>7.00499</v>
+      </c>
+      <c r="X47">
+        <v>7.00499</v>
+      </c>
+      <c r="Y47">
+        <v>469.939363</v>
+      </c>
+    </row>
+    <row r="48" spans="1:25">
+      <c r="A48" t="s">
+        <v>67</v>
+      </c>
+      <c r="B48" t="s">
+        <v>129</v>
+      </c>
+      <c r="C48" t="s">
+        <v>157</v>
+      </c>
+      <c r="D48" t="s">
+        <v>67</v>
+      </c>
+      <c r="G48" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="49" spans="1:25">
+      <c r="A49" t="s">
+        <v>31</v>
+      </c>
+      <c r="B49" t="s">
+        <v>130</v>
+      </c>
+      <c r="C49" t="s">
+        <v>157</v>
+      </c>
+      <c r="D49" t="s">
+        <v>31</v>
+      </c>
+      <c r="G49" t="s">
+        <v>208</v>
+      </c>
+      <c r="I49" t="s">
+        <v>31</v>
+      </c>
+      <c r="J49" t="s">
         <v>239</v>
       </c>
-      <c r="N45" t="s">
-        <v>245</v>
-      </c>
-      <c r="O45" t="s">
-        <v>270</v>
-      </c>
-      <c r="P45" t="s">
-        <v>312</v>
-      </c>
-      <c r="Q45">
-        <v>1</v>
-      </c>
-      <c r="R45" t="s">
-        <v>228</v>
-      </c>
-      <c r="S45">
-        <v>26.544178</v>
-      </c>
-      <c r="T45">
-        <v>0</v>
-      </c>
-      <c r="U45">
-        <v>0</v>
-      </c>
-      <c r="V45">
-        <v>26.544178</v>
-      </c>
-      <c r="W45">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:23">
-      <c r="A46" t="s">
-        <v>64</v>
-      </c>
-      <c r="B46" t="s">
-        <v>126</v>
-      </c>
-      <c r="C46" t="s">
-        <v>126</v>
-      </c>
-      <c r="D46" t="s">
-        <v>126</v>
-      </c>
-      <c r="G46" t="s">
-        <v>204</v>
-      </c>
-      <c r="I46" t="s">
-        <v>64</v>
-      </c>
-      <c r="J46" t="s">
-        <v>233</v>
-      </c>
-      <c r="K46" t="s">
-        <v>241</v>
-      </c>
-      <c r="L46" t="s">
-        <v>126</v>
-      </c>
-      <c r="M46" t="s">
-        <v>126</v>
-      </c>
-      <c r="N46" t="s">
-        <v>245</v>
-      </c>
-      <c r="O46" t="s">
-        <v>271</v>
-      </c>
-      <c r="P46" t="s">
-        <v>313</v>
-      </c>
-      <c r="Q46">
+      <c r="K49" t="s">
+        <v>254</v>
+      </c>
+      <c r="L49" t="s">
+        <v>31</v>
+      </c>
+      <c r="M49" t="s">
+        <v>157</v>
+      </c>
+      <c r="N49" t="s">
+        <v>261</v>
+      </c>
+      <c r="O49" t="s">
+        <v>301</v>
+      </c>
+      <c r="P49" t="s">
+        <v>357</v>
+      </c>
+      <c r="Q49">
+        <v>3</v>
+      </c>
+      <c r="R49" t="s">
+        <v>208</v>
+      </c>
+      <c r="S49">
+        <v>92.00158949999999</v>
+      </c>
+      <c r="T49">
+        <v>0</v>
+      </c>
+      <c r="U49">
+        <v>0</v>
+      </c>
+      <c r="V49">
+        <v>0</v>
+      </c>
+      <c r="W49">
+        <v>27.064</v>
+      </c>
+      <c r="X49">
+        <v>29.1196845</v>
+      </c>
+      <c r="Y49">
+        <v>35.817905</v>
+      </c>
+    </row>
+    <row r="50" spans="1:25">
+      <c r="A50" t="s">
+        <v>68</v>
+      </c>
+      <c r="B50" t="s">
+        <v>131</v>
+      </c>
+      <c r="C50" t="s">
+        <v>157</v>
+      </c>
+      <c r="D50" t="s">
+        <v>31</v>
+      </c>
+      <c r="G50" t="s">
+        <v>209</v>
+      </c>
+      <c r="I50" t="s">
+        <v>68</v>
+      </c>
+      <c r="J50" t="s">
+        <v>234</v>
+      </c>
+      <c r="K50" t="s">
+        <v>249</v>
+      </c>
+      <c r="L50" t="s">
+        <v>31</v>
+      </c>
+      <c r="M50" t="s">
+        <v>157</v>
+      </c>
+      <c r="N50" t="s">
+        <v>261</v>
+      </c>
+      <c r="O50" t="s">
+        <v>302</v>
+      </c>
+      <c r="P50" t="s">
+        <v>358</v>
+      </c>
+      <c r="Q50">
         <v>2</v>
       </c>
-      <c r="R46" t="s">
-        <v>204</v>
-      </c>
-      <c r="S46">
-        <v>895.986936</v>
-      </c>
-      <c r="T46">
-        <v>0</v>
-      </c>
-      <c r="U46">
-        <v>895.986936</v>
-      </c>
-      <c r="V46">
-        <v>0</v>
-      </c>
-      <c r="W46">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:23">
-      <c r="A47" t="s">
-        <v>65</v>
-      </c>
-      <c r="B47" t="s">
-        <v>127</v>
-      </c>
-      <c r="C47" t="s">
-        <v>155</v>
-      </c>
-      <c r="D47" t="s">
-        <v>65</v>
-      </c>
-      <c r="G47" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="48" spans="1:23">
-      <c r="A48" t="s">
-        <v>29</v>
-      </c>
-      <c r="B48" t="s">
-        <v>128</v>
-      </c>
-      <c r="C48" t="s">
-        <v>155</v>
-      </c>
-      <c r="D48" t="s">
-        <v>29</v>
-      </c>
-      <c r="G48" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="49" spans="1:23">
-      <c r="A49" t="s">
-        <v>66</v>
-      </c>
-      <c r="B49" t="s">
-        <v>129</v>
-      </c>
-      <c r="C49" t="s">
-        <v>155</v>
-      </c>
-      <c r="D49" t="s">
-        <v>29</v>
-      </c>
-      <c r="G49" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="50" spans="1:23">
-      <c r="A50" t="s">
-        <v>67</v>
-      </c>
-      <c r="B50" t="s">
-        <v>130</v>
-      </c>
-      <c r="C50" t="s">
-        <v>156</v>
-      </c>
-      <c r="D50" t="s">
-        <v>160</v>
-      </c>
-      <c r="E50">
+      <c r="R50" t="s">
+        <v>209</v>
+      </c>
+      <c r="S50">
+        <v>38.1497405</v>
+      </c>
+      <c r="T50">
+        <v>0</v>
+      </c>
+      <c r="U50">
+        <v>38.1497405</v>
+      </c>
+      <c r="V50">
+        <v>0</v>
+      </c>
+      <c r="W50">
+        <v>0</v>
+      </c>
+      <c r="X50">
+        <v>0</v>
+      </c>
+      <c r="Y50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:25">
+      <c r="A51" t="s">
+        <v>69</v>
+      </c>
+      <c r="B51" t="s">
+        <v>132</v>
+      </c>
+      <c r="C51" t="s">
+        <v>158</v>
+      </c>
+      <c r="D51" t="s">
+        <v>162</v>
+      </c>
+      <c r="E51">
         <v>4.1</v>
       </c>
-      <c r="F50">
-        <v>1</v>
-      </c>
-      <c r="G50" t="s">
-        <v>208</v>
-      </c>
-      <c r="H50">
+      <c r="F51">
+        <v>1</v>
+      </c>
+      <c r="G51" t="s">
+        <v>210</v>
+      </c>
+      <c r="H51">
         <v>15</v>
       </c>
-      <c r="I50" t="s">
-        <v>67</v>
-      </c>
-      <c r="J50" t="s">
-        <v>230</v>
-      </c>
-      <c r="K50" t="s">
-        <v>238</v>
-      </c>
-      <c r="L50" t="s">
-        <v>160</v>
-      </c>
-      <c r="M50" t="s">
-        <v>156</v>
-      </c>
-      <c r="N50" t="s">
-        <v>245</v>
-      </c>
-      <c r="O50" t="s">
-        <v>272</v>
-      </c>
-      <c r="P50" t="s">
-        <v>314</v>
-      </c>
-      <c r="Q50">
-        <v>1</v>
-      </c>
-      <c r="R50" t="s">
-        <v>208</v>
-      </c>
-      <c r="S50">
-        <v>9.990109</v>
-      </c>
-      <c r="T50">
-        <v>0</v>
-      </c>
-      <c r="U50">
-        <v>0</v>
-      </c>
-      <c r="V50">
-        <v>0</v>
-      </c>
-      <c r="W50">
-        <v>9.990109</v>
-      </c>
-    </row>
-    <row r="51" spans="1:23">
-      <c r="A51" t="s">
-        <v>68</v>
-      </c>
-      <c r="B51" t="s">
-        <v>131</v>
-      </c>
-      <c r="C51" t="s">
-        <v>156</v>
-      </c>
-      <c r="D51" t="s">
-        <v>158</v>
-      </c>
-      <c r="E51">
-        <v>9.1</v>
-      </c>
-      <c r="F51">
-        <v>1</v>
-      </c>
-      <c r="G51" t="s">
-        <v>209</v>
-      </c>
-      <c r="H51">
-        <v>30</v>
-      </c>
       <c r="I51" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J51" t="s">
         <v>231</v>
       </c>
       <c r="K51" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="L51" t="s">
+        <v>162</v>
+      </c>
+      <c r="M51" t="s">
         <v>158</v>
       </c>
-      <c r="M51" t="s">
-        <v>156</v>
-      </c>
       <c r="N51" t="s">
-        <v>245</v>
+        <v>260</v>
       </c>
       <c r="O51" t="s">
-        <v>273</v>
+        <v>303</v>
       </c>
       <c r="P51" t="s">
-        <v>315</v>
+        <v>359</v>
       </c>
       <c r="Q51">
         <v>1</v>
       </c>
       <c r="R51" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="S51">
-        <v>35.498551</v>
+        <v>16.4718365</v>
       </c>
       <c r="T51">
-        <v>0</v>
+        <v>16.4718365</v>
       </c>
       <c r="U51">
         <v>0</v>
       </c>
       <c r="V51">
-        <v>35.498551</v>
+        <v>0</v>
       </c>
       <c r="W51">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="1:23">
+      <c r="X51">
+        <v>0</v>
+      </c>
+      <c r="Y51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:25">
       <c r="A52" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B52" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C52" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D52" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E52">
-        <v>7.2</v>
+        <v>9.1</v>
       </c>
       <c r="F52">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G52" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H52">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I52" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J52" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="K52" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="L52" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="M52" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="N52" t="s">
-        <v>245</v>
+        <v>260</v>
       </c>
       <c r="O52" t="s">
-        <v>274</v>
+        <v>304</v>
       </c>
       <c r="P52" t="s">
-        <v>316</v>
+        <v>360</v>
       </c>
       <c r="Q52">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R52" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="S52">
-        <v>32.532022</v>
+        <v>62.0861185</v>
       </c>
       <c r="T52">
-        <v>0</v>
+        <v>62.0861185</v>
       </c>
       <c r="U52">
-        <v>32.532022</v>
+        <v>0</v>
       </c>
       <c r="V52">
         <v>0</v>
@@ -3723,283 +4692,307 @@
       <c r="W52">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="1:23">
+      <c r="X52">
+        <v>0</v>
+      </c>
+      <c r="Y52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:25">
       <c r="A53" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B53" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C53" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D53" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E53">
         <v>7.2</v>
       </c>
       <c r="F53">
+        <v>2</v>
+      </c>
+      <c r="G53" t="s">
+        <v>212</v>
+      </c>
+      <c r="H53">
+        <v>32</v>
+      </c>
+      <c r="I53" t="s">
+        <v>71</v>
+      </c>
+      <c r="J53" t="s">
+        <v>240</v>
+      </c>
+      <c r="K53" t="s">
+        <v>255</v>
+      </c>
+      <c r="L53" t="s">
+        <v>163</v>
+      </c>
+      <c r="M53" t="s">
+        <v>158</v>
+      </c>
+      <c r="N53" t="s">
+        <v>260</v>
+      </c>
+      <c r="O53" t="s">
+        <v>305</v>
+      </c>
+      <c r="P53" t="s">
+        <v>361</v>
+      </c>
+      <c r="Q53">
+        <v>2</v>
+      </c>
+      <c r="R53" t="s">
+        <v>212</v>
+      </c>
+      <c r="S53">
+        <v>30.587292</v>
+      </c>
+      <c r="T53">
+        <v>0</v>
+      </c>
+      <c r="U53">
+        <v>15.293646</v>
+      </c>
+      <c r="V53">
+        <v>0</v>
+      </c>
+      <c r="W53">
+        <v>0</v>
+      </c>
+      <c r="X53">
+        <v>15.293646</v>
+      </c>
+      <c r="Y53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:25">
+      <c r="A54" t="s">
+        <v>72</v>
+      </c>
+      <c r="B54" t="s">
+        <v>135</v>
+      </c>
+      <c r="C54" t="s">
+        <v>158</v>
+      </c>
+      <c r="D54" t="s">
+        <v>163</v>
+      </c>
+      <c r="E54">
+        <v>7.2</v>
+      </c>
+      <c r="F54">
         <v>4</v>
       </c>
-      <c r="G53" t="s">
-        <v>211</v>
-      </c>
-      <c r="H53">
+      <c r="G54" t="s">
+        <v>213</v>
+      </c>
+      <c r="H54">
         <v>180</v>
       </c>
-      <c r="I53" t="s">
-        <v>70</v>
-      </c>
-      <c r="J53" t="s">
-        <v>233</v>
-      </c>
-      <c r="K53" t="s">
-        <v>241</v>
-      </c>
-      <c r="L53" t="s">
-        <v>161</v>
-      </c>
-      <c r="M53" t="s">
-        <v>156</v>
-      </c>
-      <c r="N53" t="s">
-        <v>245</v>
-      </c>
-      <c r="O53" t="s">
-        <v>275</v>
-      </c>
-      <c r="P53" t="s">
-        <v>317</v>
-      </c>
-      <c r="Q53">
-        <v>4</v>
-      </c>
-      <c r="R53" t="s">
-        <v>211</v>
-      </c>
-      <c r="S53">
-        <v>172.302794</v>
-      </c>
-      <c r="T53">
-        <v>0</v>
-      </c>
-      <c r="U53">
-        <v>172.302794</v>
-      </c>
-      <c r="V53">
-        <v>0</v>
-      </c>
-      <c r="W53">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:23">
-      <c r="A54" t="s">
-        <v>71</v>
-      </c>
-      <c r="B54" t="s">
-        <v>134</v>
-      </c>
-      <c r="C54" t="s">
-        <v>156</v>
-      </c>
-      <c r="D54" t="s">
-        <v>160</v>
-      </c>
-      <c r="E54">
+      <c r="I54" t="s">
+        <v>72</v>
+      </c>
+      <c r="J54" t="s">
+        <v>240</v>
+      </c>
+      <c r="K54" t="s">
+        <v>255</v>
+      </c>
+      <c r="L54" t="s">
+        <v>163</v>
+      </c>
+      <c r="M54" t="s">
+        <v>158</v>
+      </c>
+      <c r="N54" t="s">
+        <v>260</v>
+      </c>
+      <c r="O54" t="s">
+        <v>306</v>
+      </c>
+      <c r="P54" t="s">
+        <v>362</v>
+      </c>
+      <c r="Q54">
+        <v>16</v>
+      </c>
+      <c r="R54" t="s">
+        <v>213</v>
+      </c>
+      <c r="S54">
+        <v>152.223724</v>
+      </c>
+      <c r="T54">
+        <v>0</v>
+      </c>
+      <c r="U54">
+        <v>76.111862</v>
+      </c>
+      <c r="V54">
+        <v>0</v>
+      </c>
+      <c r="W54">
+        <v>0</v>
+      </c>
+      <c r="X54">
+        <v>76.111862</v>
+      </c>
+      <c r="Y54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:25">
+      <c r="A55" t="s">
+        <v>73</v>
+      </c>
+      <c r="B55" t="s">
+        <v>136</v>
+      </c>
+      <c r="C55" t="s">
+        <v>158</v>
+      </c>
+      <c r="D55" t="s">
+        <v>162</v>
+      </c>
+      <c r="E55">
         <v>2.1</v>
       </c>
-      <c r="F54">
-        <v>1</v>
-      </c>
-      <c r="G54" t="s">
-        <v>212</v>
-      </c>
-      <c r="H54">
+      <c r="F55">
+        <v>1</v>
+      </c>
+      <c r="G55" t="s">
+        <v>214</v>
+      </c>
+      <c r="H55">
         <v>12</v>
       </c>
-      <c r="I54" t="s">
-        <v>71</v>
-      </c>
-      <c r="J54" t="s">
+      <c r="I55" t="s">
+        <v>73</v>
+      </c>
+      <c r="J55" t="s">
         <v>231</v>
       </c>
-      <c r="K54" t="s">
-        <v>239</v>
-      </c>
-      <c r="L54" t="s">
-        <v>160</v>
-      </c>
-      <c r="M54" t="s">
-        <v>156</v>
-      </c>
-      <c r="N54" t="s">
-        <v>245</v>
-      </c>
-      <c r="O54" t="s">
-        <v>276</v>
-      </c>
-      <c r="P54" t="s">
-        <v>318</v>
-      </c>
-      <c r="Q54">
-        <v>1</v>
-      </c>
-      <c r="R54" t="s">
-        <v>212</v>
-      </c>
-      <c r="S54">
-        <v>13.314032</v>
-      </c>
-      <c r="T54">
-        <v>0</v>
-      </c>
-      <c r="U54">
-        <v>0</v>
-      </c>
-      <c r="V54">
-        <v>13.314032</v>
-      </c>
-      <c r="W54">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="1:23">
-      <c r="A55" t="s">
-        <v>72</v>
-      </c>
-      <c r="B55" t="s">
-        <v>135</v>
-      </c>
-      <c r="C55" t="s">
-        <v>156</v>
-      </c>
-      <c r="D55" t="s">
-        <v>161</v>
-      </c>
-      <c r="E55">
+      <c r="K55" t="s">
+        <v>246</v>
+      </c>
+      <c r="L55" t="s">
+        <v>162</v>
+      </c>
+      <c r="M55" t="s">
+        <v>158</v>
+      </c>
+      <c r="N55" t="s">
+        <v>260</v>
+      </c>
+      <c r="O55" t="s">
+        <v>307</v>
+      </c>
+      <c r="P55" t="s">
+        <v>363</v>
+      </c>
+      <c r="Q55">
+        <v>1</v>
+      </c>
+      <c r="R55" t="s">
+        <v>214</v>
+      </c>
+      <c r="S55">
+        <v>8.992677</v>
+      </c>
+      <c r="T55">
+        <v>8.992677</v>
+      </c>
+      <c r="U55">
+        <v>0</v>
+      </c>
+      <c r="V55">
+        <v>0</v>
+      </c>
+      <c r="W55">
+        <v>0</v>
+      </c>
+      <c r="X55">
+        <v>0</v>
+      </c>
+      <c r="Y55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:25">
+      <c r="A56" t="s">
+        <v>74</v>
+      </c>
+      <c r="B56" t="s">
+        <v>137</v>
+      </c>
+      <c r="C56" t="s">
+        <v>158</v>
+      </c>
+      <c r="D56" t="s">
+        <v>163</v>
+      </c>
+      <c r="E56">
         <v>7.1</v>
       </c>
-      <c r="F55">
-        <v>1</v>
-      </c>
-      <c r="G55" t="s">
-        <v>213</v>
-      </c>
-      <c r="H55">
+      <c r="F56">
+        <v>1</v>
+      </c>
+      <c r="G56" t="s">
+        <v>215</v>
+      </c>
+      <c r="H56">
         <v>10</v>
       </c>
-      <c r="I55" t="s">
-        <v>72</v>
-      </c>
-      <c r="J55" t="s">
-        <v>235</v>
-      </c>
-      <c r="K55" t="s">
-        <v>243</v>
-      </c>
-      <c r="L55" t="s">
-        <v>161</v>
-      </c>
-      <c r="M55" t="s">
-        <v>156</v>
-      </c>
-      <c r="N55" t="s">
-        <v>245</v>
-      </c>
-      <c r="O55" t="s">
-        <v>277</v>
-      </c>
-      <c r="P55" t="s">
-        <v>319</v>
-      </c>
-      <c r="Q55">
-        <v>2</v>
-      </c>
-      <c r="R55" t="s">
-        <v>213</v>
-      </c>
-      <c r="S55">
-        <v>34.7560375</v>
-      </c>
-      <c r="T55">
-        <v>9.675238999999999</v>
-      </c>
-      <c r="U55">
-        <v>25.0807985</v>
-      </c>
-      <c r="V55">
-        <v>0</v>
-      </c>
-      <c r="W55">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:23">
-      <c r="A56" t="s">
-        <v>73</v>
-      </c>
-      <c r="B56" t="s">
-        <v>136</v>
-      </c>
-      <c r="C56" t="s">
-        <v>156</v>
-      </c>
-      <c r="D56" t="s">
-        <v>160</v>
-      </c>
-      <c r="E56">
-        <v>4.1</v>
-      </c>
-      <c r="F56">
-        <v>2</v>
-      </c>
-      <c r="G56" t="s">
-        <v>214</v>
-      </c>
-      <c r="H56">
-        <v>180</v>
-      </c>
       <c r="I56" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J56" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="K56" t="s">
-        <v>244</v>
+        <v>255</v>
       </c>
       <c r="L56" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="M56" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="N56" t="s">
-        <v>245</v>
+        <v>260</v>
       </c>
       <c r="O56" t="s">
-        <v>278</v>
+        <v>308</v>
       </c>
       <c r="P56" t="s">
-        <v>320</v>
+        <v>364</v>
       </c>
       <c r="Q56">
         <v>2</v>
       </c>
       <c r="R56" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="S56">
-        <v>179.2507285</v>
+        <v>22.39557</v>
       </c>
       <c r="T56">
-        <v>179.2507285</v>
+        <v>0</v>
       </c>
       <c r="U56">
-        <v>0</v>
+        <v>11.197785</v>
       </c>
       <c r="V56">
         <v>0</v>
@@ -4007,70 +5000,76 @@
       <c r="W56">
         <v>0</v>
       </c>
-    </row>
-    <row r="57" spans="1:23">
+      <c r="X56">
+        <v>11.197785</v>
+      </c>
+      <c r="Y56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:25">
       <c r="A57" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B57" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C57" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D57" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E57">
-        <v>5.5</v>
+        <v>4.1</v>
       </c>
       <c r="F57">
         <v>2</v>
       </c>
       <c r="G57" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H57">
-        <v>896</v>
+        <v>180</v>
       </c>
       <c r="I57" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J57" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="K57" t="s">
-        <v>244</v>
+        <v>255</v>
       </c>
       <c r="L57" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="M57" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="N57" t="s">
-        <v>245</v>
+        <v>260</v>
       </c>
       <c r="O57" t="s">
-        <v>279</v>
+        <v>309</v>
       </c>
       <c r="P57" t="s">
-        <v>321</v>
+        <v>365</v>
       </c>
       <c r="Q57">
         <v>2</v>
       </c>
       <c r="R57" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="S57">
-        <v>895.986936</v>
+        <v>174.111751</v>
       </c>
       <c r="T57">
-        <v>895.986936</v>
+        <v>0</v>
       </c>
       <c r="U57">
-        <v>0</v>
+        <v>87.0558755</v>
       </c>
       <c r="V57">
         <v>0</v>
@@ -4078,184 +5077,151 @@
       <c r="W57">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="1:23">
+      <c r="X57">
+        <v>87.0558755</v>
+      </c>
+      <c r="Y57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:25">
       <c r="A58" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B58" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C58" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D58" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="E58">
-        <v>9.1</v>
+        <v>5.5</v>
       </c>
       <c r="F58">
         <v>2</v>
       </c>
       <c r="G58" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H58">
+        <v>896</v>
+      </c>
+      <c r="I58" t="s">
+        <v>76</v>
+      </c>
+      <c r="J58" t="s">
+        <v>241</v>
+      </c>
+      <c r="K58" t="s">
+        <v>256</v>
+      </c>
+      <c r="L58" t="s">
+        <v>162</v>
+      </c>
+      <c r="M58" t="s">
+        <v>158</v>
+      </c>
+      <c r="N58" t="s">
+        <v>260</v>
+      </c>
+      <c r="O58" t="s">
+        <v>310</v>
+      </c>
+      <c r="P58" t="s">
+        <v>366</v>
+      </c>
+      <c r="Q58">
+        <v>1</v>
+      </c>
+      <c r="R58" t="s">
+        <v>217</v>
+      </c>
+      <c r="S58">
+        <v>462.934373</v>
+      </c>
+      <c r="T58">
+        <v>0</v>
+      </c>
+      <c r="U58">
+        <v>0</v>
+      </c>
+      <c r="V58">
+        <v>0</v>
+      </c>
+      <c r="W58">
+        <v>0</v>
+      </c>
+      <c r="X58">
+        <v>462.934373</v>
+      </c>
+      <c r="Y58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:25">
+      <c r="A59" t="s">
+        <v>77</v>
+      </c>
+      <c r="B59" t="s">
+        <v>140</v>
+      </c>
+      <c r="C59" t="s">
+        <v>158</v>
+      </c>
+      <c r="D59" t="s">
+        <v>160</v>
+      </c>
+      <c r="E59">
+        <v>9.1</v>
+      </c>
+      <c r="F59">
+        <v>2</v>
+      </c>
+      <c r="G59" t="s">
+        <v>218</v>
+      </c>
+      <c r="H59">
         <v>10</v>
       </c>
-      <c r="I58" t="s">
-        <v>75</v>
-      </c>
-      <c r="J58" t="s">
-        <v>236</v>
-      </c>
-      <c r="K58" t="s">
-        <v>244</v>
-      </c>
-      <c r="L58" t="s">
+    </row>
+    <row r="60" spans="1:25">
+      <c r="A60" t="s">
+        <v>78</v>
+      </c>
+      <c r="B60" t="s">
+        <v>141</v>
+      </c>
+      <c r="C60" t="s">
         <v>158</v>
       </c>
-      <c r="M58" t="s">
-        <v>156</v>
-      </c>
-      <c r="N58" t="s">
-        <v>245</v>
-      </c>
-      <c r="O58" t="s">
-        <v>280</v>
-      </c>
-      <c r="P58" t="s">
-        <v>322</v>
-      </c>
-      <c r="Q58">
-        <v>2</v>
-      </c>
-      <c r="R58" t="s">
-        <v>216</v>
-      </c>
-      <c r="S58">
-        <v>11.072026</v>
-      </c>
-      <c r="T58">
-        <v>11.072026</v>
-      </c>
-      <c r="U58">
-        <v>0</v>
-      </c>
-      <c r="V58">
-        <v>0</v>
-      </c>
-      <c r="W58">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="1:23">
-      <c r="A59" t="s">
-        <v>76</v>
-      </c>
-      <c r="B59" t="s">
-        <v>139</v>
-      </c>
-      <c r="C59" t="s">
-        <v>156</v>
-      </c>
-      <c r="D59" t="s">
+      <c r="D60" t="s">
+        <v>160</v>
+      </c>
+      <c r="F60">
+        <v>1</v>
+      </c>
+      <c r="G60" t="s">
+        <v>219</v>
+      </c>
+      <c r="H60">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" spans="1:25">
+      <c r="A61" t="s">
+        <v>53</v>
+      </c>
+      <c r="B61" t="s">
+        <v>142</v>
+      </c>
+      <c r="C61" t="s">
         <v>158</v>
       </c>
-      <c r="F59">
-        <v>1</v>
-      </c>
-      <c r="G59" t="s">
-        <v>217</v>
-      </c>
-      <c r="H59">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="60" spans="1:23">
-      <c r="A60" t="s">
-        <v>51</v>
-      </c>
-      <c r="B60" t="s">
-        <v>140</v>
-      </c>
-      <c r="C60" t="s">
-        <v>156</v>
-      </c>
-      <c r="D60" t="s">
-        <v>161</v>
-      </c>
-      <c r="E60">
-        <v>7.1</v>
-      </c>
-      <c r="F60">
-        <v>2</v>
-      </c>
-      <c r="G60" t="s">
-        <v>218</v>
-      </c>
-      <c r="H60">
-        <v>5</v>
-      </c>
-      <c r="I60" t="s">
-        <v>51</v>
-      </c>
-      <c r="J60" t="s">
-        <v>231</v>
-      </c>
-      <c r="K60" t="s">
-        <v>239</v>
-      </c>
-      <c r="L60" t="s">
-        <v>161</v>
-      </c>
-      <c r="M60" t="s">
-        <v>156</v>
-      </c>
-      <c r="N60" t="s">
-        <v>245</v>
-      </c>
-      <c r="O60" t="s">
-        <v>281</v>
-      </c>
-      <c r="P60" t="s">
-        <v>323</v>
-      </c>
-      <c r="Q60">
-        <v>1</v>
-      </c>
-      <c r="R60" t="s">
-        <v>218</v>
-      </c>
-      <c r="S60">
-        <v>17.154349</v>
-      </c>
-      <c r="T60">
-        <v>0</v>
-      </c>
-      <c r="U60">
-        <v>0</v>
-      </c>
-      <c r="V60">
-        <v>17.154349</v>
-      </c>
-      <c r="W60">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="1:23">
-      <c r="A61" t="s">
-        <v>52</v>
-      </c>
-      <c r="B61" t="s">
-        <v>141</v>
-      </c>
-      <c r="C61" t="s">
-        <v>156</v>
-      </c>
       <c r="D61" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E61">
         <v>7.1</v>
@@ -4264,69 +5230,75 @@
         <v>2</v>
       </c>
       <c r="G61" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H61">
         <v>5</v>
       </c>
       <c r="I61" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J61" t="s">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="K61" t="s">
-        <v>239</v>
+        <v>257</v>
       </c>
       <c r="L61" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="M61" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="N61" t="s">
-        <v>245</v>
+        <v>260</v>
       </c>
       <c r="O61" t="s">
-        <v>282</v>
+        <v>311</v>
       </c>
       <c r="P61" t="s">
-        <v>324</v>
+        <v>367</v>
       </c>
       <c r="Q61">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R61" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="S61">
-        <v>17.1529545</v>
+        <v>20.548728</v>
       </c>
       <c r="T61">
         <v>0</v>
       </c>
       <c r="U61">
-        <v>0</v>
+        <v>6.849576</v>
       </c>
       <c r="V61">
-        <v>17.1529545</v>
+        <v>0</v>
       </c>
       <c r="W61">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="1:23">
+        <v>6.849576</v>
+      </c>
+      <c r="X61">
+        <v>0</v>
+      </c>
+      <c r="Y61">
+        <v>6.849576</v>
+      </c>
+    </row>
+    <row r="62" spans="1:25">
       <c r="A62" t="s">
-        <v>77</v>
+        <v>54</v>
       </c>
       <c r="B62" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C62" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D62" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E62">
         <v>7.1</v>
@@ -4335,327 +5307,351 @@
         <v>2</v>
       </c>
       <c r="G62" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H62">
+        <v>5</v>
+      </c>
+      <c r="I62" t="s">
+        <v>54</v>
+      </c>
+      <c r="J62" t="s">
+        <v>243</v>
+      </c>
+      <c r="K62" t="s">
+        <v>258</v>
+      </c>
+      <c r="L62" t="s">
+        <v>163</v>
+      </c>
+      <c r="M62" t="s">
+        <v>158</v>
+      </c>
+      <c r="N62" t="s">
+        <v>260</v>
+      </c>
+      <c r="O62" t="s">
+        <v>312</v>
+      </c>
+      <c r="P62" t="s">
+        <v>368</v>
+      </c>
+      <c r="Q62">
+        <v>3</v>
+      </c>
+      <c r="R62" t="s">
+        <v>221</v>
+      </c>
+      <c r="S62">
+        <v>18.560214</v>
+      </c>
+      <c r="T62">
+        <v>6.849576</v>
+      </c>
+      <c r="U62">
+        <v>0</v>
+      </c>
+      <c r="V62">
+        <v>0</v>
+      </c>
+      <c r="W62">
+        <v>4.861062</v>
+      </c>
+      <c r="X62">
+        <v>6.849576</v>
+      </c>
+      <c r="Y62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:25">
+      <c r="A63" t="s">
+        <v>79</v>
+      </c>
+      <c r="B63" t="s">
+        <v>144</v>
+      </c>
+      <c r="C63" t="s">
+        <v>158</v>
+      </c>
+      <c r="D63" t="s">
+        <v>163</v>
+      </c>
+      <c r="E63">
+        <v>7.1</v>
+      </c>
+      <c r="F63">
+        <v>2</v>
+      </c>
+      <c r="G63" t="s">
+        <v>222</v>
+      </c>
+      <c r="H63">
         <v>10</v>
       </c>
-      <c r="I62" t="s">
-        <v>77</v>
-      </c>
-      <c r="J62" t="s">
-        <v>236</v>
-      </c>
-      <c r="K62" t="s">
+      <c r="I63" t="s">
+        <v>79</v>
+      </c>
+      <c r="J63" t="s">
+        <v>240</v>
+      </c>
+      <c r="K63" t="s">
+        <v>255</v>
+      </c>
+      <c r="L63" t="s">
+        <v>163</v>
+      </c>
+      <c r="M63" t="s">
+        <v>158</v>
+      </c>
+      <c r="N63" t="s">
+        <v>260</v>
+      </c>
+      <c r="O63" t="s">
+        <v>313</v>
+      </c>
+      <c r="P63" t="s">
+        <v>369</v>
+      </c>
+      <c r="Q63">
+        <v>2</v>
+      </c>
+      <c r="R63" t="s">
+        <v>222</v>
+      </c>
+      <c r="S63">
+        <v>8.733451000000001</v>
+      </c>
+      <c r="T63">
+        <v>0</v>
+      </c>
+      <c r="U63">
+        <v>4.3667255</v>
+      </c>
+      <c r="V63">
+        <v>0</v>
+      </c>
+      <c r="W63">
+        <v>0</v>
+      </c>
+      <c r="X63">
+        <v>4.3667255</v>
+      </c>
+      <c r="Y63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:25">
+      <c r="A64" t="s">
+        <v>80</v>
+      </c>
+      <c r="B64" t="s">
+        <v>145</v>
+      </c>
+      <c r="C64" t="s">
+        <v>159</v>
+      </c>
+      <c r="D64" t="s">
+        <v>162</v>
+      </c>
+      <c r="E64">
+        <v>2.1</v>
+      </c>
+      <c r="F64">
+        <v>1</v>
+      </c>
+      <c r="G64" t="s">
+        <v>223</v>
+      </c>
+      <c r="H64">
+        <v>18</v>
+      </c>
+      <c r="I64" t="s">
+        <v>80</v>
+      </c>
+      <c r="J64" t="s">
+        <v>232</v>
+      </c>
+      <c r="K64" t="s">
+        <v>247</v>
+      </c>
+      <c r="L64" t="s">
+        <v>162</v>
+      </c>
+      <c r="M64" t="s">
+        <v>159</v>
+      </c>
+      <c r="N64" t="s">
+        <v>260</v>
+      </c>
+      <c r="O64" t="s">
+        <v>314</v>
+      </c>
+      <c r="P64" t="s">
+        <v>370</v>
+      </c>
+      <c r="Q64">
+        <v>1</v>
+      </c>
+      <c r="R64" t="s">
+        <v>223</v>
+      </c>
+      <c r="S64">
+        <v>18.09956</v>
+      </c>
+      <c r="T64">
+        <v>0</v>
+      </c>
+      <c r="U64">
+        <v>0</v>
+      </c>
+      <c r="V64">
+        <v>0</v>
+      </c>
+      <c r="W64">
+        <v>18.09956</v>
+      </c>
+      <c r="X64">
+        <v>0</v>
+      </c>
+      <c r="Y64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:25">
+      <c r="A65" t="s">
+        <v>81</v>
+      </c>
+      <c r="B65" t="s">
+        <v>146</v>
+      </c>
+      <c r="C65" t="s">
+        <v>159</v>
+      </c>
+      <c r="D65" t="s">
+        <v>163</v>
+      </c>
+      <c r="E65">
+        <v>4.1</v>
+      </c>
+      <c r="F65">
+        <v>1</v>
+      </c>
+      <c r="G65" t="s">
+        <v>224</v>
+      </c>
+      <c r="H65">
+        <v>20</v>
+      </c>
+      <c r="I65" t="s">
+        <v>81</v>
+      </c>
+      <c r="J65" t="s">
         <v>244</v>
       </c>
-      <c r="L62" t="s">
-        <v>161</v>
-      </c>
-      <c r="M62" t="s">
-        <v>156</v>
-      </c>
-      <c r="N62" t="s">
-        <v>245</v>
-      </c>
-      <c r="O62" t="s">
-        <v>283</v>
-      </c>
-      <c r="P62" t="s">
-        <v>325</v>
-      </c>
-      <c r="Q62">
-        <v>2</v>
-      </c>
-      <c r="R62" t="s">
-        <v>220</v>
-      </c>
-      <c r="S62">
-        <v>9.07253</v>
-      </c>
-      <c r="T62">
-        <v>9.07253</v>
-      </c>
-      <c r="U62">
-        <v>0</v>
-      </c>
-      <c r="V62">
-        <v>0</v>
-      </c>
-      <c r="W62">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="1:23">
-      <c r="A63" t="s">
-        <v>78</v>
-      </c>
-      <c r="B63" t="s">
-        <v>143</v>
-      </c>
-      <c r="C63" t="s">
-        <v>157</v>
-      </c>
-      <c r="D63" t="s">
-        <v>160</v>
-      </c>
-      <c r="E63">
-        <v>2.1</v>
-      </c>
-      <c r="F63">
-        <v>1</v>
-      </c>
-      <c r="G63" t="s">
-        <v>221</v>
-      </c>
-      <c r="H63">
-        <v>18</v>
-      </c>
-      <c r="I63" t="s">
-        <v>78</v>
-      </c>
-      <c r="J63" t="s">
-        <v>231</v>
-      </c>
-      <c r="K63" t="s">
-        <v>239</v>
-      </c>
-      <c r="L63" t="s">
-        <v>160</v>
-      </c>
-      <c r="M63" t="s">
-        <v>157</v>
-      </c>
-      <c r="N63" t="s">
-        <v>245</v>
-      </c>
-      <c r="O63" t="s">
-        <v>284</v>
-      </c>
-      <c r="P63" t="s">
-        <v>326</v>
-      </c>
-      <c r="Q63">
-        <v>1</v>
-      </c>
-      <c r="R63" t="s">
-        <v>221</v>
-      </c>
-      <c r="S63">
-        <v>17.776442</v>
-      </c>
-      <c r="T63">
-        <v>0</v>
-      </c>
-      <c r="U63">
-        <v>0</v>
-      </c>
-      <c r="V63">
-        <v>17.776442</v>
-      </c>
-      <c r="W63">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="1:23">
-      <c r="A64" t="s">
-        <v>79</v>
-      </c>
-      <c r="B64" t="s">
-        <v>144</v>
-      </c>
-      <c r="C64" t="s">
-        <v>157</v>
-      </c>
-      <c r="D64" t="s">
-        <v>161</v>
-      </c>
-      <c r="E64">
-        <v>4.1</v>
-      </c>
-      <c r="F64">
-        <v>1</v>
-      </c>
-      <c r="G64" t="s">
-        <v>222</v>
-      </c>
-      <c r="H64">
-        <v>20</v>
-      </c>
-      <c r="I64" t="s">
-        <v>79</v>
-      </c>
-      <c r="J64" t="s">
-        <v>231</v>
-      </c>
-      <c r="K64" t="s">
-        <v>239</v>
-      </c>
-      <c r="L64" t="s">
-        <v>161</v>
-      </c>
-      <c r="M64" t="s">
-        <v>157</v>
-      </c>
-      <c r="N64" t="s">
-        <v>245</v>
-      </c>
-      <c r="O64" t="s">
-        <v>285</v>
-      </c>
-      <c r="P64" t="s">
-        <v>327</v>
-      </c>
-      <c r="Q64">
-        <v>1</v>
-      </c>
-      <c r="R64" t="s">
-        <v>222</v>
-      </c>
-      <c r="S64">
-        <v>12.942644</v>
-      </c>
-      <c r="T64">
-        <v>0</v>
-      </c>
-      <c r="U64">
-        <v>0</v>
-      </c>
-      <c r="V64">
-        <v>12.942644</v>
-      </c>
-      <c r="W64">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="1:23">
-      <c r="A65" t="s">
-        <v>80</v>
-      </c>
-      <c r="B65" t="s">
-        <v>145</v>
-      </c>
-      <c r="C65" t="s">
-        <v>157</v>
-      </c>
-      <c r="D65" t="s">
-        <v>160</v>
-      </c>
-      <c r="E65">
+      <c r="K65" t="s">
+        <v>259</v>
+      </c>
+      <c r="L65" t="s">
+        <v>163</v>
+      </c>
+      <c r="M65" t="s">
+        <v>159</v>
+      </c>
+      <c r="N65" t="s">
+        <v>260</v>
+      </c>
+      <c r="O65" t="s">
+        <v>315</v>
+      </c>
+      <c r="P65" t="s">
+        <v>371</v>
+      </c>
+      <c r="Q65">
+        <v>1</v>
+      </c>
+      <c r="R65" t="s">
+        <v>224</v>
+      </c>
+      <c r="S65">
+        <v>21.1748135</v>
+      </c>
+      <c r="T65">
+        <v>0</v>
+      </c>
+      <c r="U65">
+        <v>0</v>
+      </c>
+      <c r="V65">
+        <v>0</v>
+      </c>
+      <c r="W65">
+        <v>0</v>
+      </c>
+      <c r="X65">
+        <v>0</v>
+      </c>
+      <c r="Y65">
+        <v>21.1748135</v>
+      </c>
+    </row>
+    <row r="66" spans="1:25">
+      <c r="A66" t="s">
+        <v>82</v>
+      </c>
+      <c r="B66" t="s">
+        <v>147</v>
+      </c>
+      <c r="C66" t="s">
+        <v>159</v>
+      </c>
+      <c r="D66" t="s">
+        <v>162</v>
+      </c>
+      <c r="E66">
         <v>5.3</v>
       </c>
-      <c r="F65">
-        <v>1</v>
-      </c>
-      <c r="G65" t="s">
-        <v>223</v>
-      </c>
-      <c r="H65">
+      <c r="F66">
+        <v>1</v>
+      </c>
+      <c r="G66" t="s">
+        <v>225</v>
+      </c>
+      <c r="H66">
         <v>36</v>
       </c>
-      <c r="I65" t="s">
-        <v>80</v>
-      </c>
-      <c r="J65" t="s">
-        <v>231</v>
-      </c>
-      <c r="K65" t="s">
-        <v>239</v>
-      </c>
-      <c r="L65" t="s">
-        <v>160</v>
-      </c>
-      <c r="M65" t="s">
-        <v>157</v>
-      </c>
-      <c r="N65" t="s">
-        <v>245</v>
-      </c>
-      <c r="O65" t="s">
-        <v>286</v>
-      </c>
-      <c r="P65" t="s">
-        <v>328</v>
-      </c>
-      <c r="Q65">
-        <v>1</v>
-      </c>
-      <c r="R65" t="s">
-        <v>223</v>
-      </c>
-      <c r="S65">
-        <v>36.386102</v>
-      </c>
-      <c r="T65">
-        <v>0</v>
-      </c>
-      <c r="U65">
-        <v>0</v>
-      </c>
-      <c r="V65">
-        <v>36.386102</v>
-      </c>
-      <c r="W65">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="1:23">
-      <c r="A66" t="s">
-        <v>81</v>
-      </c>
-      <c r="B66" t="s">
-        <v>146</v>
-      </c>
-      <c r="C66" t="s">
-        <v>157</v>
-      </c>
-      <c r="D66" t="s">
-        <v>160</v>
-      </c>
-      <c r="E66">
-        <v>5.2</v>
-      </c>
-      <c r="F66">
-        <v>1</v>
-      </c>
-      <c r="G66" t="s">
-        <v>224</v>
-      </c>
-      <c r="H66">
-        <v>18</v>
-      </c>
       <c r="I66" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J66" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="K66" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="L66" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="M66" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="N66" t="s">
-        <v>245</v>
+        <v>260</v>
       </c>
       <c r="O66" t="s">
-        <v>287</v>
+        <v>316</v>
       </c>
       <c r="P66" t="s">
-        <v>329</v>
+        <v>372</v>
       </c>
       <c r="Q66">
         <v>1</v>
       </c>
       <c r="R66" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="S66">
-        <v>17.781138</v>
+        <v>37.0116145</v>
       </c>
       <c r="T66">
         <v>0</v>
@@ -4664,24 +5660,30 @@
         <v>0</v>
       </c>
       <c r="V66">
-        <v>17.781138</v>
+        <v>0</v>
       </c>
       <c r="W66">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="1:23">
+        <v>37.0116145</v>
+      </c>
+      <c r="X66">
+        <v>0</v>
+      </c>
+      <c r="Y66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:25">
       <c r="A67" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B67" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C67" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="D67" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E67">
         <v>5.2</v>
@@ -4690,196 +5692,291 @@
         <v>1</v>
       </c>
       <c r="G67" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H67">
+        <v>18</v>
+      </c>
+      <c r="I67" t="s">
+        <v>83</v>
+      </c>
+      <c r="J67" t="s">
+        <v>232</v>
+      </c>
+      <c r="K67" t="s">
+        <v>247</v>
+      </c>
+      <c r="L67" t="s">
+        <v>162</v>
+      </c>
+      <c r="M67" t="s">
+        <v>159</v>
+      </c>
+      <c r="N67" t="s">
+        <v>260</v>
+      </c>
+      <c r="O67" t="s">
+        <v>317</v>
+      </c>
+      <c r="P67" t="s">
+        <v>373</v>
+      </c>
+      <c r="Q67">
+        <v>1</v>
+      </c>
+      <c r="R67" t="s">
+        <v>226</v>
+      </c>
+      <c r="S67">
+        <v>18.096385</v>
+      </c>
+      <c r="T67">
+        <v>0</v>
+      </c>
+      <c r="U67">
+        <v>0</v>
+      </c>
+      <c r="V67">
+        <v>0</v>
+      </c>
+      <c r="W67">
+        <v>18.096385</v>
+      </c>
+      <c r="X67">
+        <v>0</v>
+      </c>
+      <c r="Y67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:25">
+      <c r="A68" t="s">
+        <v>84</v>
+      </c>
+      <c r="B68" t="s">
+        <v>149</v>
+      </c>
+      <c r="C68" t="s">
+        <v>159</v>
+      </c>
+      <c r="D68" t="s">
+        <v>162</v>
+      </c>
+      <c r="E68">
+        <v>5.2</v>
+      </c>
+      <c r="F68">
+        <v>1</v>
+      </c>
+      <c r="G68" t="s">
+        <v>227</v>
+      </c>
+      <c r="H68">
         <v>36</v>
       </c>
-      <c r="I67" t="s">
-        <v>82</v>
-      </c>
-      <c r="J67" t="s">
-        <v>231</v>
-      </c>
-      <c r="K67" t="s">
-        <v>239</v>
-      </c>
-      <c r="L67" t="s">
-        <v>160</v>
-      </c>
-      <c r="M67" t="s">
-        <v>157</v>
-      </c>
-      <c r="N67" t="s">
-        <v>245</v>
-      </c>
-      <c r="O67" t="s">
-        <v>288</v>
-      </c>
-      <c r="P67" t="s">
-        <v>330</v>
-      </c>
-      <c r="Q67">
-        <v>1</v>
-      </c>
-      <c r="R67" t="s">
-        <v>225</v>
-      </c>
-      <c r="S67">
-        <v>36.385945</v>
-      </c>
-      <c r="T67">
-        <v>0</v>
-      </c>
-      <c r="U67">
-        <v>0</v>
-      </c>
-      <c r="V67">
-        <v>36.385945</v>
-      </c>
-      <c r="W67">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="1:23">
-      <c r="A68" t="s">
-        <v>83</v>
-      </c>
-      <c r="B68" t="s">
-        <v>148</v>
-      </c>
-      <c r="C68" t="s">
-        <v>157</v>
-      </c>
-      <c r="D68" t="s">
-        <v>160</v>
-      </c>
-      <c r="E68">
+      <c r="I68" t="s">
+        <v>84</v>
+      </c>
+      <c r="J68" t="s">
+        <v>232</v>
+      </c>
+      <c r="K68" t="s">
+        <v>247</v>
+      </c>
+      <c r="L68" t="s">
+        <v>162</v>
+      </c>
+      <c r="M68" t="s">
+        <v>159</v>
+      </c>
+      <c r="N68" t="s">
+        <v>260</v>
+      </c>
+      <c r="O68" t="s">
+        <v>318</v>
+      </c>
+      <c r="P68" t="s">
+        <v>374</v>
+      </c>
+      <c r="Q68">
+        <v>1</v>
+      </c>
+      <c r="R68" t="s">
+        <v>227</v>
+      </c>
+      <c r="S68">
+        <v>37.0116145</v>
+      </c>
+      <c r="T68">
+        <v>0</v>
+      </c>
+      <c r="U68">
+        <v>0</v>
+      </c>
+      <c r="V68">
+        <v>0</v>
+      </c>
+      <c r="W68">
+        <v>37.0116145</v>
+      </c>
+      <c r="X68">
+        <v>0</v>
+      </c>
+      <c r="Y68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:25">
+      <c r="A69" t="s">
+        <v>85</v>
+      </c>
+      <c r="B69" t="s">
+        <v>150</v>
+      </c>
+      <c r="C69" t="s">
+        <v>159</v>
+      </c>
+      <c r="D69" t="s">
+        <v>162</v>
+      </c>
+      <c r="E69">
         <v>5.6</v>
       </c>
-      <c r="F68">
-        <v>1</v>
-      </c>
-      <c r="G68" t="s">
-        <v>226</v>
-      </c>
-      <c r="H68">
+      <c r="F69">
+        <v>1</v>
+      </c>
+      <c r="G69" t="s">
+        <v>228</v>
+      </c>
+      <c r="H69">
         <v>90</v>
       </c>
-      <c r="I68" t="s">
-        <v>83</v>
-      </c>
-      <c r="J68" t="s">
-        <v>231</v>
-      </c>
-      <c r="K68" t="s">
-        <v>239</v>
-      </c>
-      <c r="L68" t="s">
-        <v>160</v>
-      </c>
-      <c r="M68" t="s">
-        <v>157</v>
-      </c>
-      <c r="N68" t="s">
-        <v>245</v>
-      </c>
-      <c r="O68" t="s">
-        <v>289</v>
-      </c>
-      <c r="P68" t="s">
-        <v>331</v>
-      </c>
-      <c r="Q68">
-        <v>1</v>
-      </c>
-      <c r="R68" t="s">
-        <v>226</v>
-      </c>
-      <c r="S68">
-        <v>91.8780515</v>
-      </c>
-      <c r="T68">
-        <v>0</v>
-      </c>
-      <c r="U68">
-        <v>0</v>
-      </c>
-      <c r="V68">
-        <v>91.8780515</v>
-      </c>
-      <c r="W68">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="1:23">
-      <c r="A69" t="s">
-        <v>84</v>
-      </c>
-      <c r="B69" t="s">
-        <v>149</v>
-      </c>
-      <c r="C69" t="s">
-        <v>157</v>
-      </c>
-      <c r="D69" t="s">
-        <v>160</v>
-      </c>
-      <c r="E69">
+      <c r="I69" t="s">
+        <v>85</v>
+      </c>
+      <c r="J69" t="s">
+        <v>244</v>
+      </c>
+      <c r="K69" t="s">
+        <v>259</v>
+      </c>
+      <c r="L69" t="s">
+        <v>162</v>
+      </c>
+      <c r="M69" t="s">
+        <v>159</v>
+      </c>
+      <c r="N69" t="s">
+        <v>260</v>
+      </c>
+      <c r="O69" t="s">
+        <v>319</v>
+      </c>
+      <c r="P69" t="s">
+        <v>375</v>
+      </c>
+      <c r="Q69">
+        <v>1</v>
+      </c>
+      <c r="R69" t="s">
+        <v>228</v>
+      </c>
+      <c r="S69">
+        <v>82.35027049999999</v>
+      </c>
+      <c r="T69">
+        <v>0</v>
+      </c>
+      <c r="U69">
+        <v>0</v>
+      </c>
+      <c r="V69">
+        <v>0</v>
+      </c>
+      <c r="W69">
+        <v>0</v>
+      </c>
+      <c r="X69">
+        <v>0</v>
+      </c>
+      <c r="Y69">
+        <v>82.35027049999999</v>
+      </c>
+    </row>
+    <row r="70" spans="1:25">
+      <c r="A70" t="s">
+        <v>86</v>
+      </c>
+      <c r="B70" t="s">
+        <v>151</v>
+      </c>
+      <c r="C70" t="s">
+        <v>159</v>
+      </c>
+      <c r="D70" t="s">
+        <v>162</v>
+      </c>
+      <c r="E70">
         <v>2.1</v>
       </c>
-      <c r="F69">
-        <v>1</v>
-      </c>
-      <c r="G69" t="s">
-        <v>227</v>
-      </c>
-      <c r="H69">
+      <c r="F70">
+        <v>1</v>
+      </c>
+      <c r="G70" t="s">
+        <v>229</v>
+      </c>
+      <c r="H70">
         <v>54</v>
       </c>
-      <c r="I69" t="s">
-        <v>84</v>
-      </c>
-      <c r="J69" t="s">
-        <v>231</v>
-      </c>
-      <c r="K69" t="s">
-        <v>239</v>
-      </c>
-      <c r="L69" t="s">
-        <v>160</v>
-      </c>
-      <c r="M69" t="s">
-        <v>157</v>
-      </c>
-      <c r="N69" t="s">
-        <v>245</v>
-      </c>
-      <c r="O69" t="s">
-        <v>290</v>
-      </c>
-      <c r="P69" t="s">
-        <v>332</v>
-      </c>
-      <c r="Q69">
-        <v>1</v>
-      </c>
-      <c r="R69" t="s">
-        <v>227</v>
-      </c>
-      <c r="S69">
-        <v>55.058047</v>
-      </c>
-      <c r="T69">
-        <v>0</v>
-      </c>
-      <c r="U69">
-        <v>0</v>
-      </c>
-      <c r="V69">
-        <v>55.058047</v>
-      </c>
-      <c r="W69">
+      <c r="I70" t="s">
+        <v>86</v>
+      </c>
+      <c r="J70" t="s">
+        <v>232</v>
+      </c>
+      <c r="K70" t="s">
+        <v>247</v>
+      </c>
+      <c r="L70" t="s">
+        <v>162</v>
+      </c>
+      <c r="M70" t="s">
+        <v>159</v>
+      </c>
+      <c r="N70" t="s">
+        <v>260</v>
+      </c>
+      <c r="O70" t="s">
+        <v>320</v>
+      </c>
+      <c r="P70" t="s">
+        <v>376</v>
+      </c>
+      <c r="Q70">
+        <v>1</v>
+      </c>
+      <c r="R70" t="s">
+        <v>229</v>
+      </c>
+      <c r="S70">
+        <v>48.657669</v>
+      </c>
+      <c r="T70">
+        <v>0</v>
+      </c>
+      <c r="U70">
+        <v>0</v>
+      </c>
+      <c r="V70">
+        <v>0</v>
+      </c>
+      <c r="W70">
+        <v>48.657669</v>
+      </c>
+      <c r="X70">
+        <v>0</v>
+      </c>
+      <c r="Y70">
         <v>0</v>
       </c>
     </row>
